--- a/careerstop.xlsx
+++ b/careerstop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galja\pgaljan.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33FA7D25-2B83-4EEA-BAC3-C789222752DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF751D2-69A9-4685-A267-CA7C8E5CA3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-37" windowWidth="28996" windowHeight="15675" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
   <si>
     <t>Tools</t>
   </si>
@@ -91,63 +91,12 @@
     <t>Core</t>
   </si>
   <si>
-    <t>P&amp;L Management</t>
-  </si>
-  <si>
-    <t>Supply Chain Coordination</t>
-  </si>
-  <si>
-    <t>Customer Service Management</t>
-  </si>
-  <si>
-    <t>Compliance Management</t>
-  </si>
-  <si>
-    <t>Seasonal Planning</t>
-  </si>
-  <si>
-    <t>Budget Forecasting</t>
-  </si>
-  <si>
-    <t>Daily Standups</t>
-  </si>
-  <si>
-    <t>Performance Dashboards</t>
-  </si>
-  <si>
-    <t>Mystery Shopping</t>
-  </si>
-  <si>
-    <t>Standard Operating Procedures</t>
-  </si>
-  <si>
     <t>Organization</t>
   </si>
   <si>
     <t>Location</t>
   </si>
   <si>
-    <t>Customer Satisfaction</t>
-  </si>
-  <si>
-    <t>Operational Efficiency</t>
-  </si>
-  <si>
-    <t>Team Development</t>
-  </si>
-  <si>
-    <t>Brand Consistency</t>
-  </si>
-  <si>
-    <t>Safety &amp; Compliance</t>
-  </si>
-  <si>
-    <t>Profitability</t>
-  </si>
-  <si>
-    <t>Community Engagement</t>
-  </si>
-  <si>
     <t>Tasks/Deliverables</t>
   </si>
   <si>
@@ -304,91 +253,151 @@
     <t>Sep 2023</t>
   </si>
   <si>
-    <t>Acme Retail</t>
-  </si>
-  <si>
-    <t>Store Manager</t>
-  </si>
-  <si>
-    <t>Retail/Hospitality</t>
-  </si>
-  <si>
-    <t>Square</t>
-  </si>
-  <si>
-    <t>Toast</t>
-  </si>
-  <si>
-    <t>Shopify</t>
-  </si>
-  <si>
-    <t>NetSuite</t>
-  </si>
-  <si>
-    <t>TradeGecko</t>
-  </si>
-  <si>
-    <t>Deputy</t>
-  </si>
-  <si>
-    <t>Excel</t>
-  </si>
-  <si>
-    <t>Slack</t>
-  </si>
-  <si>
-    <t>PowerBI</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>ZenDesk</t>
-  </si>
-  <si>
     <t>Process Optimization</t>
   </si>
   <si>
-    <t>Performance Monitoring</t>
-  </si>
-  <si>
-    <t>Resource Allocation</t>
-  </si>
-  <si>
-    <t>Cross-Functional Coordination</t>
-  </si>
-  <si>
-    <t>Staff Scheduling</t>
-  </si>
-  <si>
-    <t>Vendor Management</t>
-  </si>
-  <si>
-    <t>Inventory Management</t>
-  </si>
-  <si>
-    <t>Store Performance Management</t>
-  </si>
-  <si>
-    <t>Staff Training and Development</t>
-  </si>
-  <si>
-    <t>Mechandising Strategy</t>
-  </si>
-  <si>
-    <t>Crisis management</t>
-  </si>
-  <si>
-    <t>Multi-location Oversight</t>
-  </si>
-  <si>
-    <t>Staff cross-training</t>
-  </si>
-  <si>
-    <t>Retail Operations</t>
-  </si>
-  <si>
-    <t>Rowan Davis</t>
+    <t>Patient Registration</t>
+  </si>
+  <si>
+    <t>Insurance Verification</t>
+  </si>
+  <si>
+    <t>Appointment Scheduling</t>
+  </si>
+  <si>
+    <t>Medical Records Management</t>
+  </si>
+  <si>
+    <t>Billing Coordination</t>
+  </si>
+  <si>
+    <t>Acme Medical</t>
+  </si>
+  <si>
+    <t>Morgan Chen</t>
+  </si>
+  <si>
+    <t>Healthcare Administrator</t>
+  </si>
+  <si>
+    <t>Administrator</t>
+  </si>
+  <si>
+    <t>Healthcare Operations</t>
+  </si>
+  <si>
+    <t>Patient Service Coordination</t>
+  </si>
+  <si>
+    <t>Healthcare Compliance</t>
+  </si>
+  <si>
+    <t>Data Management</t>
+  </si>
+  <si>
+    <t>Communication Facilitation</t>
+  </si>
+  <si>
+    <t>Patient Satisfaction</t>
+  </si>
+  <si>
+    <t>Confidentiality</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>Compliance</t>
+  </si>
+  <si>
+    <t>Professional Communication</t>
+  </si>
+  <si>
+    <t>Patient Check-in/Check-out</t>
+  </si>
+  <si>
+    <t>Daily Appointment Confirmations</t>
+  </si>
+  <si>
+    <t>Insurance Authorization Requests</t>
+  </si>
+  <si>
+    <t>Medical Record Updates</t>
+  </si>
+  <si>
+    <t>Revenue Cycle Monitoring</t>
+  </si>
+  <si>
+    <t>HIPAA Compliance</t>
+  </si>
+  <si>
+    <t>Medical Terminology</t>
+  </si>
+  <si>
+    <t>Insurance Claims Processing</t>
+  </si>
+  <si>
+    <t>Patient Communication</t>
+  </si>
+  <si>
+    <t>Medical Coding (ICD-10/CPT)</t>
+  </si>
+  <si>
+    <t>Electronic Health Records Management</t>
+  </si>
+  <si>
+    <t>Front Desk Operations</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Management</t>
+  </si>
+  <si>
+    <t>Patient Flow Coordination</t>
+  </si>
+  <si>
+    <t>Healthcare Documentation</t>
+  </si>
+  <si>
+    <t>Epic MyChart</t>
+  </si>
+  <si>
+    <t>Cerner PowerChart</t>
+  </si>
+  <si>
+    <t>athenahealth</t>
+  </si>
+  <si>
+    <t>Microsoft Office 365</t>
+  </si>
+  <si>
+    <t>Kareo</t>
+  </si>
+  <si>
+    <t>NextGen</t>
+  </si>
+  <si>
+    <t>Cisco Phone System</t>
+  </si>
+  <si>
+    <t>Availity</t>
+  </si>
+  <si>
+    <t>Xerox WorkCentre</t>
+  </si>
+  <si>
+    <t>Brother MFC Series</t>
+  </si>
+  <si>
+    <t>Square Terminal</t>
+  </si>
+  <si>
+    <t>Solutionreach</t>
+  </si>
+  <si>
+    <t>Zocdoc</t>
   </si>
 </sst>
 </file>
@@ -716,7 +725,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -773,6 +781,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -857,7 +868,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>15</xdr:col>
-          <xdr:colOff>1628214</xdr:colOff>
+          <xdr:colOff>1628215</xdr:colOff>
           <xdr:row>37</xdr:row>
           <xdr:rowOff>133629</xdr:rowOff>
         </xdr:to>
@@ -874,7 +885,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$AD$1:$AI$17" spid="_x0000_s1075"/>
+                  <a14:cameraTool cellRange="$AD$1:$AI$17" spid="_x0000_s1077"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1264,7 +1275,7 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.3984375" customWidth="1"/>
     <col min="3" max="3" width="3.46484375" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="3.46484375" customWidth="1"/>
@@ -1278,7 +1289,7 @@
     <col min="14" max="14" width="25.86328125" customWidth="1"/>
     <col min="15" max="15" width="3.46484375" customWidth="1"/>
     <col min="16" max="16" width="25.86328125" customWidth="1"/>
-    <col min="28" max="28" width="9.06640625" style="40"/>
+    <col min="28" max="28" width="9.06640625" style="39"/>
     <col min="30" max="33" width="29.9296875" customWidth="1"/>
     <col min="34" max="34" width="1.86328125" customWidth="1"/>
     <col min="35" max="35" width="13.3984375" customWidth="1"/>
@@ -1287,10 +1298,10 @@
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>108</v>
+        <v>16</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>70</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>8</v>
@@ -1302,7 +1313,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="L1" s="4" t="s">
         <v>5</v>
@@ -1313,16 +1324,16 @@
       <c r="P1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="15" t="str">
+      <c r="AD1" s="40" t="str">
         <f>B1&amp; " ("&amp;B2&amp;")"</f>
-        <v>Rowan Davis (Retail Operations)</v>
-      </c>
-      <c r="AE1" s="34" t="str">
+        <v>Morgan Chen (Healthcare Administrator)</v>
+      </c>
+      <c r="AE1" s="33" t="str">
         <f>B7&amp;" with "&amp;B3&amp;" ("&amp;B4&amp;")"</f>
-        <v>Store Manager with Acme Retail (Anytown, USA)</v>
-      </c>
-      <c r="AF1" s="35"/>
-      <c r="AG1" s="33" t="str">
+        <v>Administrator with Acme Medical (Anytown, USA)</v>
+      </c>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="32" t="str">
         <f>B5&amp;" - "&amp;B6</f>
         <v>Feb 2021 - Sep 2023</v>
       </c>
@@ -1331,56 +1342,56 @@
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="D2" s="38" t="b">
+      <c r="B2" s="35" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>83</v>
+      <c r="E2" s="35" t="s">
+        <v>99</v>
       </c>
       <c r="F2" s="7"/>
-      <c r="G2" s="36" t="s">
-        <v>94</v>
+      <c r="G2" s="35" t="s">
+        <v>74</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="36" t="s">
-        <v>98</v>
+      <c r="I2" s="35" t="s">
+        <v>64</v>
       </c>
       <c r="J2" s="7"/>
       <c r="K2" s="7" t="b">
         <f>IF(L2="","",ISEVEN(ROW()))</f>
         <v>1</v>
       </c>
-      <c r="L2" s="36" t="s">
-        <v>9</v>
+      <c r="L2" s="35" t="s">
+        <v>89</v>
       </c>
       <c r="M2" s="7"/>
-      <c r="N2" s="36" t="s">
-        <v>15</v>
+      <c r="N2" s="35" t="s">
+        <v>84</v>
       </c>
       <c r="O2" s="7"/>
-      <c r="P2" s="36" t="s">
-        <v>21</v>
+      <c r="P2" s="35" t="s">
+        <v>78</v>
       </c>
       <c r="AD2" s="13" t="str" cm="1">
-        <f t="array" ref="AD2:AD15">_xlfn.VSTACK(
+        <f t="array" ref="AD2:AD17">_xlfn.VSTACK(
 "Tools",
 "Core","  • "&amp;_xlfn._xlws.FILTER(E1:E17,D1:D17=TRUE),
 "Incidental","  • "&amp;_xlfn._xlws.FILTER(E1:E17,(D1:D17=FALSE)*(E1:E17&lt;&gt;"")))</f>
         <v>Tools</v>
       </c>
       <c r="AE2" s="12" t="str" cm="1">
-        <f t="array" ref="AE2:AE7">_xlfn.VSTACK("Profession",B2,"  • "&amp;_xlfn._xlws.FILTER(G2:G7,G2:G7&lt;&gt;""))</f>
+        <f t="array" ref="AE2:AE8">_xlfn.VSTACK("Profession",B2,"  • "&amp;_xlfn._xlws.FILTER(G2:G7,G2:G7&lt;&gt;""))</f>
         <v>Profession</v>
       </c>
       <c r="AF2" s="11" t="str" cm="1">
-        <f t="array" ref="AF2:AF8">_xlfn.VSTACK("Job",B7,B8,"  • "&amp;_xlfn._xlws.FILTER(I2:I6,I2:I6&lt;&gt;""))</f>
+        <f t="array" ref="AF2:AF9">_xlfn.VSTACK("Job",B7,B8,"  • "&amp;_xlfn._xlws.FILTER(I2:I6,I2:I6&lt;&gt;""))</f>
         <v>Job</v>
       </c>
       <c r="AG2" s="14" t="str" cm="1">
-        <f t="array" ref="AG2:AG15">_xlfn.VSTACK(
+        <f t="array" ref="AG2:AG14">_xlfn.VSTACK(
 "Practices","  • "&amp;_xlfn._xlws.FILTER(N2:N17,N2:N17&lt;&gt;""),
 "Priorities","  • "&amp;_xlfn._xlws.FILTER(P2:P17,P2:P17&lt;&gt;""))</f>
         <v>Practices</v>
@@ -1388,215 +1399,219 @@
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A3" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="38" t="b">
+        <v>9</v>
+      </c>
+      <c r="B3" s="35" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="36" t="s">
-        <v>84</v>
+      <c r="E3" s="35" t="s">
+        <v>100</v>
       </c>
       <c r="F3" s="7"/>
-      <c r="G3" s="36" t="s">
-        <v>95</v>
+      <c r="G3" s="35" t="s">
+        <v>75</v>
       </c>
       <c r="H3" s="7"/>
-      <c r="I3" s="36" t="s">
-        <v>99</v>
+      <c r="I3" s="35" t="s">
+        <v>65</v>
       </c>
       <c r="J3" s="7"/>
       <c r="K3" s="7" t="b">
         <f t="shared" ref="K3:K17" si="0">IF(L3="","",ISEVEN(ROW()))</f>
         <v>0</v>
       </c>
-      <c r="L3" s="36" t="s">
-        <v>102</v>
+      <c r="L3" s="35" t="s">
+        <v>90</v>
       </c>
       <c r="M3" s="7"/>
-      <c r="N3" s="36" t="s">
-        <v>16</v>
+      <c r="N3" s="35" t="s">
+        <v>85</v>
       </c>
       <c r="O3" s="7"/>
-      <c r="P3" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="AD3" s="16" t="str">
+      <c r="P3" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="AD3" s="15" t="str">
         <v>Core</v>
       </c>
-      <c r="AE3" s="17" t="str">
-        <v>Retail Operations</v>
-      </c>
-      <c r="AF3" s="22" t="str">
-        <v>Store Manager</v>
-      </c>
-      <c r="AG3" s="21" t="str">
-        <v xml:space="preserve">  • Daily Standups</v>
+      <c r="AE3" s="16" t="str">
+        <v>Healthcare Administrator</v>
+      </c>
+      <c r="AF3" s="21" t="str">
+        <v>Administrator</v>
+      </c>
+      <c r="AG3" s="20" t="str">
+        <v xml:space="preserve">  • Patient Check-in/Check-out</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="38" t="b">
+        <v>10</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="36" t="s">
-        <v>85</v>
+      <c r="E4" s="35" t="s">
+        <v>101</v>
       </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="36" t="s">
-        <v>96</v>
+      <c r="G4" s="35" t="s">
+        <v>76</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="36" t="s">
-        <v>100</v>
+      <c r="I4" s="35" t="s">
+        <v>66</v>
       </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L4" s="36" t="s">
-        <v>103</v>
+      <c r="L4" s="35" t="s">
+        <v>91</v>
       </c>
       <c r="M4" s="7"/>
-      <c r="N4" s="36" t="s">
-        <v>17</v>
+      <c r="N4" s="35" t="s">
+        <v>86</v>
       </c>
       <c r="O4" s="7"/>
-      <c r="P4" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="AD4" s="16" t="str">
-        <v xml:space="preserve">  • Square</v>
-      </c>
-      <c r="AE4" s="18" t="str">
-        <v xml:space="preserve">  • Process Optimization</v>
-      </c>
-      <c r="AF4" s="23" t="str">
-        <v>Retail/Hospitality</v>
-      </c>
-      <c r="AG4" s="21" t="str">
-        <v xml:space="preserve">  • Performance Dashboards</v>
+      <c r="P4" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD4" s="15" t="str">
+        <v xml:space="preserve">  • Epic MyChart</v>
+      </c>
+      <c r="AE4" s="17" t="str">
+        <v xml:space="preserve">  • Patient Service Coordination</v>
+      </c>
+      <c r="AF4" s="22" t="str">
+        <v>Healthcare Operations</v>
+      </c>
+      <c r="AG4" s="20" t="str">
+        <v xml:space="preserve">  • Daily Appointment Confirmations</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A5" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B5" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="38" t="b">
+        <v>13</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="36" t="s">
-        <v>86</v>
+      <c r="E5" s="35" t="s">
+        <v>102</v>
       </c>
       <c r="F5" s="7"/>
-      <c r="G5" s="36" t="s">
-        <v>97</v>
+      <c r="G5" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="H5" s="7"/>
-      <c r="I5" s="36" t="s">
-        <v>101</v>
+      <c r="I5" s="35" t="s">
+        <v>67</v>
       </c>
       <c r="J5" s="7"/>
       <c r="K5" s="7" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="36" t="s">
-        <v>10</v>
+      <c r="L5" s="35" t="s">
+        <v>92</v>
       </c>
       <c r="M5" s="7"/>
-      <c r="N5" s="36" t="s">
-        <v>106</v>
+      <c r="N5" s="35" t="s">
+        <v>87</v>
       </c>
       <c r="O5" s="7"/>
-      <c r="P5" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="AD5" s="16" t="str">
-        <v xml:space="preserve">  • Toast</v>
-      </c>
-      <c r="AE5" s="18" t="str">
-        <v xml:space="preserve">  • Performance Monitoring</v>
-      </c>
-      <c r="AF5" s="18" t="str">
-        <v xml:space="preserve">  • Staff Scheduling</v>
-      </c>
-      <c r="AG5" s="21" t="str">
-        <v xml:space="preserve">  • Mystery Shopping</v>
+      <c r="P5" s="35" t="s">
+        <v>81</v>
+      </c>
+      <c r="AD5" s="15" t="str">
+        <v xml:space="preserve">  • Cerner PowerChart</v>
+      </c>
+      <c r="AE5" s="17" t="str">
+        <v xml:space="preserve">  • Healthcare Compliance</v>
+      </c>
+      <c r="AF5" s="17" t="str">
+        <v xml:space="preserve">  • Patient Registration</v>
+      </c>
+      <c r="AG5" s="20" t="str">
+        <v xml:space="preserve">  • Insurance Authorization Requests</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="38" t="b">
+        <v>14</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>87</v>
+      <c r="E6" s="35" t="s">
+        <v>103</v>
       </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="36"/>
+      <c r="G6" s="35" t="s">
+        <v>63</v>
+      </c>
       <c r="H6" s="7"/>
-      <c r="I6" s="36"/>
+      <c r="I6" s="35" t="s">
+        <v>68</v>
+      </c>
       <c r="J6" s="7"/>
       <c r="K6" s="7" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L6" s="36" t="s">
-        <v>11</v>
+      <c r="L6" s="35" t="s">
+        <v>93</v>
       </c>
       <c r="M6" s="7"/>
-      <c r="N6" s="36" t="s">
-        <v>18</v>
+      <c r="N6" s="35" t="s">
+        <v>88</v>
       </c>
       <c r="O6" s="7"/>
-      <c r="P6" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="AD6" s="16" t="str">
-        <v xml:space="preserve">  • Shopify</v>
-      </c>
-      <c r="AE6" s="18" t="str">
-        <v xml:space="preserve">  • Resource Allocation</v>
-      </c>
-      <c r="AF6" s="18" t="str">
-        <v xml:space="preserve">  • Vendor Management</v>
-      </c>
-      <c r="AG6" s="21" t="str">
-        <v xml:space="preserve">  • Staff cross-training</v>
+      <c r="P6" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD6" s="15" t="str">
+        <v xml:space="preserve">  • athenahealth</v>
+      </c>
+      <c r="AE6" s="17" t="str">
+        <v xml:space="preserve">  • Data Management</v>
+      </c>
+      <c r="AF6" s="17" t="str">
+        <v xml:space="preserve">  • Insurance Verification</v>
+      </c>
+      <c r="AG6" s="20" t="str">
+        <v xml:space="preserve">  • Medical Record Updates</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" s="38" t="b">
+      <c r="B7" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>88</v>
+      <c r="E7" s="35" t="s">
+        <v>104</v>
       </c>
       <c r="F7" s="7"/>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="7"/>
       <c r="I7" s="8"/>
       <c r="J7" s="7"/>
@@ -1604,40 +1619,40 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="36" t="s">
-        <v>12</v>
+      <c r="L7" s="35" t="s">
+        <v>94</v>
       </c>
       <c r="M7" s="7"/>
-      <c r="N7" s="36"/>
+      <c r="N7" s="35"/>
       <c r="O7" s="7"/>
-      <c r="P7" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD7" s="16" t="str">
-        <v xml:space="preserve">  • NetSuite</v>
-      </c>
-      <c r="AE7" s="18" t="str">
-        <v xml:space="preserve">  • Cross-Functional Coordination</v>
-      </c>
-      <c r="AF7" s="18" t="str">
-        <v xml:space="preserve">  • Inventory Management</v>
-      </c>
-      <c r="AG7" s="21" t="str">
-        <v xml:space="preserve">  • Standard Operating Procedures</v>
+      <c r="P7" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="AD7" s="15" t="str">
+        <v xml:space="preserve">  • Microsoft Office 365</v>
+      </c>
+      <c r="AE7" s="17" t="str">
+        <v xml:space="preserve">  • Communication Facilitation</v>
+      </c>
+      <c r="AF7" s="17" t="str">
+        <v xml:space="preserve">  • Appointment Scheduling</v>
+      </c>
+      <c r="AG7" s="20" t="str">
+        <v xml:space="preserve">  • Revenue Cycle Monitoring</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="38" t="b">
+      <c r="B8" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="37" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>89</v>
+      <c r="E8" s="35" t="s">
+        <v>105</v>
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="8"/>
@@ -1648,32 +1663,32 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L8" s="36" t="s">
-        <v>105</v>
+      <c r="L8" s="35" t="s">
+        <v>95</v>
       </c>
       <c r="M8" s="7"/>
-      <c r="N8" s="36"/>
+      <c r="N8" s="35"/>
       <c r="O8" s="7"/>
-      <c r="P8" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD8" s="16" t="str">
-        <v xml:space="preserve">  • TradeGecko</v>
-      </c>
-      <c r="AE8" s="18"/>
-      <c r="AF8" s="18" t="str">
-        <v xml:space="preserve">  • Store Performance Management</v>
+      <c r="P8" s="35"/>
+      <c r="AD8" s="15" t="str">
+        <v xml:space="preserve">  • Kareo</v>
+      </c>
+      <c r="AE8" s="17" t="str">
+        <v xml:space="preserve">  • Process Optimization</v>
+      </c>
+      <c r="AF8" s="17" t="str">
+        <v xml:space="preserve">  • Medical Records Management</v>
       </c>
       <c r="AG8" s="10" t="str">
         <v>Priorities</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D9" s="38" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>90</v>
+      <c r="D9" s="37" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="35" t="s">
+        <v>106</v>
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
@@ -1684,28 +1699,30 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="36" t="s">
-        <v>104</v>
+      <c r="L9" s="35" t="s">
+        <v>96</v>
       </c>
       <c r="M9" s="7"/>
-      <c r="N9" s="36"/>
+      <c r="N9" s="35"/>
       <c r="O9" s="7"/>
-      <c r="P9" s="36"/>
-      <c r="AD9" s="16" t="str">
-        <v xml:space="preserve">  • Deputy</v>
-      </c>
-      <c r="AE9" s="19"/>
-      <c r="AF9" s="24"/>
-      <c r="AG9" s="21" t="str">
-        <v xml:space="preserve">  • Customer Satisfaction</v>
+      <c r="P9" s="35"/>
+      <c r="AD9" s="15" t="str">
+        <v xml:space="preserve">  • NextGen</v>
+      </c>
+      <c r="AE9" s="18"/>
+      <c r="AF9" s="23" t="str">
+        <v xml:space="preserve">  • Billing Coordination</v>
+      </c>
+      <c r="AG9" s="20" t="str">
+        <v xml:space="preserve">  • Patient Satisfaction</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D10" s="38" t="b">
+      <c r="D10" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="36" t="s">
-        <v>91</v>
+      <c r="E10" s="35" t="s">
+        <v>107</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
@@ -1716,30 +1733,30 @@
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L10" s="36" t="s">
-        <v>13</v>
+      <c r="L10" s="35" t="s">
+        <v>97</v>
       </c>
       <c r="M10" s="7"/>
       <c r="N10" s="8"/>
       <c r="O10" s="7"/>
       <c r="P10" s="8"/>
-      <c r="AD10" s="20" t="str">
-        <v xml:space="preserve">  • Excel</v>
-      </c>
-      <c r="AE10" s="28" t="s">
+      <c r="AD10" s="19" t="str">
+        <v xml:space="preserve">  • Cisco Phone System</v>
+      </c>
+      <c r="AE10" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="AF10" s="28"/>
-      <c r="AG10" s="21" t="str">
-        <v xml:space="preserve">  • Operational Efficiency</v>
+      <c r="AF10" s="27"/>
+      <c r="AG10" s="20" t="str">
+        <v xml:space="preserve">  • Confidentiality</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D11" s="38" t="b">
+      <c r="D11" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="36" t="s">
-        <v>92</v>
+      <c r="E11" s="35" t="s">
+        <v>108</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1750,35 +1767,35 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L11" s="36" t="s">
-        <v>14</v>
+      <c r="L11" s="35" t="s">
+        <v>98</v>
       </c>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
       <c r="O11" s="7"/>
       <c r="P11" s="7"/>
-      <c r="AD11" s="20" t="str">
-        <v xml:space="preserve">  • Slack</v>
-      </c>
-      <c r="AE11" s="29" t="str" cm="1">
+      <c r="AD11" s="19" t="str">
+        <v>Incidental</v>
+      </c>
+      <c r="AE11" s="28" t="str" cm="1">
         <f t="array" ref="AE11:AF15">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
 " • "&amp;_xlfn._xlws.FILTER(L2:L17,K2:K17=TRUE),
 " • "&amp;_xlfn._xlws.FILTER(L2:L17,(K2:K17=FALSE)*(L2:L17&lt;&gt;""))),"")),"")</f>
-        <v xml:space="preserve"> • P&amp;L Management</v>
-      </c>
-      <c r="AF11" s="29" t="str">
-        <v xml:space="preserve"> • Staff Training and Development</v>
-      </c>
-      <c r="AG11" s="21" t="str">
-        <v xml:space="preserve">  • Team Development</v>
+        <v xml:space="preserve"> • HIPAA Compliance</v>
+      </c>
+      <c r="AF11" s="28" t="str">
+        <v xml:space="preserve"> • Medical Terminology</v>
+      </c>
+      <c r="AG11" s="20" t="str">
+        <v xml:space="preserve">  • Accuracy</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D12" s="38" t="b">
+      <c r="D12" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="36" t="s">
-        <v>93</v>
+      <c r="E12" s="35" t="s">
+        <v>109</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
@@ -1789,29 +1806,31 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L12" s="36"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="7"/>
       <c r="N12" s="7"/>
       <c r="O12" s="7"/>
       <c r="P12" s="7"/>
-      <c r="AD12" s="20" t="str">
-        <v>Incidental</v>
-      </c>
-      <c r="AE12" s="29" t="str">
-        <v xml:space="preserve"> • Mechandising Strategy</v>
-      </c>
-      <c r="AF12" s="29" t="str">
-        <v xml:space="preserve"> • Supply Chain Coordination</v>
-      </c>
-      <c r="AG12" s="21" t="str">
-        <v xml:space="preserve">  • Brand Consistency</v>
+      <c r="AD12" s="19" t="str">
+        <v xml:space="preserve">  • Availity</v>
+      </c>
+      <c r="AE12" s="28" t="str">
+        <v xml:space="preserve"> • Insurance Claims Processing</v>
+      </c>
+      <c r="AF12" s="28" t="str">
+        <v xml:space="preserve"> • Patient Communication</v>
+      </c>
+      <c r="AG12" s="20" t="str">
+        <v xml:space="preserve">  • Efficiency</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D13" s="38" t="b">
+      <c r="D13" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="36"/>
+      <c r="E13" s="35" t="s">
+        <v>110</v>
+      </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
@@ -1821,29 +1840,31 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L13" s="36"/>
+      <c r="L13" s="35"/>
       <c r="M13" s="7"/>
       <c r="N13" s="7"/>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
-      <c r="AD13" s="20" t="str">
-        <v xml:space="preserve">  • PowerBI</v>
-      </c>
-      <c r="AE13" s="29" t="str">
-        <v xml:space="preserve"> • Customer Service Management</v>
-      </c>
-      <c r="AF13" s="29" t="str">
-        <v xml:space="preserve"> • Compliance Management</v>
-      </c>
-      <c r="AG13" s="21" t="str">
-        <v xml:space="preserve">  • Safety &amp; Compliance</v>
+      <c r="AD13" s="19" t="str">
+        <v xml:space="preserve">  • Xerox WorkCentre</v>
+      </c>
+      <c r="AE13" s="28" t="str">
+        <v xml:space="preserve"> • Medical Coding (ICD-10/CPT)</v>
+      </c>
+      <c r="AF13" s="28" t="str">
+        <v xml:space="preserve"> • Electronic Health Records Management</v>
+      </c>
+      <c r="AG13" s="20" t="str">
+        <v xml:space="preserve">  • Compliance</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D14" s="38" t="b">
+      <c r="D14" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="36"/>
+      <c r="E14" s="35" t="s">
+        <v>111</v>
+      </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
@@ -1853,29 +1874,29 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L14" s="36"/>
+      <c r="L14" s="35"/>
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="7"/>
       <c r="P14" s="7"/>
-      <c r="AD14" s="20" t="str">
-        <v xml:space="preserve">  • Salesforce</v>
-      </c>
-      <c r="AE14" s="29" t="str">
-        <v xml:space="preserve"> • Multi-location Oversight</v>
-      </c>
-      <c r="AF14" s="29" t="str">
-        <v xml:space="preserve"> • Crisis management</v>
-      </c>
-      <c r="AG14" s="21" t="str">
-        <v xml:space="preserve">  • Profitability</v>
+      <c r="AD14" s="19" t="str">
+        <v xml:space="preserve">  • Brother MFC Series</v>
+      </c>
+      <c r="AE14" s="28" t="str">
+        <v xml:space="preserve"> • Front Desk Operations</v>
+      </c>
+      <c r="AF14" s="28" t="str">
+        <v xml:space="preserve"> • Accounts Receivable Management</v>
+      </c>
+      <c r="AG14" s="20" t="str">
+        <v xml:space="preserve">  • Professional Communication</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D15" s="38" t="b">
+      <c r="D15" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="39"/>
+      <c r="E15" s="38"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
@@ -1885,32 +1906,30 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="36"/>
+      <c r="L15" s="35"/>
       <c r="M15" s="7"/>
       <c r="N15" s="7"/>
       <c r="O15" s="7"/>
       <c r="P15" s="7"/>
-      <c r="AD15" s="20" t="str">
-        <v xml:space="preserve">  • ZenDesk</v>
-      </c>
-      <c r="AE15" s="29" t="str">
-        <v xml:space="preserve"> • Seasonal Planning</v>
-      </c>
-      <c r="AF15" s="29" t="str">
-        <v xml:space="preserve"> • Budget Forecasting</v>
-      </c>
-      <c r="AG15" s="21" t="str">
-        <v xml:space="preserve">  • Community Engagement</v>
-      </c>
-      <c r="AI15" s="25" t="s">
-        <v>29</v>
+      <c r="AD15" s="19" t="str">
+        <v xml:space="preserve">  • Square Terminal</v>
+      </c>
+      <c r="AE15" s="28" t="str">
+        <v xml:space="preserve"> • Patient Flow Coordination</v>
+      </c>
+      <c r="AF15" s="28" t="str">
+        <v xml:space="preserve"> • Healthcare Documentation</v>
+      </c>
+      <c r="AG15" s="20"/>
+      <c r="AI15" s="24" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D16" s="38" t="b">
+      <c r="D16" s="37" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="36"/>
+      <c r="E16" s="35"/>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
@@ -1925,12 +1944,14 @@
       <c r="N16" s="7"/>
       <c r="O16" s="7"/>
       <c r="P16" s="7"/>
-      <c r="AD16" s="20"/>
-      <c r="AE16" s="29"/>
-      <c r="AF16" s="29"/>
-      <c r="AG16" s="21"/>
-      <c r="AI16" s="26" t="s">
-        <v>34</v>
+      <c r="AD16" s="19" t="str">
+        <v xml:space="preserve">  • Solutionreach</v>
+      </c>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="20"/>
+      <c r="AI16" s="25" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="4:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -1952,12 +1973,14 @@
       <c r="N17" s="7"/>
       <c r="O17" s="7"/>
       <c r="P17" s="7"/>
-      <c r="AD17" s="30"/>
-      <c r="AE17" s="31"/>
-      <c r="AF17" s="31"/>
-      <c r="AG17" s="32"/>
-      <c r="AI17" s="27" t="s">
-        <v>35</v>
+      <c r="AD17" s="29" t="str">
+        <v xml:space="preserve">  • Zocdoc</v>
+      </c>
+      <c r="AE17" s="30"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="31"/>
+      <c r="AI17" s="26" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -2008,13 +2031,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B1" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
@@ -2022,10 +2045,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.45">
@@ -2033,10 +2056,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.45">
@@ -2044,10 +2067,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -2055,10 +2078,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.45">
@@ -2066,10 +2089,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
@@ -2077,10 +2100,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.45">
@@ -2088,10 +2111,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.45">
@@ -2099,10 +2122,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.45">
@@ -2110,10 +2133,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.45">
@@ -2121,10 +2144,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.45">
@@ -2132,10 +2155,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.45">
@@ -2143,10 +2166,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.45">
@@ -2154,10 +2177,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.45">
@@ -2165,10 +2188,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
@@ -2176,10 +2199,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -2187,10 +2210,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -2198,10 +2221,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -2209,10 +2232,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -2220,10 +2243,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -2231,10 +2254,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>

--- a/careerstop.xlsx
+++ b/careerstop.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galja\pgaljan.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBF751D2-69A9-4685-A267-CA7C8E5CA3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA38F772-D867-4F39-8418-985395839C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-37" windowWidth="28996" windowHeight="15675" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
   </bookViews>
   <sheets>
     <sheet name="careerstop" sheetId="1" r:id="rId1"/>
-    <sheet name="names" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="names" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="randomName">_xlfn.XLOOKUP(RANDBETWEEN(1,20),Table1[index],Table1[first]) &amp; " " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,20),Table1[index],Table1[last])</definedName>
+    <definedName name="randomName">_xlfn.XLOOKUP(RANDBETWEEN(1,20),names[index],names[first]) &amp; " " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,20),names[index],names[last])</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="309">
   <si>
     <t>Tools</t>
   </si>
@@ -220,9 +220,6 @@
     <t>Rodriguez</t>
   </si>
   <si>
-    <t>Singh</t>
-  </si>
-  <si>
     <t>Wilson</t>
   </si>
   <si>
@@ -232,9 +229,6 @@
     <t>Jackson</t>
   </si>
   <si>
-    <t>White</t>
-  </si>
-  <si>
     <t>Lewis</t>
   </si>
   <si>
@@ -256,148 +250,745 @@
     <t>Process Optimization</t>
   </si>
   <si>
-    <t>Patient Registration</t>
-  </si>
-  <si>
-    <t>Insurance Verification</t>
-  </si>
-  <si>
-    <t>Appointment Scheduling</t>
-  </si>
-  <si>
-    <t>Medical Records Management</t>
-  </si>
-  <si>
-    <t>Billing Coordination</t>
-  </si>
-  <si>
-    <t>Acme Medical</t>
-  </si>
-  <si>
-    <t>Morgan Chen</t>
-  </si>
-  <si>
-    <t>Healthcare Administrator</t>
-  </si>
-  <si>
-    <t>Administrator</t>
-  </si>
-  <si>
-    <t>Healthcare Operations</t>
-  </si>
-  <si>
-    <t>Patient Service Coordination</t>
-  </si>
-  <si>
-    <t>Healthcare Compliance</t>
-  </si>
-  <si>
-    <t>Data Management</t>
-  </si>
-  <si>
-    <t>Communication Facilitation</t>
-  </si>
-  <si>
-    <t>Patient Satisfaction</t>
-  </si>
-  <si>
-    <t>Confidentiality</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>Compliance</t>
-  </si>
-  <si>
-    <t>Professional Communication</t>
-  </si>
-  <si>
-    <t>Patient Check-in/Check-out</t>
-  </si>
-  <si>
-    <t>Daily Appointment Confirmations</t>
-  </si>
-  <si>
-    <t>Insurance Authorization Requests</t>
-  </si>
-  <si>
-    <t>Medical Record Updates</t>
-  </si>
-  <si>
-    <t>Revenue Cycle Monitoring</t>
-  </si>
-  <si>
-    <t>HIPAA Compliance</t>
-  </si>
-  <si>
-    <t>Medical Terminology</t>
-  </si>
-  <si>
-    <t>Insurance Claims Processing</t>
-  </si>
-  <si>
-    <t>Patient Communication</t>
-  </si>
-  <si>
-    <t>Medical Coding (ICD-10/CPT)</t>
-  </si>
-  <si>
-    <t>Electronic Health Records Management</t>
-  </si>
-  <si>
-    <t>Front Desk Operations</t>
-  </si>
-  <si>
-    <t>Accounts Receivable Management</t>
-  </si>
-  <si>
-    <t>Patient Flow Coordination</t>
-  </si>
-  <si>
-    <t>Healthcare Documentation</t>
-  </si>
-  <si>
-    <t>Epic MyChart</t>
-  </si>
-  <si>
-    <t>Cerner PowerChart</t>
-  </si>
-  <si>
-    <t>athenahealth</t>
-  </si>
-  <si>
-    <t>Microsoft Office 365</t>
-  </si>
-  <si>
-    <t>Kareo</t>
-  </si>
-  <si>
-    <t>NextGen</t>
-  </si>
-  <si>
-    <t>Cisco Phone System</t>
-  </si>
-  <si>
-    <t>Availity</t>
-  </si>
-  <si>
-    <t>Xerox WorkCentre</t>
-  </si>
-  <si>
-    <t>Brother MFC Series</t>
-  </si>
-  <si>
-    <t>Square Terminal</t>
-  </si>
-  <si>
-    <t>Solutionreach</t>
-  </si>
-  <si>
-    <t>Zocdoc</t>
+    <t>Accomplishment 1</t>
+  </si>
+  <si>
+    <t>Accomplishment 4</t>
+  </si>
+  <si>
+    <t>Accomplishment 3</t>
+  </si>
+  <si>
+    <t>Accomplishment 2</t>
+  </si>
+  <si>
+    <t>Key Accomplishments</t>
+  </si>
+  <si>
+    <t>Parker</t>
+  </si>
+  <si>
+    <t>Miller</t>
+  </si>
+  <si>
+    <t>Lopez</t>
+  </si>
+  <si>
+    <t>Gonzalez</t>
+  </si>
+  <si>
+    <t>Drew</t>
+  </si>
+  <si>
+    <t>Skyler</t>
+  </si>
+  <si>
+    <t>Lane</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>Hernandez</t>
+  </si>
+  <si>
+    <t>Indigo</t>
+  </si>
+  <si>
+    <t>Martin</t>
+  </si>
+  <si>
+    <t>Harley</t>
+  </si>
+  <si>
+    <t>Clark</t>
+  </si>
+  <si>
+    <t>Dallas</t>
+  </si>
+  <si>
+    <t>Peyton</t>
+  </si>
+  <si>
+    <t>Walker</t>
+  </si>
+  <si>
+    <t>Remy</t>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>Kai</t>
+  </si>
+  <si>
+    <t>Allen</t>
+  </si>
+  <si>
+    <t>Brook</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Ari</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>Sloan</t>
+  </si>
+  <si>
+    <t>Wright</t>
+  </si>
+  <si>
+    <t>Devon</t>
+  </si>
+  <si>
+    <t>Scott</t>
+  </si>
+  <si>
+    <t>Aubrey</t>
+  </si>
+  <si>
+    <t>Torres</t>
+  </si>
+  <si>
+    <t>Rory</t>
+  </si>
+  <si>
+    <t>Nguyen</t>
+  </si>
+  <si>
+    <t>Hill</t>
+  </si>
+  <si>
+    <t>Micah</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>Jaden</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Bailey</t>
+  </si>
+  <si>
+    <t>Adams</t>
+  </si>
+  <si>
+    <t>Nelson</t>
+  </si>
+  <si>
+    <t>Shay</t>
+  </si>
+  <si>
+    <t>Baker</t>
+  </si>
+  <si>
+    <t>Robin</t>
+  </si>
+  <si>
+    <t>Mitchell</t>
+  </si>
+  <si>
+    <t>Storm</t>
+  </si>
+  <si>
+    <t>Perez</t>
+  </si>
+  <si>
+    <t>Ocean</t>
+  </si>
+  <si>
+    <t>Roberts</t>
+  </si>
+  <si>
+    <t>Arrow</t>
+  </si>
+  <si>
+    <t>Turner</t>
+  </si>
+  <si>
+    <t>Aspen</t>
+  </si>
+  <si>
+    <t>Phillips</t>
+  </si>
+  <si>
+    <t>Emerson</t>
+  </si>
+  <si>
+    <t>Campbell</t>
+  </si>
+  <si>
+    <t>Nova</t>
+  </si>
+  <si>
+    <t>Evans</t>
+  </si>
+  <si>
+    <t>Vale</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>Gray</t>
+  </si>
+  <si>
+    <t>Collins</t>
+  </si>
+  <si>
+    <t>Wren</t>
+  </si>
+  <si>
+    <t>Stewart</t>
+  </si>
+  <si>
+    <t>Sanchez</t>
+  </si>
+  <si>
+    <t>Briar</t>
+  </si>
+  <si>
+    <t>Morris</t>
+  </si>
+  <si>
+    <t>Ellis</t>
+  </si>
+  <si>
+    <t>Rogers</t>
+  </si>
+  <si>
+    <t>Jules</t>
+  </si>
+  <si>
+    <t>Reed</t>
+  </si>
+  <si>
+    <t>Marlowe</t>
+  </si>
+  <si>
+    <t>Cook</t>
+  </si>
+  <si>
+    <t>Darian</t>
+  </si>
+  <si>
+    <t>Sasha</t>
+  </si>
+  <si>
+    <t>Bell</t>
+  </si>
+  <si>
+    <t>Tatum</t>
+  </si>
+  <si>
+    <t>Murphy</t>
+  </si>
+  <si>
+    <t>Cooper</t>
+  </si>
+  <si>
+    <t>Oakley</t>
+  </si>
+  <si>
+    <t>Richardson</t>
+  </si>
+  <si>
+    <t>Justice</t>
+  </si>
+  <si>
+    <t>Cox</t>
+  </si>
+  <si>
+    <t>Howard</t>
+  </si>
+  <si>
+    <t>Bellamy</t>
+  </si>
+  <si>
+    <t>Ward</t>
+  </si>
+  <si>
+    <t>Ren</t>
+  </si>
+  <si>
+    <t>Scout</t>
+  </si>
+  <si>
+    <t>Peterson</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Ramirez</t>
+  </si>
+  <si>
+    <t>Payton</t>
+  </si>
+  <si>
+    <t>James</t>
+  </si>
+  <si>
+    <t>Jude</t>
+  </si>
+  <si>
+    <t>Watson</t>
+  </si>
+  <si>
+    <t>Lux</t>
+  </si>
+  <si>
+    <t>Brooks</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>Camden</t>
+  </si>
+  <si>
+    <t>Sanders</t>
+  </si>
+  <si>
+    <t>Ira</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Palmer</t>
+  </si>
+  <si>
+    <t>Bennett</t>
+  </si>
+  <si>
+    <t>Remi</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Frankie</t>
+  </si>
+  <si>
+    <t>Barnes</t>
+  </si>
+  <si>
+    <t>Onyx</t>
+  </si>
+  <si>
+    <t>Ross</t>
+  </si>
+  <si>
+    <t>Soren</t>
+  </si>
+  <si>
+    <t>Henderson</t>
+  </si>
+  <si>
+    <t>Merit</t>
+  </si>
+  <si>
+    <t>Coleman</t>
+  </si>
+  <si>
+    <t>Asa</t>
+  </si>
+  <si>
+    <t>Jenkins</t>
+  </si>
+  <si>
+    <t>Cypress</t>
+  </si>
+  <si>
+    <t>Perry</t>
+  </si>
+  <si>
+    <t>Haven</t>
+  </si>
+  <si>
+    <t>Powell</t>
+  </si>
+  <si>
+    <t>Journey</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Patterson</t>
+  </si>
+  <si>
+    <t>Reign</t>
+  </si>
+  <si>
+    <t>Hughes</t>
+  </si>
+  <si>
+    <t>Seven</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>Timber</t>
+  </si>
+  <si>
+    <t>Butler</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>Simmons</t>
+  </si>
+  <si>
+    <t>Echo</t>
+  </si>
+  <si>
+    <t>Foster</t>
+  </si>
+  <si>
+    <t>Harbor</t>
+  </si>
+  <si>
+    <t>Gonzales</t>
+  </si>
+  <si>
+    <t>Bryant</t>
+  </si>
+  <si>
+    <t>Novel</t>
+  </si>
+  <si>
+    <t>Alexander</t>
+  </si>
+  <si>
+    <t>Poet</t>
+  </si>
+  <si>
+    <t>Russell</t>
+  </si>
+  <si>
+    <t>Quest</t>
+  </si>
+  <si>
+    <t>Griffin</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>Diaz</t>
+  </si>
+  <si>
+    <t>Zion</t>
+  </si>
+  <si>
+    <t>Hayes</t>
+  </si>
+  <si>
+    <t>Baylor</t>
+  </si>
+  <si>
+    <t>Myers</t>
+  </si>
+  <si>
+    <t>Lark</t>
+  </si>
+  <si>
+    <t>Ford</t>
+  </si>
+  <si>
+    <t>Rebel</t>
+  </si>
+  <si>
+    <t>Hamilton</t>
+  </si>
+  <si>
+    <t>Graham</t>
+  </si>
+  <si>
+    <t>Stone</t>
+  </si>
+  <si>
+    <t>Sullivan</t>
+  </si>
+  <si>
+    <t>Wallace</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Woods</t>
+  </si>
+  <si>
+    <t>Zephyr</t>
+  </si>
+  <si>
+    <t>Cole</t>
+  </si>
+  <si>
+    <t>Bryce</t>
+  </si>
+  <si>
+    <t>Owens</t>
+  </si>
+  <si>
+    <t>Reynolds</t>
+  </si>
+  <si>
+    <t>Fisher</t>
+  </si>
+  <si>
+    <t>Harrison</t>
+  </si>
+  <si>
+    <t>Gibson</t>
+  </si>
+  <si>
+    <t>McDonald</t>
+  </si>
+  <si>
+    <t>Cruz</t>
+  </si>
+  <si>
+    <t>Marshall</t>
+  </si>
+  <si>
+    <t>Ortiz</t>
+  </si>
+  <si>
+    <t>Gomez</t>
+  </si>
+  <si>
+    <t>Murray</t>
+  </si>
+  <si>
+    <t>Freeman</t>
+  </si>
+  <si>
+    <t>Wells</t>
+  </si>
+  <si>
+    <t>Webb</t>
+  </si>
+  <si>
+    <t>Simpson</t>
+  </si>
+  <si>
+    <t>Stevens</t>
+  </si>
+  <si>
+    <t>Tucker</t>
+  </si>
+  <si>
+    <t>Porter</t>
+  </si>
+  <si>
+    <t>Hunter</t>
+  </si>
+  <si>
+    <t>Hicks</t>
+  </si>
+  <si>
+    <t>Crawford</t>
+  </si>
+  <si>
+    <t>Henry</t>
+  </si>
+  <si>
+    <t>Boyd</t>
+  </si>
+  <si>
+    <t>Mason</t>
+  </si>
+  <si>
+    <t>Morales</t>
+  </si>
+  <si>
+    <t>Practices &amp; Priorities</t>
+  </si>
+  <si>
+    <t>Org Description</t>
+  </si>
+  <si>
+    <t>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</t>
+  </si>
+  <si>
+    <t>Staff Scheduling</t>
+  </si>
+  <si>
+    <t>Vendor Management</t>
+  </si>
+  <si>
+    <t>Inventory Management</t>
+  </si>
+  <si>
+    <t>Store Performance Management</t>
+  </si>
+  <si>
+    <t>Customer Service Oversight</t>
+  </si>
+  <si>
+    <t>Performance Monitoring</t>
+  </si>
+  <si>
+    <t>Resource Coordination</t>
+  </si>
+  <si>
+    <t>Cross-Functional Coordination</t>
+  </si>
+  <si>
+    <t>Staff Development</t>
+  </si>
+  <si>
+    <t>Retail/Operations Management</t>
+  </si>
+  <si>
+    <t>Anytown Retail</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>Square POS</t>
+  </si>
+  <si>
+    <t>Toast</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>NetSuite</t>
+  </si>
+  <si>
+    <t>TradeGecko</t>
+  </si>
+  <si>
+    <t>Deputy</t>
+  </si>
+  <si>
+    <t>Excel</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>PowerBI</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>Zendesk</t>
+  </si>
+  <si>
+    <t>Mailchimp</t>
+  </si>
+  <si>
+    <t>QuickBooks</t>
+  </si>
+  <si>
+    <t>Staff Training &amp; Development</t>
+  </si>
+  <si>
+    <t>Merchandising Strategy</t>
+  </si>
+  <si>
+    <t>Supply Chain Coordination</t>
+  </si>
+  <si>
+    <t>Customer Service Management</t>
+  </si>
+  <si>
+    <t>Compliance Management</t>
+  </si>
+  <si>
+    <t>Multi-location Oversight</t>
+  </si>
+  <si>
+    <t>Crisis Management</t>
+  </si>
+  <si>
+    <t>Seasonal Planning</t>
+  </si>
+  <si>
+    <t>Budget Forecasting</t>
+  </si>
+  <si>
+    <t>Operations Management</t>
+  </si>
+  <si>
+    <t>Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</t>
+  </si>
+  <si>
+    <t>Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</t>
+  </si>
+  <si>
+    <t>Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</t>
+  </si>
+  <si>
+    <t>Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</t>
+  </si>
+  <si>
+    <t>Daily Standups</t>
+  </si>
+  <si>
+    <t>Performance Dashboards</t>
+  </si>
+  <si>
+    <t>Mystery Shopping</t>
+  </si>
+  <si>
+    <t>Staff Cross-training</t>
+  </si>
+  <si>
+    <t>Standard Operating Procedures</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction</t>
+  </si>
+  <si>
+    <t>Operational Efficiency</t>
+  </si>
+  <si>
+    <t>Team Development</t>
+  </si>
+  <si>
+    <t>Brand Consistency</t>
+  </si>
+  <si>
+    <t>Safety &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Community Engagement</t>
+  </si>
+  <si>
+    <t>Profitability</t>
+  </si>
+  <si>
+    <t>Accomplishments (&lt;=4)</t>
   </si>
 </sst>
 </file>
@@ -544,66 +1135,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color indexed="64"/>
@@ -643,23 +1174,52 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -670,7 +1230,44 @@
         <color indexed="64"/>
       </right>
       <top/>
-      <bottom style="medium">
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -679,7 +1276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -696,13 +1293,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
-          <xfpb:xfComplement i="0"/>
-        </ext>
-      </extLst>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -712,30 +1302,20 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -743,22 +1323,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
@@ -782,14 +1346,127 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="47">
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -835,6 +1512,279 @@
         <color theme="0"/>
       </font>
     </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -862,22 +1812,22 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>6</xdr:col>
-          <xdr:colOff>156882</xdr:colOff>
-          <xdr:row>18</xdr:row>
-          <xdr:rowOff>123264</xdr:rowOff>
+          <xdr:colOff>1832161</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>5603</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>15</xdr:col>
-          <xdr:colOff>1628215</xdr:colOff>
-          <xdr:row>37</xdr:row>
-          <xdr:rowOff>133629</xdr:rowOff>
+          <xdr:col>17</xdr:col>
+          <xdr:colOff>985277</xdr:colOff>
+          <xdr:row>46</xdr:row>
+          <xdr:rowOff>29416</xdr:rowOff>
         </xdr:to>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="5" name="Picture 4">
+            <xdr:cNvPr id="6" name="Picture 5">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{06ABBC4D-FCA4-1919-2E1C-CC28E5338F07}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B29D5E16-BD03-D863-814D-150D7B920569}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -885,7 +1835,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$AD$1:$AI$17" spid="_x0000_s1077"/>
+                  <a14:cameraTool cellRange="$AD$150:$AI$172" spid="_x0000_s1094"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -899,22 +1849,22 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="5031441" y="3356162"/>
-              <a:ext cx="9769288" cy="3416953"/>
+              <a:off x="8213912" y="4095750"/>
+              <a:ext cx="9658630" cy="4326872"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
             </a:prstGeom>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="292100" dist="139700" dir="2700000" algn="tl" rotWithShape="0">
-                <a:srgbClr val="333333">
-                  <a:alpha val="65000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
+            <a:noFill/>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+            </a:extLst>
           </xdr:spPr>
         </xdr:pic>
         <xdr:clientData/>
@@ -943,10 +1893,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}" name="Table1" displayName="Table1" ref="A1:C21" totalsRowShown="0">
-  <autoFilter ref="A1:C21" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}" name="names" displayName="names" ref="A1:C135" totalsRowShown="0">
+  <autoFilter ref="A1:C135" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index"/>
+    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="46">
+      <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
+    </tableColumn>
     <tableColumn id="2" xr3:uid="{2FBF4AE8-10BE-49DC-A08D-B377AD3CB245}" name="first"/>
     <tableColumn id="3" xr3:uid="{E9C8B136-54A2-474F-A6BF-CBF27C756B26}" name="last"/>
   </tableColumns>
@@ -1271,748 +2223,902 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3348163-AFAC-4B5E-B6D7-A630EDC47AB4}">
-  <dimension ref="A1:AI17"/>
+  <dimension ref="A2:AI171"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.3984375" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.265625" customWidth="1"/>
     <col min="3" max="3" width="3.46484375" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.46484375" customWidth="1"/>
+    <col min="6" max="6" width="3.86328125" customWidth="1"/>
     <col min="7" max="7" width="25.86328125" customWidth="1"/>
     <col min="8" max="8" width="3.46484375" customWidth="1"/>
     <col min="9" max="9" width="24.6640625" customWidth="1"/>
-    <col min="10" max="10" width="3.46484375" customWidth="1"/>
+    <col min="10" max="10" width="3.86328125" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="25.86328125" customWidth="1"/>
-    <col min="13" max="13" width="3.46484375" customWidth="1"/>
+    <col min="13" max="13" width="3.86328125" customWidth="1"/>
     <col min="14" max="14" width="25.86328125" customWidth="1"/>
-    <col min="15" max="15" width="3.46484375" customWidth="1"/>
+    <col min="15" max="15" width="3.86328125" customWidth="1"/>
     <col min="16" max="16" width="25.86328125" customWidth="1"/>
-    <col min="28" max="28" width="9.06640625" style="39"/>
+    <col min="17" max="17" width="3.86328125" customWidth="1"/>
+    <col min="18" max="18" width="23.46484375" customWidth="1"/>
+    <col min="28" max="28" width="9.06640625" style="24"/>
     <col min="30" max="33" width="29.9296875" customWidth="1"/>
     <col min="34" max="34" width="1.86328125" customWidth="1"/>
     <col min="35" max="35" width="13.3984375" customWidth="1"/>
     <col min="36" max="36" width="24.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="9" t="s">
+    <row r="2" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="B3" s="39" t="str" cm="1">
+        <f t="array" aca="1" ref="B3" ca="1">randomName</f>
+        <v>Rowan Thompson</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="40" t="str">
-        <f>B1&amp; " ("&amp;B2&amp;")"</f>
-        <v>Morgan Chen (Healthcare Administrator)</v>
-      </c>
-      <c r="AE1" s="33" t="str">
-        <f>B7&amp;" with "&amp;B3&amp;" ("&amp;B4&amp;")"</f>
-        <v>Administrator with Acme Medical (Anytown, USA)</v>
-      </c>
-      <c r="AF1" s="34"/>
-      <c r="AG1" s="32" t="str">
-        <f>B5&amp;" - "&amp;B6</f>
-        <v>Feb 2021 - Sep 2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+    </row>
+    <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="37" t="b">
+      <c r="B4" s="39" t="s">
+        <v>291</v>
+      </c>
+      <c r="D4" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="F2" s="7"/>
-      <c r="G2" s="35" t="s">
-        <v>74</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7" t="b">
-        <f>IF(L2="","",ISEVEN(ROW()))</f>
+      <c r="E4" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="b">
+        <f>IF(L4="","",ISEVEN(ROW()))</f>
         <v>1</v>
       </c>
-      <c r="L2" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="O2" s="7"/>
-      <c r="P2" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD2" s="13" t="str" cm="1">
-        <f t="array" ref="AD2:AD17">_xlfn.VSTACK(
-"Tools",
-"Core","  • "&amp;_xlfn._xlws.FILTER(E1:E17,D1:D17=TRUE),
-"Incidental","  • "&amp;_xlfn._xlws.FILTER(E1:E17,(D1:D17=FALSE)*(E1:E17&lt;&gt;"")))</f>
-        <v>Tools</v>
-      </c>
-      <c r="AE2" s="12" t="str" cm="1">
-        <f t="array" ref="AE2:AE8">_xlfn.VSTACK("Profession",B2,"  • "&amp;_xlfn._xlws.FILTER(G2:G7,G2:G7&lt;&gt;""))</f>
-        <v>Profession</v>
-      </c>
-      <c r="AF2" s="11" t="str" cm="1">
-        <f t="array" ref="AF2:AF9">_xlfn.VSTACK("Job",B7,B8,"  • "&amp;_xlfn._xlws.FILTER(I2:I6,I2:I6&lt;&gt;""))</f>
-        <v>Job</v>
-      </c>
-      <c r="AG2" s="14" t="str" cm="1">
-        <f t="array" ref="AG2:AG14">_xlfn.VSTACK(
-"Practices","  • "&amp;_xlfn._xlws.FILTER(N2:N17,N2:N17&lt;&gt;""),
-"Priorities","  • "&amp;_xlfn._xlws.FILTER(P2:P17,P2:P17&lt;&gt;""))</f>
-        <v>Practices</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="9" t="s">
+      <c r="L4" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="M4" s="6"/>
+      <c r="N4" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="O4" s="6"/>
+      <c r="P4" s="20" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="37" t="b">
+      <c r="B5" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7" t="b">
-        <f t="shared" ref="K3:K17" si="0">IF(L3="","",ISEVEN(ROW()))</f>
+      <c r="E5" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="6"/>
+      <c r="G5" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6" t="b">
+        <f t="shared" ref="K5:K19" si="0">IF(L5="","",ISEVEN(ROW()))</f>
         <v>0</v>
       </c>
-      <c r="L3" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="M3" s="7"/>
-      <c r="N3" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="35" t="s">
-        <v>79</v>
-      </c>
-      <c r="AD3" s="15" t="str">
-        <v>Core</v>
-      </c>
-      <c r="AE3" s="16" t="str">
-        <v>Healthcare Administrator</v>
-      </c>
-      <c r="AF3" s="21" t="str">
-        <v>Administrator</v>
-      </c>
-      <c r="AG3" s="20" t="str">
-        <v xml:space="preserve">  • Patient Check-in/Check-out</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A4" s="9" t="s">
+      <c r="L5" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="M5" s="6"/>
+      <c r="N5" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="20" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="35" t="s">
+      <c r="B6" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="37" t="b">
+      <c r="D6" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="35" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="35" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="35" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7" t="b">
+      <c r="E6" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L4" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="M4" s="7"/>
-      <c r="N4" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="O4" s="7"/>
-      <c r="P4" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD4" s="15" t="str">
-        <v xml:space="preserve">  • Epic MyChart</v>
-      </c>
-      <c r="AE4" s="17" t="str">
-        <v xml:space="preserve">  • Patient Service Coordination</v>
-      </c>
-      <c r="AF4" s="22" t="str">
-        <v>Healthcare Operations</v>
-      </c>
-      <c r="AG4" s="20" t="str">
-        <v xml:space="preserve">  • Daily Appointment Confirmations</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A5" s="9" t="s">
+      <c r="L6" s="20" t="s">
+        <v>284</v>
+      </c>
+      <c r="M6" s="6"/>
+      <c r="N6" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="O6" s="6"/>
+      <c r="P6" s="20" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="37" t="b">
+      <c r="B7" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7" t="b">
+      <c r="E7" s="20" t="s">
+        <v>272</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L5" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="M5" s="7"/>
-      <c r="N5" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="35" t="s">
-        <v>81</v>
-      </c>
-      <c r="AD5" s="15" t="str">
-        <v xml:space="preserve">  • Cerner PowerChart</v>
-      </c>
-      <c r="AE5" s="17" t="str">
-        <v xml:space="preserve">  • Healthcare Compliance</v>
-      </c>
-      <c r="AF5" s="17" t="str">
-        <v xml:space="preserve">  • Patient Registration</v>
-      </c>
-      <c r="AG5" s="20" t="str">
-        <v xml:space="preserve">  • Insurance Authorization Requests</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A6" s="9" t="s">
+      <c r="L7" s="20" t="s">
+        <v>285</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="O7" s="6"/>
+      <c r="P7" s="20" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="37" t="b">
+      <c r="B8" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7" t="b">
+      <c r="E8" s="20" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L6" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="7"/>
-      <c r="N6" s="35" t="s">
-        <v>88</v>
-      </c>
-      <c r="O6" s="7"/>
-      <c r="P6" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="AD6" s="15" t="str">
-        <v xml:space="preserve">  • athenahealth</v>
-      </c>
-      <c r="AE6" s="17" t="str">
-        <v xml:space="preserve">  • Data Management</v>
-      </c>
-      <c r="AF6" s="17" t="str">
-        <v xml:space="preserve">  • Insurance Verification</v>
-      </c>
-      <c r="AG6" s="20" t="str">
-        <v xml:space="preserve">  • Medical Record Updates</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A7" s="3" t="s">
+      <c r="L8" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="M8" s="6"/>
+      <c r="N8" s="20" t="s">
+        <v>300</v>
+      </c>
+      <c r="O8" s="6"/>
+      <c r="P8" s="20" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="35" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="37" t="b">
+      <c r="B9" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="D9" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7" t="b">
+      <c r="E9" s="20" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L7" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="M7" s="7"/>
-      <c r="N7" s="35"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="AD7" s="15" t="str">
-        <v xml:space="preserve">  • Microsoft Office 365</v>
-      </c>
-      <c r="AE7" s="17" t="str">
-        <v xml:space="preserve">  • Communication Facilitation</v>
-      </c>
-      <c r="AF7" s="17" t="str">
-        <v xml:space="preserve">  • Appointment Scheduling</v>
-      </c>
-      <c r="AG7" s="20" t="str">
-        <v xml:space="preserve">  • Revenue Cycle Monitoring</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A8" s="3" t="s">
+      <c r="L9" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="M9" s="6"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="20" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="35" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="37" t="b">
+      <c r="B10" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7" t="b">
+      <c r="E10" s="20" t="s">
+        <v>275</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L8" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="M8" s="7"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="35"/>
-      <c r="AD8" s="15" t="str">
-        <v xml:space="preserve">  • Kareo</v>
-      </c>
-      <c r="AE8" s="17" t="str">
-        <v xml:space="preserve">  • Process Optimization</v>
-      </c>
-      <c r="AF8" s="17" t="str">
-        <v xml:space="preserve">  • Medical Records Management</v>
-      </c>
-      <c r="AG8" s="10" t="str">
-        <v>Priorities</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D9" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7" t="b">
+      <c r="L10" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="M10" s="6"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="6"/>
+      <c r="P10" s="20" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="B11" s="26"/>
+      <c r="D11" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L9" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="35"/>
-      <c r="AD9" s="15" t="str">
-        <v xml:space="preserve">  • NextGen</v>
-      </c>
-      <c r="AE9" s="18"/>
-      <c r="AF9" s="23" t="str">
-        <v xml:space="preserve">  • Billing Coordination</v>
-      </c>
-      <c r="AG9" s="20" t="str">
-        <v xml:space="preserve">  • Patient Satisfaction</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D10" s="37" t="b">
+      <c r="L11" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="20"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="B12" s="26"/>
+      <c r="D12" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7" t="b">
+      <c r="E12" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="L10" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="8"/>
-      <c r="AD10" s="19" t="str">
-        <v xml:space="preserve">  • Cisco Phone System</v>
-      </c>
-      <c r="AE10" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF10" s="27"/>
-      <c r="AG10" s="20" t="str">
-        <v xml:space="preserve">  • Confidentiality</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D11" s="37" t="b">
+      <c r="L12" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="M12" s="6"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="6"/>
+      <c r="P12" s="7"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="B13" s="26"/>
+      <c r="D13" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L11" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="AD11" s="19" t="str">
-        <v>Incidental</v>
-      </c>
-      <c r="AE11" s="28" t="str" cm="1">
-        <f t="array" ref="AE11:AF15">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
-" • "&amp;_xlfn._xlws.FILTER(L2:L17,K2:K17=TRUE),
-" • "&amp;_xlfn._xlws.FILTER(L2:L17,(K2:K17=FALSE)*(L2:L17&lt;&gt;""))),"")),"")</f>
-        <v xml:space="preserve"> • HIPAA Compliance</v>
-      </c>
-      <c r="AF11" s="28" t="str">
-        <v xml:space="preserve"> • Medical Terminology</v>
-      </c>
-      <c r="AG11" s="20" t="str">
-        <v xml:space="preserve">  • Accuracy</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D12" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="35" t="s">
-        <v>109</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7" t="str">
+      <c r="E13" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L12" s="35"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="AD12" s="19" t="str">
-        <v xml:space="preserve">  • Availity</v>
-      </c>
-      <c r="AE12" s="28" t="str">
-        <v xml:space="preserve"> • Insurance Claims Processing</v>
-      </c>
-      <c r="AF12" s="28" t="str">
-        <v xml:space="preserve"> • Patient Communication</v>
-      </c>
-      <c r="AG12" s="20" t="str">
-        <v xml:space="preserve">  • Efficiency</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D13" s="37" t="b">
+      <c r="L13" s="20"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="B14" s="26"/>
+      <c r="D14" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7" t="str">
+      <c r="E14" s="20" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L13" s="35"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="AD13" s="19" t="str">
-        <v xml:space="preserve">  • Xerox WorkCentre</v>
-      </c>
-      <c r="AE13" s="28" t="str">
-        <v xml:space="preserve"> • Medical Coding (ICD-10/CPT)</v>
-      </c>
-      <c r="AF13" s="28" t="str">
-        <v xml:space="preserve"> • Electronic Health Records Management</v>
-      </c>
-      <c r="AG13" s="20" t="str">
-        <v xml:space="preserve">  • Compliance</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D14" s="37" t="b">
+      <c r="L14" s="20"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="D15" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7" t="str">
+      <c r="E15" s="20" t="s">
+        <v>280</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L14" s="35"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
-      <c r="AD14" s="19" t="str">
-        <v xml:space="preserve">  • Brother MFC Series</v>
-      </c>
-      <c r="AE14" s="28" t="str">
-        <v xml:space="preserve"> • Front Desk Operations</v>
-      </c>
-      <c r="AF14" s="28" t="str">
-        <v xml:space="preserve"> • Accounts Receivable Management</v>
-      </c>
-      <c r="AG14" s="20" t="str">
-        <v xml:space="preserve">  • Professional Communication</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D15" s="37" t="b">
+      <c r="L15" s="31"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="6"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="D16" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7" t="str">
+      <c r="E16" s="20" t="s">
+        <v>281</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="35"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
-      <c r="AD15" s="19" t="str">
-        <v xml:space="preserve">  • Square Terminal</v>
-      </c>
-      <c r="AE15" s="28" t="str">
-        <v xml:space="preserve"> • Patient Flow Coordination</v>
-      </c>
-      <c r="AF15" s="28" t="str">
-        <v xml:space="preserve"> • Healthcare Documentation</v>
-      </c>
-      <c r="AG15" s="20"/>
-      <c r="AI15" s="24" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="D16" s="37" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7" t="str">
+      <c r="L16" s="31"/>
+      <c r="M16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="D17" s="28"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L16" s="8"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="AD16" s="19" t="str">
-        <v xml:space="preserve">  • Solutionreach</v>
-      </c>
-      <c r="AE16" s="28"/>
-      <c r="AF16" s="28"/>
-      <c r="AG16" s="20"/>
-      <c r="AI16" s="25" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="4:35" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D17" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7" t="str">
+      <c r="L17" s="20"/>
+      <c r="M17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="E18" s="20"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="AD17" s="29" t="str">
-        <v xml:space="preserve">  • Zocdoc</v>
-      </c>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="31"/>
-      <c r="AI17" s="26" t="s">
+      <c r="L18" s="28"/>
+      <c r="M18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A19" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A23" s="25" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A24" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A25" s="27" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A26" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A27" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A28" s="27"/>
+      <c r="B28" s="6"/>
+    </row>
+    <row r="149" spans="30:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="150" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD150" s="41" t="str">
+        <f ca="1">B3&amp; " ("&amp;B10&amp;")"</f>
+        <v>Rowan Thompson (Retail/Operations Management)</v>
+      </c>
+      <c r="AE150" s="42" t="str">
+        <f>B9&amp;" with "&amp;B5&amp;" ("&amp;B6&amp;")"</f>
+        <v>Store Manager with Anytown Retail (Anytown, USA)</v>
+      </c>
+      <c r="AF150" s="43"/>
+      <c r="AG150" s="44" t="str">
+        <f>B7&amp;" - "&amp;B8</f>
+        <v>Feb 2021 - Sep 2023</v>
+      </c>
+    </row>
+    <row r="151" spans="30:33" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AD151" s="45" t="str">
+        <f>B19</f>
+        <v>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</v>
+      </c>
+      <c r="AE151" s="46"/>
+      <c r="AF151" s="46"/>
+      <c r="AG151" s="47"/>
+    </row>
+    <row r="152" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD152" s="11" t="str" cm="1">
+        <f t="array" ref="AD152:AD167">_xlfn.VSTACK(
+"Tools",
+"Core","  • "&amp;_xlfn._xlws.FILTER(E3:E19,D3:D19=TRUE),
+"Incidental","  • "&amp;_xlfn._xlws.FILTER(E3:E19,(D3:D19=FALSE)*(E3:E19&lt;&gt;"")))</f>
+        <v>Tools</v>
+      </c>
+      <c r="AE152" s="10" t="str" cm="1">
+        <f t="array" ref="AE152:AE158">_xlfn.VSTACK("Profession",B10,"  • "&amp;_xlfn._xlws.FILTER(G4:G9,G4:G9&lt;&gt;""))</f>
+        <v>Profession</v>
+      </c>
+      <c r="AF152" s="9" t="str" cm="1">
+        <f t="array" ref="AF152:AF159">_xlfn.VSTACK("Job",B9,B10,"  • "&amp;_xlfn._xlws.FILTER(I4:I8,I4:I8&lt;&gt;""))</f>
+        <v>Job</v>
+      </c>
+      <c r="AG152" s="40" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="153" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD153" s="33" t="str">
+        <v>Core</v>
+      </c>
+      <c r="AE153" s="12" t="str">
+        <v>Retail/Operations Management</v>
+      </c>
+      <c r="AF153" s="12" t="str">
+        <v>Store Manager</v>
+      </c>
+      <c r="AG153" s="34" t="str" cm="1">
+        <f t="array" ref="AG153:AG166">_xlfn.VSTACK(
+"Practices","  • "&amp;_xlfn._xlws.FILTER(N4:N19,N4:N19&lt;&gt;""),
+"Priorities","  • "&amp;_xlfn._xlws.FILTER(P4:P19,P4:P19&lt;&gt;""))</f>
+        <v>Practices</v>
+      </c>
+    </row>
+    <row r="154" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD154" s="35" t="str">
+        <v xml:space="preserve">  • Square POS</v>
+      </c>
+      <c r="AE154" s="13" t="str">
+        <v xml:space="preserve">  • Process Optimization</v>
+      </c>
+      <c r="AF154" s="15" t="str">
+        <v>Retail/Operations Management</v>
+      </c>
+      <c r="AG154" s="13" t="str">
+        <v xml:space="preserve">  • Daily Standups</v>
+      </c>
+    </row>
+    <row r="155" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD155" s="35" t="str">
+        <v xml:space="preserve">  • Toast</v>
+      </c>
+      <c r="AE155" s="13" t="str">
+        <v xml:space="preserve">  • Performance Monitoring</v>
+      </c>
+      <c r="AF155" s="13" t="str">
+        <v xml:space="preserve">  • Staff Scheduling</v>
+      </c>
+      <c r="AG155" s="13" t="str">
+        <v xml:space="preserve">  • Performance Dashboards</v>
+      </c>
+    </row>
+    <row r="156" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD156" s="35" t="str">
+        <v xml:space="preserve">  • Shopify</v>
+      </c>
+      <c r="AE156" s="13" t="str">
+        <v xml:space="preserve">  • Resource Coordination</v>
+      </c>
+      <c r="AF156" s="13" t="str">
+        <v xml:space="preserve">  • Vendor Management</v>
+      </c>
+      <c r="AG156" s="13" t="str">
+        <v xml:space="preserve">  • Mystery Shopping</v>
+      </c>
+    </row>
+    <row r="157" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD157" s="35" t="str">
+        <v xml:space="preserve">  • NetSuite</v>
+      </c>
+      <c r="AE157" s="13" t="str">
+        <v xml:space="preserve">  • Cross-Functional Coordination</v>
+      </c>
+      <c r="AF157" s="13" t="str">
+        <v xml:space="preserve">  • Inventory Management</v>
+      </c>
+      <c r="AG157" s="13" t="str">
+        <v xml:space="preserve">  • Staff Cross-training</v>
+      </c>
+    </row>
+    <row r="158" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD158" s="35" t="str">
+        <v xml:space="preserve">  • TradeGecko</v>
+      </c>
+      <c r="AE158" s="13" t="str">
+        <v xml:space="preserve">  • Staff Development</v>
+      </c>
+      <c r="AF158" s="13" t="str">
+        <v xml:space="preserve">  • Store Performance Management</v>
+      </c>
+      <c r="AG158" s="32" t="str">
+        <v xml:space="preserve">  • Standard Operating Procedures</v>
+      </c>
+    </row>
+    <row r="159" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD159" s="35" t="str">
+        <v xml:space="preserve">  • Deputy</v>
+      </c>
+      <c r="AE159" s="14"/>
+      <c r="AF159" s="16" t="str">
+        <v xml:space="preserve">  • Customer Service Oversight</v>
+      </c>
+      <c r="AG159" s="13" t="str">
+        <v>Priorities</v>
+      </c>
+    </row>
+    <row r="160" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD160" s="36" t="str">
+        <v xml:space="preserve">  • Excel</v>
+      </c>
+      <c r="AE160" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF160" s="37"/>
+      <c r="AG160" s="13" t="str">
+        <v xml:space="preserve">  • Customer Satisfaction</v>
+      </c>
+    </row>
+    <row r="161" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD161" s="36" t="str">
+        <v xml:space="preserve">  • Slack</v>
+      </c>
+      <c r="AE161" s="29" t="str" cm="1">
+        <f t="array" ref="AE161:AF165">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
+" • "&amp;_xlfn._xlws.FILTER(L4:L19,K4:K19=TRUE),
+" • "&amp;_xlfn._xlws.FILTER(L4:L19,(K4:K19=FALSE)*(L4:L19&lt;&gt;""))),"")),"")</f>
+        <v xml:space="preserve"> • Staff Training &amp; Development</v>
+      </c>
+      <c r="AF161" s="29" t="str">
+        <v xml:space="preserve"> • Merchandising Strategy</v>
+      </c>
+      <c r="AG161" s="13" t="str">
+        <v xml:space="preserve">  • Operational Efficiency</v>
+      </c>
+    </row>
+    <row r="162" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD162" s="36" t="str">
+        <v>Incidental</v>
+      </c>
+      <c r="AE162" s="29" t="str">
+        <v xml:space="preserve"> • Supply Chain Coordination</v>
+      </c>
+      <c r="AF162" s="29" t="str">
+        <v xml:space="preserve"> • Customer Service Management</v>
+      </c>
+      <c r="AG162" s="13" t="str">
+        <v xml:space="preserve">  • Team Development</v>
+      </c>
+    </row>
+    <row r="163" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD163" s="36" t="str">
+        <v xml:space="preserve">  • PowerBI</v>
+      </c>
+      <c r="AE163" s="29" t="str">
+        <v xml:space="preserve"> • Compliance Management</v>
+      </c>
+      <c r="AF163" s="29" t="str">
+        <v xml:space="preserve"> • Multi-location Oversight</v>
+      </c>
+      <c r="AG163" s="13" t="str">
+        <v xml:space="preserve">  • Brand Consistency</v>
+      </c>
+    </row>
+    <row r="164" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD164" s="36" t="str">
+        <v xml:space="preserve">  • Salesforce</v>
+      </c>
+      <c r="AE164" s="29" t="str">
+        <v xml:space="preserve"> • Crisis Management</v>
+      </c>
+      <c r="AF164" s="29" t="str">
+        <v xml:space="preserve"> • Seasonal Planning</v>
+      </c>
+      <c r="AG164" s="13" t="str">
+        <v xml:space="preserve">  • Safety &amp; Compliance</v>
+      </c>
+    </row>
+    <row r="165" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD165" s="36" t="str">
+        <v xml:space="preserve">  • Zendesk</v>
+      </c>
+      <c r="AE165" s="29" t="str">
+        <v xml:space="preserve"> • Budget Forecasting</v>
+      </c>
+      <c r="AF165" s="29" t="str">
+        <v/>
+      </c>
+      <c r="AG165" s="13" t="str">
+        <v xml:space="preserve">  • Community Engagement</v>
+      </c>
+      <c r="AI165" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="166" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD166" s="36" t="str">
+        <v xml:space="preserve">  • Mailchimp</v>
+      </c>
+      <c r="AE166" s="29"/>
+      <c r="AF166" s="29"/>
+      <c r="AG166" s="13" t="str">
+        <v xml:space="preserve">  • Profitability</v>
+      </c>
+      <c r="AI166" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="167" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD167" s="16" t="str">
+        <v xml:space="preserve">  • QuickBooks</v>
+      </c>
+      <c r="AE167" s="29"/>
+      <c r="AF167" s="29"/>
+      <c r="AG167" s="13"/>
+      <c r="AI167" s="19" t="s">
         <v>18</v>
       </c>
     </row>
+    <row r="168" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD168" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE168" s="30" t="str" cm="1">
+        <f t="array" ref="AE168:AE171">_xlfn._xlws.FILTER(B24:B28,B24:B28&lt;&gt;"")</f>
+        <v>Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</v>
+      </c>
+      <c r="AF168" s="30"/>
+      <c r="AG168" s="30"/>
+    </row>
+    <row r="169" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AE169" t="str">
+        <v>Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</v>
+      </c>
+    </row>
+    <row r="170" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AE170" t="str">
+        <v>Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</v>
+      </c>
+    </row>
+    <row r="171" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AE171" t="str">
+        <v>Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</v>
+      </c>
+    </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <conditionalFormatting sqref="D2:D17">
-    <cfRule type="expression" dxfId="5" priority="9">
-      <formula>$E2=""</formula>
+  <mergeCells count="1">
+    <mergeCell ref="AD151:AG151"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D4:D16">
+    <cfRule type="expression" dxfId="12" priority="18">
+      <formula>$E4=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE2">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>OR(AD2="Core",AD2="Incidental")</formula>
+  <conditionalFormatting sqref="AD152:AE167 AD25:AE50">
+    <cfRule type="expression" dxfId="11" priority="14">
+      <formula>OR(AD25="Core",AD25="Incidental",AD25="Key Accomplishments")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2 AD3:AD1048576">
-    <cfRule type="expression" dxfId="3" priority="8">
-      <formula>OR(AD2="Core",AD2="Incidental")</formula>
+  <conditionalFormatting sqref="AG152 AD25:AD1048576">
+    <cfRule type="expression" dxfId="10" priority="17">
+      <formula>OR(AD25="Core",AD25="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG1048576">
-    <cfRule type="expression" dxfId="2" priority="6">
-      <formula>OR(AG2="Practices",AG2="Priorities")</formula>
+  <conditionalFormatting sqref="AG25:AG1048576">
+    <cfRule type="expression" dxfId="9" priority="15">
+      <formula>OR(AG25="Practices",AG25="Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI16:AI17">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>OR(AI16="Core",AI16="Incidental")</formula>
+  <conditionalFormatting sqref="AI166:AI167">
+    <cfRule type="expression" dxfId="8" priority="11">
+      <formula>OR(AI166="Core",AI166="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI17">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>OR(AI17="Practices",AI17="Priorities")</formula>
+  <conditionalFormatting sqref="AI167">
+    <cfRule type="expression" dxfId="7" priority="10">
+      <formula>OR(AI167="Practices",AI167="Priorities")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A19 A24:A1048576">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>A3=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24:A28">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>B24=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:G29">
+    <cfRule type="expression" dxfId="4" priority="4">
+      <formula>LEN($B24)&gt;112</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD23:AG23 AD168:AG170">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>AND($AE24="",$AE23&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD23 AD168:AD171">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>$AE23&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG23 AG168:AG171">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$AE23&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD171:AG171">
+    <cfRule type="expression" dxfId="0" priority="20">
+      <formula>AND($AE23="",$AE171&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2023,25 +3129,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175234B1-B47F-451A-9952-E15FBC3697C2}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="9.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" t="s">
         <v>58</v>
       </c>
-      <c r="B1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="E1" t="str">
+        <f ca="1">_xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[first])&amp;" " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[last])</f>
+        <v>Phoenix West</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
+        <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -2051,8 +3162,9 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2062,206 +3174,1592 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A13">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B21" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>77</v>
+      </c>
+      <c r="C24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>84</v>
+      </c>
+      <c r="C28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A33">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A34">
+        <f t="shared" ref="A34:A65" si="1">ROW()-1</f>
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="C34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A35">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>98</v>
+      </c>
+      <c r="C35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A36">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A37">
+        <f t="shared" si="1"/>
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A38">
+        <f t="shared" si="1"/>
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>103</v>
+      </c>
+      <c r="C38" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A39">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>105</v>
+      </c>
+      <c r="C39" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A40">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A41">
+        <f t="shared" si="1"/>
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A42">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>110</v>
+      </c>
+      <c r="C42" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A43">
+        <f t="shared" si="1"/>
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>112</v>
+      </c>
+      <c r="C43" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A44">
+        <f t="shared" si="1"/>
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A45">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>116</v>
+      </c>
+      <c r="C45" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A46">
+        <f t="shared" si="1"/>
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>118</v>
+      </c>
+      <c r="C46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A47">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>120</v>
+      </c>
+      <c r="C47" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A48">
+        <f t="shared" si="1"/>
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>73</v>
+      </c>
+      <c r="C48" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A49">
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="C21" t="s">
+      <c r="B49" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A50">
+        <f t="shared" si="1"/>
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A51">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>126</v>
+      </c>
+      <c r="C51" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A52">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>128</v>
+      </c>
+      <c r="C52" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A53">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A54">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>131</v>
+      </c>
+      <c r="C54" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A55">
+        <f t="shared" si="1"/>
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A56">
+        <f t="shared" si="1"/>
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>135</v>
+      </c>
+      <c r="C56" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A57">
+        <f t="shared" si="1"/>
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>137</v>
+      </c>
+      <c r="C57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A58">
+        <f t="shared" si="1"/>
         <v>57</v>
       </c>
+      <c r="B58" t="s">
+        <v>139</v>
+      </c>
+      <c r="C58" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A59">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>140</v>
+      </c>
+      <c r="C59" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A60">
+        <f t="shared" si="1"/>
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>142</v>
+      </c>
+      <c r="C60" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A61">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A62">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>145</v>
+      </c>
+      <c r="C62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A63">
+        <f t="shared" si="1"/>
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A64">
+        <f t="shared" si="1"/>
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>43</v>
+      </c>
+      <c r="C64" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A65">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>150</v>
+      </c>
+      <c r="C65" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A66">
+        <f t="shared" ref="A66:A97" si="2">ROW()-1</f>
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>152</v>
+      </c>
+      <c r="C66" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A67">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A68">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="B68" t="b">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A69">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>155</v>
+      </c>
+      <c r="C69" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A70">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>157</v>
+      </c>
+      <c r="C70" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A71">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A72">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A73">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A74">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C74" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A75">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>166</v>
+      </c>
+      <c r="C75" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A76">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>168</v>
+      </c>
+      <c r="C76" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A77">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>170</v>
+      </c>
+      <c r="C77" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A78">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>172</v>
+      </c>
+      <c r="C78" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A79">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A80">
+        <f t="shared" si="2"/>
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A81">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A82">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A83">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A84">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>184</v>
+      </c>
+      <c r="C84" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A85">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>186</v>
+      </c>
+      <c r="C85" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A86">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>188</v>
+      </c>
+      <c r="C86" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A87">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>190</v>
+      </c>
+      <c r="C87" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A88">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>192</v>
+      </c>
+      <c r="C88" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A89">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>193</v>
+      </c>
+      <c r="C89" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A90">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>195</v>
+      </c>
+      <c r="C90" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A91">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>197</v>
+      </c>
+      <c r="C91" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A92">
+        <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A93">
+        <f t="shared" si="2"/>
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>201</v>
+      </c>
+      <c r="C93" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A94">
+        <f t="shared" si="2"/>
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A95">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>204</v>
+      </c>
+      <c r="C95" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A96">
+        <f t="shared" si="2"/>
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>206</v>
+      </c>
+      <c r="C96" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A97">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>208</v>
+      </c>
+      <c r="C97" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A98">
+        <f t="shared" ref="A98:A129" si="3">ROW()-1</f>
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>210</v>
+      </c>
+      <c r="C98" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A99">
+        <f t="shared" si="3"/>
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>212</v>
+      </c>
+      <c r="C99" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A100">
+        <f t="shared" si="3"/>
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>214</v>
+      </c>
+      <c r="C100" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A101">
+        <f t="shared" si="3"/>
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>216</v>
+      </c>
+      <c r="C101" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A102">
+        <f t="shared" si="3"/>
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>218</v>
+      </c>
+      <c r="C102" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A103">
+        <f t="shared" si="3"/>
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>28</v>
+      </c>
+      <c r="C103" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A104">
+        <f t="shared" si="3"/>
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>221</v>
+      </c>
+      <c r="C104" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A105">
+        <f t="shared" si="3"/>
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>124</v>
+      </c>
+      <c r="C105" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A106">
+        <f t="shared" si="3"/>
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>224</v>
+      </c>
+      <c r="C106" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A107">
+        <f t="shared" si="3"/>
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>226</v>
+      </c>
+      <c r="C107" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A108">
+        <f t="shared" si="3"/>
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>228</v>
+      </c>
+      <c r="C108" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A109">
+        <f t="shared" si="3"/>
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>27</v>
+      </c>
+      <c r="C109" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A110">
+        <f t="shared" si="3"/>
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>73</v>
+      </c>
+      <c r="C110" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A111">
+        <f t="shared" si="3"/>
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>116</v>
+      </c>
+      <c r="C111" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A112">
+        <f t="shared" si="3"/>
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>201</v>
+      </c>
+      <c r="C112" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A113">
+        <f t="shared" si="3"/>
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>28</v>
+      </c>
+      <c r="C113" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A114">
+        <f t="shared" si="3"/>
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>114</v>
+      </c>
+      <c r="C114" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A115">
+        <f t="shared" si="3"/>
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>128</v>
+      </c>
+      <c r="C115" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A116">
+        <f t="shared" si="3"/>
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>124</v>
+      </c>
+      <c r="C116" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A117">
+        <f t="shared" si="3"/>
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>112</v>
+      </c>
+      <c r="C117" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A118">
+        <f t="shared" si="3"/>
+        <v>117</v>
+      </c>
+      <c r="B118" t="b">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A119">
+        <f t="shared" si="3"/>
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>188</v>
+      </c>
+      <c r="C119" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A120">
+        <f t="shared" si="3"/>
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A121">
+        <f t="shared" si="3"/>
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A122">
+        <f t="shared" si="3"/>
+        <v>121</v>
+      </c>
+      <c r="B122" t="s">
+        <v>73</v>
+      </c>
+      <c r="C122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A123">
+        <f t="shared" si="3"/>
+        <v>122</v>
+      </c>
+      <c r="B123" t="s">
+        <v>28</v>
+      </c>
+      <c r="C123" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A124">
+        <f t="shared" si="3"/>
+        <v>123</v>
+      </c>
+      <c r="B124" t="s">
+        <v>124</v>
+      </c>
+      <c r="C124" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A125">
+        <f t="shared" si="3"/>
+        <v>124</v>
+      </c>
+      <c r="B125" t="s">
+        <v>114</v>
+      </c>
+      <c r="C125" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A126">
+        <f t="shared" si="3"/>
+        <v>125</v>
+      </c>
+      <c r="B126" t="s">
+        <v>112</v>
+      </c>
+      <c r="C126" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A127">
+        <f t="shared" si="3"/>
+        <v>126</v>
+      </c>
+      <c r="B127" t="b">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A128">
+        <f t="shared" si="3"/>
+        <v>127</v>
+      </c>
+      <c r="B128" t="s">
+        <v>188</v>
+      </c>
+      <c r="C128" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A129">
+        <f t="shared" si="3"/>
+        <v>128</v>
+      </c>
+      <c r="B129" t="s">
+        <v>126</v>
+      </c>
+      <c r="C129" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A130">
+        <f t="shared" ref="A130:A135" si="4">ROW()-1</f>
+        <v>129</v>
+      </c>
+      <c r="B130" t="s">
+        <v>27</v>
+      </c>
+      <c r="C130" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A131">
+        <f t="shared" si="4"/>
+        <v>130</v>
+      </c>
+      <c r="B131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C131" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A132">
+        <f t="shared" si="4"/>
+        <v>131</v>
+      </c>
+      <c r="B132" t="s">
+        <v>28</v>
+      </c>
+      <c r="C132" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A133">
+        <f t="shared" si="4"/>
+        <v>132</v>
+      </c>
+      <c r="B133" t="s">
+        <v>124</v>
+      </c>
+      <c r="C133" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A134">
+        <f t="shared" si="4"/>
+        <v>133</v>
+      </c>
+      <c r="B134" t="s">
+        <v>114</v>
+      </c>
+      <c r="C134" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A135">
+        <f t="shared" si="4"/>
+        <v>134</v>
+      </c>
+      <c r="B135" t="s">
+        <v>112</v>
+      </c>
+      <c r="C135" t="s">
+        <v>253</v>
+      </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/careerstop.xlsx
+++ b/careerstop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galja\pgaljan.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA38F772-D867-4F39-8418-985395839C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2A44B5-1298-4724-A6A9-253030ADA587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-37" windowWidth="28996" windowHeight="15675" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="309">
   <si>
     <t>Tools</t>
   </si>
@@ -109,9 +109,6 @@
     <t>To</t>
   </si>
   <si>
-    <t>Anytown, USA</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -241,15 +238,6 @@
     <t>last</t>
   </si>
   <si>
-    <t>Feb 2021</t>
-  </si>
-  <si>
-    <t>Sep 2023</t>
-  </si>
-  <si>
-    <t>Process Optimization</t>
-  </si>
-  <si>
     <t>Accomplishment 1</t>
   </si>
   <si>
@@ -832,170 +820,182 @@
     <t>Org Description</t>
   </si>
   <si>
-    <t>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</t>
-  </si>
-  <si>
-    <t>Staff Scheduling</t>
-  </si>
-  <si>
-    <t>Vendor Management</t>
-  </si>
-  <si>
-    <t>Inventory Management</t>
-  </si>
-  <si>
-    <t>Store Performance Management</t>
-  </si>
-  <si>
-    <t>Customer Service Oversight</t>
-  </si>
-  <si>
-    <t>Performance Monitoring</t>
-  </si>
-  <si>
-    <t>Resource Coordination</t>
-  </si>
-  <si>
-    <t>Cross-Functional Coordination</t>
-  </si>
-  <si>
-    <t>Staff Development</t>
-  </si>
-  <si>
-    <t>Retail/Operations Management</t>
-  </si>
-  <si>
-    <t>Anytown Retail</t>
-  </si>
-  <si>
-    <t>Store Manager</t>
-  </si>
-  <si>
-    <t>Square POS</t>
-  </si>
-  <si>
-    <t>Toast</t>
-  </si>
-  <si>
-    <t>Shopify</t>
-  </si>
-  <si>
-    <t>NetSuite</t>
-  </si>
-  <si>
-    <t>TradeGecko</t>
-  </si>
-  <si>
-    <t>Deputy</t>
-  </si>
-  <si>
     <t>Excel</t>
   </si>
   <si>
-    <t>Slack</t>
-  </si>
-  <si>
-    <t>PowerBI</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
-    <t>Zendesk</t>
-  </si>
-  <si>
-    <t>Mailchimp</t>
-  </si>
-  <si>
-    <t>QuickBooks</t>
-  </si>
-  <si>
-    <t>Staff Training &amp; Development</t>
-  </si>
-  <si>
-    <t>Merchandising Strategy</t>
-  </si>
-  <si>
-    <t>Supply Chain Coordination</t>
-  </si>
-  <si>
-    <t>Customer Service Management</t>
-  </si>
-  <si>
-    <t>Compliance Management</t>
-  </si>
-  <si>
-    <t>Multi-location Oversight</t>
-  </si>
-  <si>
-    <t>Crisis Management</t>
-  </si>
-  <si>
-    <t>Seasonal Planning</t>
-  </si>
-  <si>
-    <t>Budget Forecasting</t>
-  </si>
-  <si>
-    <t>Operations Management</t>
-  </si>
-  <si>
-    <t>Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</t>
-  </si>
-  <si>
-    <t>Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</t>
-  </si>
-  <si>
-    <t>Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</t>
-  </si>
-  <si>
-    <t>Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</t>
-  </si>
-  <si>
-    <t>Daily Standups</t>
-  </si>
-  <si>
-    <t>Performance Dashboards</t>
-  </si>
-  <si>
-    <t>Mystery Shopping</t>
-  </si>
-  <si>
-    <t>Staff Cross-training</t>
-  </si>
-  <si>
-    <t>Standard Operating Procedures</t>
-  </si>
-  <si>
-    <t>Customer Satisfaction</t>
-  </si>
-  <si>
-    <t>Operational Efficiency</t>
-  </si>
-  <si>
-    <t>Team Development</t>
-  </si>
-  <si>
-    <t>Brand Consistency</t>
-  </si>
-  <si>
-    <t>Safety &amp; Compliance</t>
-  </si>
-  <si>
-    <t>Community Engagement</t>
-  </si>
-  <si>
-    <t>Profitability</t>
-  </si>
-  <si>
     <t>Accomplishments (&lt;=4)</t>
+  </si>
+  <si>
+    <t>Paul Galjan</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Dell Technologies</t>
+  </si>
+  <si>
+    <t>Hopkinton, MA</t>
+  </si>
+  <si>
+    <t>Infrastructure Automation</t>
+  </si>
+  <si>
+    <t>Oct 2023</t>
+  </si>
+  <si>
+    <t>current</t>
+  </si>
+  <si>
+    <t>Power Platform</t>
+  </si>
+  <si>
+    <t>Markdown</t>
+  </si>
+  <si>
+    <t>Drawio</t>
+  </si>
+  <si>
+    <t>VSCode</t>
+  </si>
+  <si>
+    <t>Confluence</t>
+  </si>
+  <si>
+    <t>PowerPoint</t>
+  </si>
+  <si>
+    <t>Jira</t>
+  </si>
+  <si>
+    <t>Jira Align</t>
+  </si>
+  <si>
+    <t>Miro</t>
+  </si>
+  <si>
+    <t>CoPilot</t>
+  </si>
+  <si>
+    <t>Analyst</t>
+  </si>
+  <si>
+    <t>Data Collection</t>
+  </si>
+  <si>
+    <t>Data Classification</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>Impact Assessment</t>
+  </si>
+  <si>
+    <t>Product Planning</t>
+  </si>
+  <si>
+    <t>Requirements Development</t>
+  </si>
+  <si>
+    <t>Development Execution</t>
+  </si>
+  <si>
+    <t>Core Team Support</t>
+  </si>
+  <si>
+    <t>Data Visualization</t>
+  </si>
+  <si>
+    <t>API Defintiion</t>
+  </si>
+  <si>
+    <t>Data Modeling</t>
+  </si>
+  <si>
+    <t>Market Analysis</t>
+  </si>
+  <si>
+    <t>Extract/Transform/Load (ETL)</t>
+  </si>
+  <si>
+    <t>System Architecture</t>
+  </si>
+  <si>
+    <t>Agile Development</t>
+  </si>
+  <si>
+    <t>Value Pricing</t>
+  </si>
+  <si>
+    <t>Hypothesis Testing</t>
+  </si>
+  <si>
+    <t>Project Management</t>
+  </si>
+  <si>
+    <t>Timeboxed Planning</t>
+  </si>
+  <si>
+    <t>Visual Storytelling</t>
+  </si>
+  <si>
+    <t>Quantification</t>
+  </si>
+  <si>
+    <t>Frameworks</t>
+  </si>
+  <si>
+    <t>Structured Analysis</t>
+  </si>
+  <si>
+    <t>Work Breakdown</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>Efficiency</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Clarity</t>
+  </si>
+  <si>
+    <t>Consistency</t>
+  </si>
+  <si>
+    <t>Community</t>
+  </si>
+  <si>
+    <t>Copy/Paste below as picture</t>
+  </si>
+  <si>
+    <t>Streamlined UI/API definition handoff with UI Mockup-as-code initiative</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standardized Dell ISG 2-year software lifecycle policy, replacing fragmented product cycles with predictable enterprise planning.  </t>
+  </si>
+  <si>
+    <t>Created constent data model for representation of Dell and 3rd party infrastructure assets in Dell Automation Platform</t>
+  </si>
+  <si>
+    <t>Created consistent project management consumption method to naviagte the transitionbetween project management platforms and approaches</t>
+  </si>
+  <si>
+    <t>Dell Automation Platform - specializing in TOSCA-based declarative automation solutions with hybrid imperative capabilities, serving enterprise clients through agile development methodologies and related optimization.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,8 +1019,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1055,6 +1062,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1273,10 +1285,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1339,10 +1352,6 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1355,25 +1364,17 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1399,19 +1400,40 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Accent1" xfId="1" builtinId="29"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="40">
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFDAE8FC"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <border>
@@ -1424,9 +1446,9 @@
     </dxf>
     <dxf>
       <border>
-        <left style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </left>
+        </bottom>
         <vertical/>
         <horizontal/>
       </border>
@@ -1439,6 +1461,32 @@
         <vertical/>
         <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1496,6 +1544,33 @@
       </fill>
     </dxf>
     <dxf>
+      <border>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1508,11 +1583,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -1522,13 +1592,9 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1586,6 +1652,33 @@
       </fill>
     </dxf>
     <dxf>
+      <border>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1598,11 +1691,6 @@
       </font>
     </dxf>
     <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <border>
         <left style="thin">
           <color auto="1"/>
@@ -1612,13 +1700,9 @@
       </border>
     </dxf>
     <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <font>
+        <color theme="0"/>
+      </font>
     </dxf>
     <dxf>
       <fill>
@@ -1646,141 +1730,6 @@
           <bgColor theme="0"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -1811,16 +1760,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>6</xdr:col>
-          <xdr:colOff>1832161</xdr:colOff>
-          <xdr:row>22</xdr:row>
-          <xdr:rowOff>5603</xdr:rowOff>
+          <xdr:col>1</xdr:col>
+          <xdr:colOff>22411</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>39222</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>17</xdr:col>
-          <xdr:colOff>985277</xdr:colOff>
-          <xdr:row>46</xdr:row>
-          <xdr:rowOff>29416</xdr:rowOff>
+          <xdr:col>13</xdr:col>
+          <xdr:colOff>773206</xdr:colOff>
+          <xdr:row>52</xdr:row>
+          <xdr:rowOff>61634</xdr:rowOff>
         </xdr:to>
         <xdr:pic>
           <xdr:nvPicPr>
@@ -1835,7 +1784,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$AD$150:$AI$172" spid="_x0000_s1094"/>
+                  <a14:cameraTool cellRange="$AD$147:$AI$169" spid="_x0000_s1097"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1849,8 +1798,8 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="8213912" y="4095750"/>
-              <a:ext cx="9658630" cy="4326872"/>
+              <a:off x="1473573" y="5205134"/>
+              <a:ext cx="11939868" cy="4325471"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1896,7 +1845,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}" name="names" displayName="names" ref="A1:C135" totalsRowShown="0">
   <autoFilter ref="A1:C135" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="46">
+    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="39">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2FBF4AE8-10BE-49DC-A08D-B377AD3CB245}" name="first"/>
@@ -2223,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3348163-AFAC-4B5E-B6D7-A630EDC47AB4}">
-  <dimension ref="A2:AI171"/>
+  <dimension ref="A2:AI168"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
@@ -2243,8 +2192,8 @@
     <col min="16" max="16" width="25.86328125" customWidth="1"/>
     <col min="17" max="17" width="3.86328125" customWidth="1"/>
     <col min="18" max="18" width="23.46484375" customWidth="1"/>
-    <col min="28" max="28" width="9.06640625" style="24"/>
-    <col min="30" max="33" width="29.9296875" customWidth="1"/>
+    <col min="28" max="28" width="9.06640625" style="23"/>
+    <col min="30" max="33" width="37.9296875" customWidth="1"/>
     <col min="34" max="34" width="1.86328125" customWidth="1"/>
     <col min="35" max="35" width="13.3984375" customWidth="1"/>
     <col min="36" max="36" width="24.3984375" bestFit="1" customWidth="1"/>
@@ -2253,11 +2202,10 @@
     <row r="2" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="39" t="str" cm="1">
-        <f t="array" aca="1" ref="B3" ca="1">randomName</f>
-        <v>Rowan Thompson</v>
+        <v>15</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>254</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -2285,22 +2233,22 @@
       <c r="A4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="39" t="s">
-        <v>291</v>
+      <c r="B4" s="6" t="s">
+        <v>271</v>
       </c>
       <c r="D4" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="20" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="20" t="s">
-        <v>61</v>
+        <v>272</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="20" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="b">
@@ -2308,15 +2256,15 @@
         <v>1</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="20" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="20" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.45">
@@ -2324,37 +2272,37 @@
         <v>9</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="D5" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="20" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="20" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="b">
-        <f t="shared" ref="K5:K19" si="0">IF(L5="","",ISEVEN(ROW()))</f>
+        <f t="shared" ref="K5:K18" si="0">IF(L5="","",ISEVEN(ROW()))</f>
         <v>0</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="20" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="20" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
@@ -2362,21 +2310,21 @@
         <v>10</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>15</v>
+        <v>257</v>
       </c>
       <c r="D6" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="20" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="20" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="20" t="s">
-        <v>259</v>
+        <v>279</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="b">
@@ -2384,15 +2332,15 @@
         <v>1</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="20" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="20" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -2400,21 +2348,21 @@
         <v>13</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>59</v>
+        <v>259</v>
       </c>
       <c r="D7" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="20" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="20" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="b">
@@ -2422,15 +2370,15 @@
         <v>0</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="20" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="O7" s="6"/>
       <c r="P7" s="20" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
@@ -2438,37 +2386,35 @@
         <v>14</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>60</v>
+        <v>260</v>
       </c>
       <c r="D8" s="22" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="20" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="20" t="s">
-        <v>261</v>
-      </c>
+      <c r="I8" s="20"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="M8" s="6"/>
       <c r="N8" s="20" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="O8" s="6"/>
       <c r="P8" s="20" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
@@ -2476,13 +2422,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="D9" s="22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="20"/>
@@ -2494,13 +2440,15 @@
         <v>0</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M9" s="6"/>
-      <c r="N9" s="20"/>
+      <c r="N9" s="20" t="s">
+        <v>296</v>
+      </c>
       <c r="O9" s="6"/>
       <c r="P9" s="20" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
@@ -2508,13 +2456,13 @@
         <v>3</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="D10" s="22" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>266</v>
-      </c>
-      <c r="D10" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>275</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="7"/>
@@ -2526,22 +2474,20 @@
         <v>1</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="M10" s="6"/>
       <c r="N10" s="20"/>
       <c r="O10" s="6"/>
-      <c r="P10" s="20" t="s">
-        <v>307</v>
-      </c>
+      <c r="P10" s="20"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B11" s="26"/>
+      <c r="B11" s="25"/>
       <c r="D11" s="22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
@@ -2553,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="20"/>
@@ -2561,12 +2507,12 @@
       <c r="P11" s="20"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B12" s="26"/>
+      <c r="B12" s="25"/>
       <c r="D12" s="22" t="b">
         <v>0</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
@@ -2578,7 +2524,7 @@
         <v>1</v>
       </c>
       <c r="L12" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="M12" s="6"/>
       <c r="N12" s="7"/>
@@ -2586,46 +2532,50 @@
       <c r="P12" s="7"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B13" s="26"/>
+      <c r="B13" s="25"/>
       <c r="D13" s="22" t="b">
         <v>0</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="6" t="str">
+      <c r="K13" s="6" t="b">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="L13" s="20" t="s">
+        <v>289</v>
+      </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B14" s="26"/>
+      <c r="B14" s="25"/>
       <c r="D14" s="22" t="b">
         <v>0</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6" t="str">
+      <c r="K14" s="6" t="b">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="L14" s="20" t="s">
+        <v>290</v>
+      </c>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
@@ -2635,9 +2585,7 @@
       <c r="D15" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E15" s="20" t="s">
-        <v>280</v>
-      </c>
+      <c r="E15" s="20"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="H15" s="6"/>
@@ -2647,7 +2595,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="31"/>
+      <c r="L15" s="20"/>
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
       <c r="O15" s="6"/>
@@ -2657,9 +2605,7 @@
       <c r="D16" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E16" s="20" t="s">
-        <v>281</v>
-      </c>
+      <c r="E16" s="20"/>
       <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="6"/>
@@ -2669,14 +2615,13 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L16" s="31"/>
+      <c r="L16" s="20"/>
       <c r="M16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="D17" s="28"/>
-      <c r="E17" s="23"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2686,13 +2631,19 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L17" s="20"/>
+      <c r="L17" s="27"/>
       <c r="M17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="E18" s="20"/>
+      <c r="A18" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
@@ -2702,423 +2653,402 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L18" s="28"/>
+      <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A19" s="8" t="s">
-        <v>255</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="str">
-        <f t="shared" si="0"/>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A20" s="24" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A21" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A22" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A23" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A24" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A25" s="26"/>
+      <c r="B25" s="6"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="B28" s="44" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="146" spans="30:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="147" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD147" s="37" t="str">
+        <f>B3&amp; " ("&amp;B10&amp;")"</f>
+        <v>Paul Galjan (Infrastructure Automation)</v>
+      </c>
+      <c r="AE147" s="38" t="str">
+        <f>B9&amp;" with "&amp;B5&amp;" ("&amp;B6&amp;")"</f>
+        <v>Product Manager with Dell Technologies (Hopkinton, MA)</v>
+      </c>
+      <c r="AF147" s="39"/>
+      <c r="AG147" s="40" t="str">
+        <f>B7&amp;" - "&amp;B8</f>
+        <v>Oct 2023 - current</v>
+      </c>
+    </row>
+    <row r="148" spans="30:33" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="AD148" s="41" t="str">
+        <f>B18</f>
+        <v>Dell Automation Platform - specializing in TOSCA-based declarative automation solutions with hybrid imperative capabilities, serving enterprise clients through agile development methodologies and related optimization.</v>
+      </c>
+      <c r="AE148" s="42"/>
+      <c r="AF148" s="42"/>
+      <c r="AG148" s="43"/>
+    </row>
+    <row r="149" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD149" s="11" t="str" cm="1">
+        <f t="array" ref="AD149:AD162">_xlfn.VSTACK(
+"Tools",
+"Core","  • "&amp;_xlfn._xlws.FILTER(E3:E18,D3:D18=TRUE),
+"Incidental","  • "&amp;_xlfn._xlws.FILTER(E3:E18,(D3:D18=FALSE)*(E3:E18&lt;&gt;"")))</f>
+        <v>Tools</v>
+      </c>
+      <c r="AE149" s="10" t="str" cm="1">
+        <f t="array" ref="AE149:AE155">_xlfn.VSTACK("Profession",B4,"  • "&amp;_xlfn._xlws.FILTER(G4:G9,G4:G9&lt;&gt;""))</f>
+        <v>Profession</v>
+      </c>
+      <c r="AF149" s="9" t="str" cm="1">
+        <f t="array" ref="AF149:AF155">_xlfn.VSTACK("Job",B9,B10,"  • "&amp;_xlfn._xlws.FILTER(I4:I8,I4:I8&lt;&gt;""))</f>
+        <v>Job</v>
+      </c>
+      <c r="AG149" s="36" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="150" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD150" s="30" t="str">
+        <v>Core</v>
+      </c>
+      <c r="AE150" s="12" t="str">
+        <v>Analyst</v>
+      </c>
+      <c r="AF150" s="12" t="str">
+        <v>Product Manager</v>
+      </c>
+      <c r="AG150" s="31" t="str" cm="1">
+        <f t="array" ref="AG150:AG163">_xlfn.VSTACK(
+  "  Practices","  • "&amp;_xlfn._xlws.FILTER(N4:N18,N4:N18&lt;&gt;""),
+"  Priorities","  • "&amp;_xlfn._xlws.FILTER(P4:P18,P4:P18&lt;&gt;""))</f>
+        <v xml:space="preserve">  Practices</v>
+      </c>
+    </row>
+    <row r="151" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD151" s="32" t="str">
+        <v xml:space="preserve">  • Excel</v>
+      </c>
+      <c r="AE151" s="13" t="str">
+        <v xml:space="preserve">  • Data Collection</v>
+      </c>
+      <c r="AF151" s="15" t="str">
+        <v>Infrastructure Automation</v>
+      </c>
+      <c r="AG151" s="13" t="str">
+        <v xml:space="preserve">  • Timeboxed Planning</v>
+      </c>
+    </row>
+    <row r="152" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD152" s="32" t="str">
+        <v xml:space="preserve">  • Power Platform</v>
+      </c>
+      <c r="AE152" s="13" t="str">
+        <v xml:space="preserve">  • Data Classification</v>
+      </c>
+      <c r="AF152" s="13" t="str">
+        <v xml:space="preserve">  • Product Planning</v>
+      </c>
+      <c r="AG152" s="13" t="str">
+        <v xml:space="preserve">  • Visual Storytelling</v>
+      </c>
+    </row>
+    <row r="153" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD153" s="32" t="str">
+        <v xml:space="preserve">  • Markdown</v>
+      </c>
+      <c r="AE153" s="13" t="str">
+        <v xml:space="preserve">  • Analysis</v>
+      </c>
+      <c r="AF153" s="13" t="str">
+        <v xml:space="preserve">  • Requirements Development</v>
+      </c>
+      <c r="AG153" s="13" t="str">
+        <v xml:space="preserve">  • Quantification</v>
+      </c>
+    </row>
+    <row r="154" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD154" s="32" t="str">
+        <v xml:space="preserve">  • Drawio</v>
+      </c>
+      <c r="AE154" s="13" t="str">
+        <v xml:space="preserve">  • Communication</v>
+      </c>
+      <c r="AF154" s="13" t="str">
+        <v xml:space="preserve">  • Development Execution</v>
+      </c>
+      <c r="AG154" s="13" t="str">
+        <v xml:space="preserve">  • Frameworks</v>
+      </c>
+    </row>
+    <row r="155" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD155" s="32" t="str">
+        <v xml:space="preserve">  • VSCode</v>
+      </c>
+      <c r="AE155" s="13" t="str">
+        <v xml:space="preserve">  • Impact Assessment</v>
+      </c>
+      <c r="AF155" s="13" t="str">
+        <v xml:space="preserve">  • Core Team Support</v>
+      </c>
+      <c r="AG155" s="29" t="str">
+        <v xml:space="preserve">  • Structured Analysis</v>
+      </c>
+    </row>
+    <row r="156" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD156" s="32" t="str">
+        <v>Incidental</v>
+      </c>
+      <c r="AE156" s="14"/>
+      <c r="AF156" s="16"/>
+      <c r="AG156" s="13" t="str">
+        <v xml:space="preserve">  • Work Breakdown</v>
+      </c>
+    </row>
+    <row r="157" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD157" s="33" t="str">
+        <v xml:space="preserve">  • Confluence</v>
+      </c>
+      <c r="AE157" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF157" s="34"/>
+      <c r="AG157" s="13" t="str">
+        <v xml:space="preserve">  Priorities</v>
+      </c>
+    </row>
+    <row r="158" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD158" s="33" t="str">
+        <v xml:space="preserve">  • PowerPoint</v>
+      </c>
+      <c r="AE158" s="28" t="str" cm="1">
+        <f t="array" ref="AE158:AF163">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
+" • "&amp;_xlfn._xlws.FILTER(L4:L18,K4:K18=TRUE),
+" • "&amp;_xlfn._xlws.FILTER(L4:L18,(K4:K18=FALSE)*(L4:L18&lt;&gt;""))),"")),"")</f>
+        <v xml:space="preserve"> • Data Visualization</v>
+      </c>
+      <c r="AF158" s="28" t="str">
+        <v xml:space="preserve"> • API Defintiion</v>
+      </c>
+      <c r="AG158" s="13" t="str">
+        <v xml:space="preserve">  • Purpose</v>
+      </c>
+    </row>
+    <row r="159" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD159" s="33" t="str">
+        <v xml:space="preserve">  • Jira</v>
+      </c>
+      <c r="AE159" s="28" t="str">
+        <v xml:space="preserve"> • Data Modeling</v>
+      </c>
+      <c r="AF159" s="28" t="str">
+        <v xml:space="preserve"> • Market Analysis</v>
+      </c>
+      <c r="AG159" s="13" t="str">
+        <v xml:space="preserve">  • Efficiency</v>
+      </c>
+    </row>
+    <row r="160" spans="30:33" x14ac:dyDescent="0.45">
+      <c r="AD160" s="33" t="str">
+        <v xml:space="preserve">  • Jira Align</v>
+      </c>
+      <c r="AE160" s="28" t="str">
+        <v xml:space="preserve"> • Extract/Transform/Load (ETL)</v>
+      </c>
+      <c r="AF160" s="28" t="str">
+        <v xml:space="preserve"> • System Architecture</v>
+      </c>
+      <c r="AG160" s="13" t="str">
+        <v xml:space="preserve">  • Process</v>
+      </c>
+    </row>
+    <row r="161" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD161" s="33" t="str">
+        <v xml:space="preserve">  • Miro</v>
+      </c>
+      <c r="AE161" s="28" t="str">
+        <v xml:space="preserve"> • Agile Development</v>
+      </c>
+      <c r="AF161" s="28" t="str">
+        <v xml:space="preserve"> • Market Analysis</v>
+      </c>
+      <c r="AG161" s="13" t="str">
+        <v xml:space="preserve">  • Clarity</v>
+      </c>
+    </row>
+    <row r="162" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD162" s="33" t="str">
+        <v xml:space="preserve">  • CoPilot</v>
+      </c>
+      <c r="AE162" s="28" t="str">
+        <v xml:space="preserve"> • Value Pricing</v>
+      </c>
+      <c r="AF162" s="28" t="str">
+        <v xml:space="preserve"> • Hypothesis Testing</v>
+      </c>
+      <c r="AG162" s="13" t="str">
+        <v xml:space="preserve">  • Consistency</v>
+      </c>
+      <c r="AI162" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="163" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD163" s="33"/>
+      <c r="AE163" s="28" t="str">
+        <v xml:space="preserve"> • Project Management</v>
+      </c>
+      <c r="AF163" s="28" t="str">
         <v/>
       </c>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A23" s="25" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A24" s="27" t="s">
+      <c r="AG163" s="13" t="str">
+        <v xml:space="preserve">  • Community</v>
+      </c>
+      <c r="AI163" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="164" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD164" s="16"/>
+      <c r="AE164" s="28"/>
+      <c r="AF164" s="28"/>
+      <c r="AG164" s="13"/>
+      <c r="AI164" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="165" spans="30:35" x14ac:dyDescent="0.45">
+      <c r="AD165" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A25" s="27" t="s">
-        <v>65</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A26" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A27" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A28" s="27"/>
-      <c r="B28" s="6"/>
-    </row>
-    <row r="149" spans="30:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="150" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD150" s="41" t="str">
-        <f ca="1">B3&amp; " ("&amp;B10&amp;")"</f>
-        <v>Rowan Thompson (Retail/Operations Management)</v>
-      </c>
-      <c r="AE150" s="42" t="str">
-        <f>B9&amp;" with "&amp;B5&amp;" ("&amp;B6&amp;")"</f>
-        <v>Store Manager with Anytown Retail (Anytown, USA)</v>
-      </c>
-      <c r="AF150" s="43"/>
-      <c r="AG150" s="44" t="str">
-        <f>B7&amp;" - "&amp;B8</f>
-        <v>Feb 2021 - Sep 2023</v>
-      </c>
-    </row>
-    <row r="151" spans="30:33" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="AD151" s="45" t="str">
-        <f>B19</f>
-        <v>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</v>
-      </c>
-      <c r="AE151" s="46"/>
-      <c r="AF151" s="46"/>
-      <c r="AG151" s="47"/>
-    </row>
-    <row r="152" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD152" s="11" t="str" cm="1">
-        <f t="array" ref="AD152:AD167">_xlfn.VSTACK(
-"Tools",
-"Core","  • "&amp;_xlfn._xlws.FILTER(E3:E19,D3:D19=TRUE),
-"Incidental","  • "&amp;_xlfn._xlws.FILTER(E3:E19,(D3:D19=FALSE)*(E3:E19&lt;&gt;"")))</f>
-        <v>Tools</v>
-      </c>
-      <c r="AE152" s="10" t="str" cm="1">
-        <f t="array" ref="AE152:AE158">_xlfn.VSTACK("Profession",B10,"  • "&amp;_xlfn._xlws.FILTER(G4:G9,G4:G9&lt;&gt;""))</f>
-        <v>Profession</v>
-      </c>
-      <c r="AF152" s="9" t="str" cm="1">
-        <f t="array" ref="AF152:AF159">_xlfn.VSTACK("Job",B9,B10,"  • "&amp;_xlfn._xlws.FILTER(I4:I8,I4:I8&lt;&gt;""))</f>
-        <v>Job</v>
-      </c>
-      <c r="AG152" s="40" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="153" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD153" s="33" t="str">
-        <v>Core</v>
-      </c>
-      <c r="AE153" s="12" t="str">
-        <v>Retail/Operations Management</v>
-      </c>
-      <c r="AF153" s="12" t="str">
-        <v>Store Manager</v>
-      </c>
-      <c r="AG153" s="34" t="str" cm="1">
-        <f t="array" ref="AG153:AG166">_xlfn.VSTACK(
-"Practices","  • "&amp;_xlfn._xlws.FILTER(N4:N19,N4:N19&lt;&gt;""),
-"Priorities","  • "&amp;_xlfn._xlws.FILTER(P4:P19,P4:P19&lt;&gt;""))</f>
-        <v>Practices</v>
-      </c>
-    </row>
-    <row r="154" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD154" s="35" t="str">
-        <v xml:space="preserve">  • Square POS</v>
-      </c>
-      <c r="AE154" s="13" t="str">
-        <v xml:space="preserve">  • Process Optimization</v>
-      </c>
-      <c r="AF154" s="15" t="str">
-        <v>Retail/Operations Management</v>
-      </c>
-      <c r="AG154" s="13" t="str">
-        <v xml:space="preserve">  • Daily Standups</v>
-      </c>
-    </row>
-    <row r="155" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD155" s="35" t="str">
-        <v xml:space="preserve">  • Toast</v>
-      </c>
-      <c r="AE155" s="13" t="str">
-        <v xml:space="preserve">  • Performance Monitoring</v>
-      </c>
-      <c r="AF155" s="13" t="str">
-        <v xml:space="preserve">  • Staff Scheduling</v>
-      </c>
-      <c r="AG155" s="13" t="str">
-        <v xml:space="preserve">  • Performance Dashboards</v>
-      </c>
-    </row>
-    <row r="156" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD156" s="35" t="str">
-        <v xml:space="preserve">  • Shopify</v>
-      </c>
-      <c r="AE156" s="13" t="str">
-        <v xml:space="preserve">  • Resource Coordination</v>
-      </c>
-      <c r="AF156" s="13" t="str">
-        <v xml:space="preserve">  • Vendor Management</v>
-      </c>
-      <c r="AG156" s="13" t="str">
-        <v xml:space="preserve">  • Mystery Shopping</v>
-      </c>
-    </row>
-    <row r="157" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD157" s="35" t="str">
-        <v xml:space="preserve">  • NetSuite</v>
-      </c>
-      <c r="AE157" s="13" t="str">
-        <v xml:space="preserve">  • Cross-Functional Coordination</v>
-      </c>
-      <c r="AF157" s="13" t="str">
-        <v xml:space="preserve">  • Inventory Management</v>
-      </c>
-      <c r="AG157" s="13" t="str">
-        <v xml:space="preserve">  • Staff Cross-training</v>
-      </c>
-    </row>
-    <row r="158" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD158" s="35" t="str">
-        <v xml:space="preserve">  • TradeGecko</v>
-      </c>
-      <c r="AE158" s="13" t="str">
-        <v xml:space="preserve">  • Staff Development</v>
-      </c>
-      <c r="AF158" s="13" t="str">
-        <v xml:space="preserve">  • Store Performance Management</v>
-      </c>
-      <c r="AG158" s="32" t="str">
-        <v xml:space="preserve">  • Standard Operating Procedures</v>
-      </c>
-    </row>
-    <row r="159" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD159" s="35" t="str">
-        <v xml:space="preserve">  • Deputy</v>
-      </c>
-      <c r="AE159" s="14"/>
-      <c r="AF159" s="16" t="str">
-        <v xml:space="preserve">  • Customer Service Oversight</v>
-      </c>
-      <c r="AG159" s="13" t="str">
-        <v>Priorities</v>
-      </c>
-    </row>
-    <row r="160" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD160" s="36" t="str">
-        <v xml:space="preserve">  • Excel</v>
-      </c>
-      <c r="AE160" s="37" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF160" s="37"/>
-      <c r="AG160" s="13" t="str">
-        <v xml:space="preserve">  • Customer Satisfaction</v>
-      </c>
-    </row>
-    <row r="161" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD161" s="36" t="str">
-        <v xml:space="preserve">  • Slack</v>
-      </c>
-      <c r="AE161" s="29" t="str" cm="1">
-        <f t="array" ref="AE161:AF165">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
-" • "&amp;_xlfn._xlws.FILTER(L4:L19,K4:K19=TRUE),
-" • "&amp;_xlfn._xlws.FILTER(L4:L19,(K4:K19=FALSE)*(L4:L19&lt;&gt;""))),"")),"")</f>
-        <v xml:space="preserve"> • Staff Training &amp; Development</v>
-      </c>
-      <c r="AF161" s="29" t="str">
-        <v xml:space="preserve"> • Merchandising Strategy</v>
-      </c>
-      <c r="AG161" s="13" t="str">
-        <v xml:space="preserve">  • Operational Efficiency</v>
-      </c>
-    </row>
-    <row r="162" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD162" s="36" t="str">
-        <v>Incidental</v>
-      </c>
-      <c r="AE162" s="29" t="str">
-        <v xml:space="preserve"> • Supply Chain Coordination</v>
-      </c>
-      <c r="AF162" s="29" t="str">
-        <v xml:space="preserve"> • Customer Service Management</v>
-      </c>
-      <c r="AG162" s="13" t="str">
-        <v xml:space="preserve">  • Team Development</v>
-      </c>
-    </row>
-    <row r="163" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD163" s="36" t="str">
-        <v xml:space="preserve">  • PowerBI</v>
-      </c>
-      <c r="AE163" s="29" t="str">
-        <v xml:space="preserve"> • Compliance Management</v>
-      </c>
-      <c r="AF163" s="29" t="str">
-        <v xml:space="preserve"> • Multi-location Oversight</v>
-      </c>
-      <c r="AG163" s="13" t="str">
-        <v xml:space="preserve">  • Brand Consistency</v>
-      </c>
-    </row>
-    <row r="164" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD164" s="36" t="str">
-        <v xml:space="preserve">  • Salesforce</v>
-      </c>
-      <c r="AE164" s="29" t="str">
-        <v xml:space="preserve"> • Crisis Management</v>
-      </c>
-      <c r="AF164" s="29" t="str">
-        <v xml:space="preserve"> • Seasonal Planning</v>
-      </c>
-      <c r="AG164" s="13" t="str">
-        <v xml:space="preserve">  • Safety &amp; Compliance</v>
-      </c>
-    </row>
-    <row r="165" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD165" s="36" t="str">
-        <v xml:space="preserve">  • Zendesk</v>
-      </c>
-      <c r="AE165" s="29" t="str">
-        <v xml:space="preserve"> • Budget Forecasting</v>
-      </c>
-      <c r="AF165" s="29" t="str">
-        <v/>
-      </c>
-      <c r="AG165" s="13" t="str">
-        <v xml:space="preserve">  • Community Engagement</v>
-      </c>
-      <c r="AI165" s="17" t="s">
-        <v>12</v>
+      <c r="AE165" t="str" cm="1">
+        <f t="array" ref="AE165:AE168">_xlfn._xlws.FILTER(B21:B25,B21:B25&lt;&gt;"")</f>
+        <v xml:space="preserve">Standardized Dell ISG 2-year software lifecycle policy, replacing fragmented product cycles with predictable enterprise planning.  </v>
       </c>
     </row>
     <row r="166" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD166" s="36" t="str">
-        <v xml:space="preserve">  • Mailchimp</v>
-      </c>
-      <c r="AE166" s="29"/>
-      <c r="AF166" s="29"/>
-      <c r="AG166" s="13" t="str">
-        <v xml:space="preserve">  • Profitability</v>
-      </c>
-      <c r="AI166" s="18" t="s">
-        <v>17</v>
+      <c r="AE166" t="str">
+        <v>Created constent data model for representation of Dell and 3rd party infrastructure assets in Dell Automation Platform</v>
       </c>
     </row>
     <row r="167" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD167" s="16" t="str">
-        <v xml:space="preserve">  • QuickBooks</v>
-      </c>
-      <c r="AE167" s="29"/>
-      <c r="AF167" s="29"/>
-      <c r="AG167" s="13"/>
-      <c r="AI167" s="19" t="s">
-        <v>18</v>
+      <c r="AE167" t="str">
+        <v>Streamlined UI/API definition handoff with UI Mockup-as-code initiative</v>
       </c>
     </row>
     <row r="168" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD168" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE168" s="30" t="str" cm="1">
-        <f t="array" ref="AE168:AE171">_xlfn._xlws.FILTER(B24:B28,B24:B28&lt;&gt;"")</f>
-        <v>Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</v>
-      </c>
-      <c r="AF168" s="30"/>
-      <c r="AG168" s="30"/>
-    </row>
-    <row r="169" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE169" t="str">
-        <v>Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</v>
-      </c>
-    </row>
-    <row r="170" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE170" t="str">
-        <v>Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</v>
-      </c>
-    </row>
-    <row r="171" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE171" t="str">
-        <v>Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</v>
+      <c r="AE168" t="str">
+        <v>Created consistent project management consumption method to naviagte the transitionbetween project management platforms and approaches</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="AD151:AG151"/>
+    <mergeCell ref="AD148:AG148"/>
   </mergeCells>
+  <conditionalFormatting sqref="A21:A1048576 A3:A18">
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>A3=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21:A25">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>B21=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:G26">
+    <cfRule type="expression" dxfId="10" priority="4">
+      <formula>LEN($B21)&gt;149</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D4:D16">
-    <cfRule type="expression" dxfId="12" priority="18">
+    <cfRule type="expression" dxfId="9" priority="18">
       <formula>$E4=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD152:AE167 AD25:AE50">
-    <cfRule type="expression" dxfId="11" priority="14">
-      <formula>OR(AD25="Core",AD25="Incidental",AD25="Key Accomplishments")</formula>
+  <conditionalFormatting sqref="AD20 AD165:AD168">
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>$AE20&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG152 AD25:AD1048576">
-    <cfRule type="expression" dxfId="10" priority="17">
-      <formula>OR(AD25="Core",AD25="Incidental")</formula>
+  <conditionalFormatting sqref="AD22:AD1048576 AG149">
+    <cfRule type="expression" dxfId="7" priority="17">
+      <formula>OR(AD22="Core",AD22="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG25:AG1048576">
-    <cfRule type="expression" dxfId="9" priority="15">
-      <formula>OR(AG25="Practices",AG25="Priorities")</formula>
+  <conditionalFormatting sqref="AD22:AE47 AD149:AE164">
+    <cfRule type="expression" dxfId="6" priority="14">
+      <formula>OR(AD22="Core",AD22="Incidental",AD22="Key Accomplishments")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI166:AI167">
-    <cfRule type="expression" dxfId="8" priority="11">
-      <formula>OR(AI166="Core",AI166="Incidental")</formula>
+  <conditionalFormatting sqref="AD20:AG20 AD165:AG167">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>AND($AE21="",$AE20&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI167">
-    <cfRule type="expression" dxfId="7" priority="10">
-      <formula>OR(AI167="Practices",AI167="Priorities")</formula>
+  <conditionalFormatting sqref="AD168:AG168">
+    <cfRule type="expression" dxfId="4" priority="20">
+      <formula>AND($AE20="",$AE168&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:A19 A24:A1048576">
-    <cfRule type="expression" dxfId="6" priority="9">
-      <formula>A3=""</formula>
+  <conditionalFormatting sqref="AG20 AG165:AG168">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>$AE20&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A24:A28">
-    <cfRule type="expression" dxfId="5" priority="8">
-      <formula>B24=""</formula>
+  <conditionalFormatting sqref="AG22:AG1048576">
+    <cfRule type="expression" dxfId="2" priority="15">
+      <formula>OR(AG22="  Practices",AG22="  Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24:G29">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>LEN($B24)&gt;112</formula>
+  <conditionalFormatting sqref="AI163:AI164">
+    <cfRule type="expression" dxfId="1" priority="11">
+      <formula>OR(AI163="Core",AI163="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD23:AG23 AD168:AG170">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>AND($AE24="",$AE23&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD23 AD168:AD171">
-    <cfRule type="expression" dxfId="2" priority="2">
-      <formula>$AE23&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG23 AG168:AG171">
-    <cfRule type="expression" dxfId="1" priority="1">
-      <formula>$AE23&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD171:AG171">
-    <cfRule type="expression" dxfId="0" priority="20">
-      <formula>AND($AE23="",$AE171&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="AI164">
+    <cfRule type="expression" dxfId="0" priority="10">
+      <formula>OR(AI164="Practices",AI164="Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3137,17 +3067,17 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
         <v>56</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>57</v>
-      </c>
-      <c r="C1" t="s">
-        <v>58</v>
       </c>
       <c r="E1" t="str">
         <f ca="1">_xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[first])&amp;" " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[last])</f>
-        <v>Phoenix West</v>
+        <v>Finley Phillips</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.45">
@@ -3156,10 +3086,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.45">
@@ -3168,10 +3098,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
@@ -3180,10 +3110,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.45">
@@ -3192,10 +3122,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
@@ -3204,10 +3134,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.45">
@@ -3216,10 +3146,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
@@ -3228,10 +3158,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.45">
@@ -3240,10 +3170,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
@@ -3252,10 +3182,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.45">
@@ -3264,10 +3194,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.45">
@@ -3276,10 +3206,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.45">
@@ -3288,10 +3218,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.45">
@@ -3300,10 +3230,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.45">
@@ -3312,10 +3242,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C15" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.45">
@@ -3324,10 +3254,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.45">
@@ -3336,10 +3266,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.45">
@@ -3348,10 +3278,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.45">
@@ -3360,10 +3290,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C19" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.45">
@@ -3372,10 +3302,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.45">
@@ -3384,10 +3314,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.45">
@@ -3396,10 +3326,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C22" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
@@ -3408,10 +3338,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C23" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.45">
@@ -3420,10 +3350,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.45">
@@ -3432,10 +3362,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.45">
@@ -3444,10 +3374,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.45">
@@ -3456,10 +3386,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.45">
@@ -3468,10 +3398,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.45">
@@ -3480,10 +3410,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.45">
@@ -3492,10 +3422,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.45">
@@ -3504,10 +3434,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.45">
@@ -3516,10 +3446,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.45">
@@ -3528,10 +3458,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.45">
@@ -3540,10 +3470,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.45">
@@ -3552,10 +3482,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.45">
@@ -3564,10 +3494,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.45">
@@ -3576,10 +3506,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.45">
@@ -3588,10 +3518,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C38" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.45">
@@ -3600,10 +3530,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C39" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.45">
@@ -3612,10 +3542,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.45">
@@ -3624,10 +3554,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C41" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.45">
@@ -3636,10 +3566,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C42" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.45">
@@ -3648,10 +3578,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C43" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.45">
@@ -3660,10 +3590,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.45">
@@ -3672,10 +3602,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.45">
@@ -3684,10 +3614,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.45">
@@ -3696,10 +3626,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.45">
@@ -3708,10 +3638,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C48" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.45">
@@ -3720,10 +3650,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.45">
@@ -3732,10 +3662,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C50" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.45">
@@ -3744,10 +3674,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.45">
@@ -3756,10 +3686,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C52" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.45">
@@ -3768,10 +3698,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.45">
@@ -3780,10 +3710,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C54" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.45">
@@ -3792,10 +3722,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.45">
@@ -3804,10 +3734,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C56" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.45">
@@ -3816,10 +3746,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.45">
@@ -3828,10 +3758,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.45">
@@ -3840,10 +3770,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C59" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.45">
@@ -3852,10 +3782,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C60" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.45">
@@ -3864,10 +3794,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C61" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.45">
@@ -3876,10 +3806,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C62" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.45">
@@ -3888,10 +3818,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C63" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.45">
@@ -3900,10 +3830,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C64" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.45">
@@ -3912,10 +3842,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C65" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.45">
@@ -3924,10 +3854,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C66" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.45">
@@ -3936,10 +3866,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.45">
@@ -3951,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.45">
@@ -3960,10 +3890,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C69" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.45">
@@ -3972,10 +3902,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.45">
@@ -3984,10 +3914,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C71" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.45">
@@ -3996,10 +3926,10 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C72" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.45">
@@ -4008,10 +3938,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C73" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.45">
@@ -4020,10 +3950,10 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C74" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.45">
@@ -4032,10 +3962,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C75" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.45">
@@ -4044,10 +3974,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C76" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.45">
@@ -4056,10 +3986,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C77" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.45">
@@ -4068,10 +3998,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C78" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.45">
@@ -4080,10 +4010,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C79" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.45">
@@ -4092,10 +4022,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C80" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.45">
@@ -4104,10 +4034,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.45">
@@ -4116,10 +4046,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C82" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.45">
@@ -4128,10 +4058,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C83" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.45">
@@ -4140,10 +4070,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.45">
@@ -4152,10 +4082,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.45">
@@ -4164,10 +4094,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C86" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.45">
@@ -4176,10 +4106,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C87" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.45">
@@ -4188,10 +4118,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.45">
@@ -4200,10 +4130,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C89" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.45">
@@ -4212,10 +4142,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.45">
@@ -4224,10 +4154,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C91" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.45">
@@ -4236,10 +4166,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C92" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.45">
@@ -4248,10 +4178,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C93" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.45">
@@ -4260,10 +4190,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C94" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.45">
@@ -4272,10 +4202,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C95" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.45">
@@ -4284,10 +4214,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C96" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.45">
@@ -4296,10 +4226,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C97" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.45">
@@ -4308,10 +4238,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C98" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.45">
@@ -4320,10 +4250,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C99" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.45">
@@ -4332,10 +4262,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C100" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.45">
@@ -4344,10 +4274,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C101" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.45">
@@ -4356,10 +4286,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C102" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.45">
@@ -4368,10 +4298,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C103" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.45">
@@ -4380,10 +4310,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C104" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.45">
@@ -4392,10 +4322,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C105" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.45">
@@ -4404,10 +4334,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C106" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.45">
@@ -4416,10 +4346,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C107" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.45">
@@ -4428,10 +4358,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C108" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.45">
@@ -4440,10 +4370,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.45">
@@ -4452,10 +4382,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C110" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.45">
@@ -4464,10 +4394,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C111" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.45">
@@ -4476,10 +4406,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C112" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.45">
@@ -4488,10 +4418,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C113" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.45">
@@ -4500,10 +4430,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C114" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.45">
@@ -4512,10 +4442,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.45">
@@ -4524,10 +4454,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C116" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.45">
@@ -4536,10 +4466,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C117" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.45">
@@ -4551,7 +4481,7 @@
         <v>1</v>
       </c>
       <c r="C118" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.45">
@@ -4560,10 +4490,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C119" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.45">
@@ -4572,10 +4502,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C120" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.45">
@@ -4584,10 +4514,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C121" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.45">
@@ -4596,10 +4526,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C122" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.45">
@@ -4608,10 +4538,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C123" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.45">
@@ -4620,10 +4550,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C124" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.45">
@@ -4632,10 +4562,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C125" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.45">
@@ -4644,10 +4574,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C126" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.45">
@@ -4659,7 +4589,7 @@
         <v>1</v>
       </c>
       <c r="C127" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.45">
@@ -4668,10 +4598,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C128" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.45">
@@ -4680,10 +4610,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C129" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.45">
@@ -4692,10 +4622,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.45">
@@ -4704,10 +4634,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C131" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.45">
@@ -4716,10 +4646,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C132" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.45">
@@ -4728,10 +4658,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C133" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.45">
@@ -4740,10 +4670,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C134" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.45">
@@ -4752,10 +4682,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C135" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/careerstop.xlsx
+++ b/careerstop.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galja\pgaljan.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED2A44B5-1298-4724-A6A9-253030ADA587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038209E8-FA6F-4D1B-B4AF-68B42B5A45C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28898" yWindow="-37" windowWidth="28996" windowHeight="15675" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
   </bookViews>
   <sheets>
     <sheet name="careerstop" sheetId="1" r:id="rId1"/>
-    <sheet name="names" sheetId="2" r:id="rId2"/>
+    <sheet name="output" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="randomName">_xlfn.XLOOKUP(RANDBETWEEN(1,20),names[index],names[first]) &amp; " " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,20),names[index],names[last])</definedName>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="309">
   <si>
     <t>Tools</t>
   </si>
@@ -826,75 +826,9 @@
     <t>Accomplishments (&lt;=4)</t>
   </si>
   <si>
-    <t>Paul Galjan</t>
-  </si>
-  <si>
-    <t>Product Manager</t>
-  </si>
-  <si>
-    <t>Dell Technologies</t>
-  </si>
-  <si>
-    <t>Hopkinton, MA</t>
-  </si>
-  <si>
-    <t>Infrastructure Automation</t>
-  </si>
-  <si>
     <t>Oct 2023</t>
   </si>
   <si>
-    <t>current</t>
-  </si>
-  <si>
-    <t>Power Platform</t>
-  </si>
-  <si>
-    <t>Markdown</t>
-  </si>
-  <si>
-    <t>Drawio</t>
-  </si>
-  <si>
-    <t>VSCode</t>
-  </si>
-  <si>
-    <t>Confluence</t>
-  </si>
-  <si>
-    <t>PowerPoint</t>
-  </si>
-  <si>
-    <t>Jira</t>
-  </si>
-  <si>
-    <t>Jira Align</t>
-  </si>
-  <si>
-    <t>Miro</t>
-  </si>
-  <si>
-    <t>CoPilot</t>
-  </si>
-  <si>
-    <t>Analyst</t>
-  </si>
-  <si>
-    <t>Data Collection</t>
-  </si>
-  <si>
-    <t>Data Classification</t>
-  </si>
-  <si>
-    <t>Analysis</t>
-  </si>
-  <si>
-    <t>Communication</t>
-  </si>
-  <si>
-    <t>Impact Assessment</t>
-  </si>
-  <si>
     <t>Product Planning</t>
   </si>
   <si>
@@ -907,95 +841,161 @@
     <t>Core Team Support</t>
   </si>
   <si>
-    <t>Data Visualization</t>
-  </si>
-  <si>
-    <t>API Defintiion</t>
-  </si>
-  <si>
-    <t>Data Modeling</t>
-  </si>
-  <si>
-    <t>Market Analysis</t>
-  </si>
-  <si>
-    <t>Extract/Transform/Load (ETL)</t>
-  </si>
-  <si>
-    <t>System Architecture</t>
-  </si>
-  <si>
-    <t>Agile Development</t>
-  </si>
-  <si>
-    <t>Value Pricing</t>
-  </si>
-  <si>
-    <t>Hypothesis Testing</t>
-  </si>
-  <si>
-    <t>Project Management</t>
-  </si>
-  <si>
-    <t>Timeboxed Planning</t>
-  </si>
-  <si>
-    <t>Visual Storytelling</t>
-  </si>
-  <si>
-    <t>Quantification</t>
-  </si>
-  <si>
-    <t>Frameworks</t>
-  </si>
-  <si>
-    <t>Structured Analysis</t>
-  </si>
-  <si>
-    <t>Work Breakdown</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>Process</t>
-  </si>
-  <si>
-    <t>Clarity</t>
-  </si>
-  <si>
-    <t>Consistency</t>
-  </si>
-  <si>
-    <t>Community</t>
-  </si>
-  <si>
-    <t>Copy/Paste below as picture</t>
-  </si>
-  <si>
-    <t>Streamlined UI/API definition handoff with UI Mockup-as-code initiative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Standardized Dell ISG 2-year software lifecycle policy, replacing fragmented product cycles with predictable enterprise planning.  </t>
-  </si>
-  <si>
-    <t>Created constent data model for representation of Dell and 3rd party infrastructure assets in Dell Automation Platform</t>
-  </si>
-  <si>
-    <t>Created consistent project management consumption method to naviagte the transitionbetween project management platforms and approaches</t>
-  </si>
-  <si>
-    <t>Dell Automation Platform - specializing in TOSCA-based declarative automation solutions with hybrid imperative capabilities, serving enterprise clients through agile development methodologies and related optimization.</t>
+    <t>PowerBI</t>
+  </si>
+  <si>
+    <t>Oct 2019</t>
+  </si>
+  <si>
+    <t>Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</t>
+  </si>
+  <si>
+    <t>Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</t>
+  </si>
+  <si>
+    <t>Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</t>
+  </si>
+  <si>
+    <t>Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</t>
+  </si>
+  <si>
+    <t>Avery Taylor</t>
+  </si>
+  <si>
+    <t>P&amp;L Management</t>
+  </si>
+  <si>
+    <t>Staff Training &amp; Development</t>
+  </si>
+  <si>
+    <t>Merchandising Strategy</t>
+  </si>
+  <si>
+    <t>Supply Chain Coordination</t>
+  </si>
+  <si>
+    <t>Customer Service Management</t>
+  </si>
+  <si>
+    <t>Compliance Management</t>
+  </si>
+  <si>
+    <t>Multi-location Oversight</t>
+  </si>
+  <si>
+    <t>Crisis Management</t>
+  </si>
+  <si>
+    <t>Seasonal Planning</t>
+  </si>
+  <si>
+    <t>Budget Forecasting</t>
+  </si>
+  <si>
+    <t>Daily Standups</t>
+  </si>
+  <si>
+    <t>Performance Dashboards</t>
+  </si>
+  <si>
+    <t>Mystery Shopping</t>
+  </si>
+  <si>
+    <t>Staff Cross-training</t>
+  </si>
+  <si>
+    <t>Standard Operating Procedures</t>
+  </si>
+  <si>
+    <t>Customer Satisfaction</t>
+  </si>
+  <si>
+    <t>Operational Efficiency</t>
+  </si>
+  <si>
+    <t>Team Development</t>
+  </si>
+  <si>
+    <t>Brand Consistency</t>
+  </si>
+  <si>
+    <t>Safety &amp; Compliance</t>
+  </si>
+  <si>
+    <t>Community Engagement</t>
+  </si>
+  <si>
+    <t>Profitability</t>
+  </si>
+  <si>
+    <t>Square POS</t>
+  </si>
+  <si>
+    <t>Shopify</t>
+  </si>
+  <si>
+    <t>NetSuite</t>
+  </si>
+  <si>
+    <t>TradeGecko</t>
+  </si>
+  <si>
+    <t>Deputy</t>
+  </si>
+  <si>
+    <t>Slack</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
+    <t>Zendesk</t>
+  </si>
+  <si>
+    <t>Mailchimp</t>
+  </si>
+  <si>
+    <t>QuickBooks</t>
+  </si>
+  <si>
+    <t>Process Optimization</t>
+  </si>
+  <si>
+    <t>Performance Monitoring</t>
+  </si>
+  <si>
+    <t>Resource Coordination</t>
+  </si>
+  <si>
+    <t>Cross-Functional Coordination</t>
+  </si>
+  <si>
+    <t>Staff Development</t>
+  </si>
+  <si>
+    <t>Operations Specialist</t>
+  </si>
+  <si>
+    <t>Acme Retail</t>
+  </si>
+  <si>
+    <t>Anytown USA</t>
+  </si>
+  <si>
+    <t>Store Manager</t>
+  </si>
+  <si>
+    <t>Retail/Hospitality</t>
+  </si>
+  <si>
+    <t>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1019,15 +1019,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1062,11 +1055,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1285,11 +1273,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1388,9 +1375,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1400,13 +1384,85 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Accent1" xfId="1" builtinId="29"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="22">
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1436,33 +1492,6 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1475,33 +1504,9 @@
       </font>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1537,167 +1542,6 @@
         <b/>
         <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFDAE8FC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1760,23 +1604,23 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>1</xdr:col>
-          <xdr:colOff>22411</xdr:colOff>
-          <xdr:row>28</xdr:row>
-          <xdr:rowOff>39222</xdr:rowOff>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>1109384</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>112057</xdr:rowOff>
         </xdr:from>
         <xdr:to>
-          <xdr:col>13</xdr:col>
-          <xdr:colOff>773206</xdr:colOff>
-          <xdr:row>52</xdr:row>
-          <xdr:rowOff>61634</xdr:rowOff>
+          <xdr:col>15</xdr:col>
+          <xdr:colOff>979395</xdr:colOff>
+          <xdr:row>45</xdr:row>
+          <xdr:rowOff>116821</xdr:rowOff>
         </xdr:to>
         <xdr:pic>
           <xdr:nvPicPr>
-            <xdr:cNvPr id="6" name="Picture 5">
+            <xdr:cNvPr id="3" name="Picture 2">
               <a:extLst>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B29D5E16-BD03-D863-814D-150D7B920569}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79655B18-512D-DCD7-0972-FC64F0126C26}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1784,7 +1628,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="$AD$147:$AI$169" spid="_x0000_s1097"/>
+                  <a14:cameraTool cellRange="output!$G$1:$L$22" spid="_x0000_s1104"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1798,8 +1642,8 @@
           </xdr:blipFill>
           <xdr:spPr bwMode="auto">
             <a:xfrm>
-              <a:off x="1473573" y="5205134"/>
-              <a:ext cx="11939868" cy="4325471"/>
+              <a:off x="4336678" y="4235822"/>
+              <a:ext cx="10319497" cy="3949234"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1845,7 +1689,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}" name="names" displayName="names" ref="A1:C135" totalsRowShown="0">
   <autoFilter ref="A1:C135" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="39">
+    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="21">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2FBF4AE8-10BE-49DC-A08D-B377AD3CB245}" name="first"/>
@@ -2172,18 +2016,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3348163-AFAC-4B5E-B6D7-A630EDC47AB4}">
-  <dimension ref="A2:AI168"/>
+  <dimension ref="A1:AB147"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.265625" customWidth="1"/>
-    <col min="3" max="3" width="3.46484375" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="3.86328125" customWidth="1"/>
-    <col min="7" max="7" width="25.86328125" customWidth="1"/>
-    <col min="8" max="8" width="3.46484375" customWidth="1"/>
-    <col min="9" max="9" width="24.6640625" customWidth="1"/>
-    <col min="10" max="10" width="3.86328125" customWidth="1"/>
+    <col min="2" max="2" width="23.73046875" customWidth="1"/>
+    <col min="3" max="3" width="1.06640625" customWidth="1"/>
+    <col min="4" max="4" width="23.73046875" customWidth="1"/>
+    <col min="5" max="5" width="3.46484375" customWidth="1"/>
+    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.86328125" customWidth="1"/>
+    <col min="9" max="9" width="25.86328125" customWidth="1"/>
+    <col min="10" max="10" width="3.46484375" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="25.86328125" customWidth="1"/>
     <col min="13" max="13" width="3.86328125" customWidth="1"/>
@@ -2199,132 +2043,206 @@
     <col min="36" max="36" width="24.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" ht="25.5" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="6"/>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="20" t="s">
+        <v>298</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6" t="b">
+        <f>IF(L2="","",ISEVEN(ROW()))</f>
+        <v>1</v>
+      </c>
+      <c r="L2" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="M2" s="6"/>
+      <c r="N2" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="O2" s="6"/>
+      <c r="P2" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20" t="s">
+        <v>256</v>
+      </c>
+      <c r="F3" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="b">
+        <f t="shared" ref="K3:K17" si="0">IF(L3="","",ISEVEN(ROW()))</f>
         <v>0</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A4" s="5" t="s">
+      <c r="L3" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="M3" s="6"/>
+      <c r="N3" s="20" t="s">
+        <v>277</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="20" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20" t="s">
+        <v>257</v>
+      </c>
+      <c r="F4" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="D4" s="22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>252</v>
-      </c>
-      <c r="F4" s="6"/>
       <c r="G4" s="20" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="20" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="b">
-        <f>IF(L4="","",ISEVEN(ROW()))</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L4" s="20" t="s">
-        <v>281</v>
+        <v>268</v>
       </c>
       <c r="M4" s="6"/>
       <c r="N4" s="20" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="O4" s="6"/>
       <c r="P4" s="20" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>256</v>
-      </c>
-      <c r="D5" s="22" t="b">
+        <v>13</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="20" t="s">
+        <v>258</v>
+      </c>
+      <c r="F5" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>261</v>
-      </c>
-      <c r="F5" s="6"/>
       <c r="G5" s="20" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="20" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="b">
-        <f t="shared" ref="K5:K18" si="0">IF(L5="","",ISEVEN(ROW()))</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="M5" s="6"/>
       <c r="N5" s="20" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
       <c r="O5" s="6"/>
       <c r="P5" s="20" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>257</v>
-      </c>
-      <c r="D6" s="22" t="b">
+        <v>14</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="21"/>
+      <c r="D6" s="20"/>
+      <c r="F6" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="20" t="s">
-        <v>262</v>
-      </c>
-      <c r="F6" s="6"/>
       <c r="G6" s="20" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="20" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="b">
@@ -2332,140 +2250,113 @@
         <v>1</v>
       </c>
       <c r="L6" s="20" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="M6" s="6"/>
       <c r="N6" s="20" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="O6" s="6"/>
       <c r="P6" s="20" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" s="22" t="b">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="7"/>
+      <c r="F7" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="20" t="s">
-        <v>263</v>
-      </c>
-      <c r="F7" s="6"/>
       <c r="G7" s="20" t="s">
-        <v>275</v>
+        <v>252</v>
       </c>
       <c r="H7" s="6"/>
-      <c r="I7" s="20" t="s">
-        <v>280</v>
-      </c>
+      <c r="I7" s="20"/>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7" s="20" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="M7" s="6"/>
-      <c r="N7" s="20" t="s">
-        <v>294</v>
-      </c>
+      <c r="N7" s="20"/>
       <c r="O7" s="6"/>
       <c r="P7" s="20" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A8" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>260</v>
-      </c>
-      <c r="D8" s="22" t="b">
+      <c r="A8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="F8" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="20" t="s">
-        <v>264</v>
-      </c>
-      <c r="F8" s="6"/>
       <c r="G8" s="20" t="s">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="H8" s="6"/>
-      <c r="I8" s="20"/>
+      <c r="I8" s="7"/>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L8" s="20" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="M8" s="6"/>
-      <c r="N8" s="20" t="s">
-        <v>295</v>
-      </c>
+      <c r="N8" s="20"/>
       <c r="O8" s="6"/>
       <c r="P8" s="20" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>255</v>
-      </c>
-      <c r="D9" s="22" t="b">
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="F9" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="20" t="s">
-        <v>265</v>
-      </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20" t="s">
+        <v>259</v>
+      </c>
       <c r="H9" s="6"/>
-      <c r="I9" s="7"/>
+      <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L9" s="20" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="M9" s="6"/>
-      <c r="N9" s="20" t="s">
-        <v>296</v>
-      </c>
+      <c r="N9" s="20"/>
       <c r="O9" s="6"/>
-      <c r="P9" s="20" t="s">
-        <v>302</v>
-      </c>
+      <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>258</v>
-      </c>
-      <c r="D10" s="22" t="b">
+      <c r="F10" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="20" t="s">
+        <v>294</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
@@ -2474,23 +2365,20 @@
         <v>1</v>
       </c>
       <c r="L10" s="20" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="M10" s="6"/>
-      <c r="N10" s="20"/>
+      <c r="N10" s="7"/>
       <c r="O10" s="6"/>
-      <c r="P10" s="20"/>
+      <c r="P10" s="7"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B11" s="25"/>
-      <c r="D11" s="22" t="b">
+      <c r="F11" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="20" t="s">
-        <v>267</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
+      <c r="G11" s="20" t="s">
+        <v>295</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
@@ -2499,95 +2387,73 @@
         <v>0</v>
       </c>
       <c r="L11" s="20" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="M11" s="6"/>
-      <c r="N11" s="20"/>
+      <c r="N11" s="6"/>
       <c r="O11" s="6"/>
-      <c r="P11" s="20"/>
+      <c r="P11" s="6"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B12" s="25"/>
-      <c r="D12" s="22" t="b">
+      <c r="F12" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="20" t="s">
-        <v>268</v>
-      </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="G12" s="20" t="s">
+        <v>296</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="K12" s="6" t="b">
+      <c r="K12" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L12" s="20" t="s">
-        <v>288</v>
-      </c>
+        <v/>
+      </c>
+      <c r="L12" s="20"/>
       <c r="M12" s="6"/>
-      <c r="N12" s="7"/>
+      <c r="N12" s="6"/>
       <c r="O12" s="6"/>
-      <c r="P12" s="7"/>
+      <c r="P12" s="6"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B13" s="25"/>
-      <c r="D13" s="22" t="b">
+      <c r="F13" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="20" t="s">
-        <v>269</v>
-      </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
+      <c r="G13" s="20" t="s">
+        <v>297</v>
+      </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="6" t="b">
+      <c r="K13" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L13" s="20" t="s">
-        <v>289</v>
-      </c>
+        <v/>
+      </c>
+      <c r="L13" s="20"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B14" s="25"/>
-      <c r="D14" s="22" t="b">
+      <c r="F14" s="22" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="20" t="s">
-        <v>270</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
-      <c r="K14" s="6" t="b">
+      <c r="K14" s="6" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="L14" s="20" t="s">
-        <v>290</v>
-      </c>
+        <v/>
+      </c>
+      <c r="L14" s="20"/>
       <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="D15" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="44"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -2595,34 +2461,31 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="20"/>
+      <c r="L15" s="45"/>
       <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="D16" s="22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="G16" s="20"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
-      <c r="K16" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L16" s="20"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="44"/>
       <c r="M16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="E17" s="20"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
@@ -2631,424 +2494,105 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L17" s="27"/>
+      <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A18" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A19" s="24" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A20" s="24" t="s">
-        <v>253</v>
-      </c>
+      <c r="A20" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" s="26" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>305</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" s="26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>306</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>304</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A24" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A25" s="26"/>
-      <c r="B25" s="6"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="B28" s="44" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="146" spans="30:33" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="147" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD147" s="37" t="str">
-        <f>B3&amp; " ("&amp;B10&amp;")"</f>
-        <v>Paul Galjan (Infrastructure Automation)</v>
-      </c>
-      <c r="AE147" s="38" t="str">
-        <f>B9&amp;" with "&amp;B5&amp;" ("&amp;B6&amp;")"</f>
-        <v>Product Manager with Dell Technologies (Hopkinton, MA)</v>
-      </c>
-      <c r="AF147" s="39"/>
-      <c r="AG147" s="40" t="str">
-        <f>B7&amp;" - "&amp;B8</f>
-        <v>Oct 2023 - current</v>
-      </c>
-    </row>
-    <row r="148" spans="30:33" ht="30" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="AD148" s="41" t="str">
-        <f>B18</f>
-        <v>Dell Automation Platform - specializing in TOSCA-based declarative automation solutions with hybrid imperative capabilities, serving enterprise clients through agile development methodologies and related optimization.</v>
-      </c>
-      <c r="AE148" s="42"/>
-      <c r="AF148" s="42"/>
-      <c r="AG148" s="43"/>
-    </row>
-    <row r="149" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD149" s="11" t="str" cm="1">
-        <f t="array" ref="AD149:AD162">_xlfn.VSTACK(
-"Tools",
-"Core","  • "&amp;_xlfn._xlws.FILTER(E3:E18,D3:D18=TRUE),
-"Incidental","  • "&amp;_xlfn._xlws.FILTER(E3:E18,(D3:D18=FALSE)*(E3:E18&lt;&gt;"")))</f>
-        <v>Tools</v>
-      </c>
-      <c r="AE149" s="10" t="str" cm="1">
-        <f t="array" ref="AE149:AE155">_xlfn.VSTACK("Profession",B4,"  • "&amp;_xlfn._xlws.FILTER(G4:G9,G4:G9&lt;&gt;""))</f>
-        <v>Profession</v>
-      </c>
-      <c r="AF149" s="9" t="str" cm="1">
-        <f t="array" ref="AF149:AF155">_xlfn.VSTACK("Job",B9,B10,"  • "&amp;_xlfn._xlws.FILTER(I4:I8,I4:I8&lt;&gt;""))</f>
-        <v>Job</v>
-      </c>
-      <c r="AG149" s="36" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="150" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD150" s="30" t="str">
-        <v>Core</v>
-      </c>
-      <c r="AE150" s="12" t="str">
-        <v>Analyst</v>
-      </c>
-      <c r="AF150" s="12" t="str">
-        <v>Product Manager</v>
-      </c>
-      <c r="AG150" s="31" t="str" cm="1">
-        <f t="array" ref="AG150:AG163">_xlfn.VSTACK(
-  "  Practices","  • "&amp;_xlfn._xlws.FILTER(N4:N18,N4:N18&lt;&gt;""),
-"  Priorities","  • "&amp;_xlfn._xlws.FILTER(P4:P18,P4:P18&lt;&gt;""))</f>
-        <v xml:space="preserve">  Practices</v>
-      </c>
-    </row>
-    <row r="151" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD151" s="32" t="str">
-        <v xml:space="preserve">  • Excel</v>
-      </c>
-      <c r="AE151" s="13" t="str">
-        <v xml:space="preserve">  • Data Collection</v>
-      </c>
-      <c r="AF151" s="15" t="str">
-        <v>Infrastructure Automation</v>
-      </c>
-      <c r="AG151" s="13" t="str">
-        <v xml:space="preserve">  • Timeboxed Planning</v>
-      </c>
-    </row>
-    <row r="152" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD152" s="32" t="str">
-        <v xml:space="preserve">  • Power Platform</v>
-      </c>
-      <c r="AE152" s="13" t="str">
-        <v xml:space="preserve">  • Data Classification</v>
-      </c>
-      <c r="AF152" s="13" t="str">
-        <v xml:space="preserve">  • Product Planning</v>
-      </c>
-      <c r="AG152" s="13" t="str">
-        <v xml:space="preserve">  • Visual Storytelling</v>
-      </c>
-    </row>
-    <row r="153" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD153" s="32" t="str">
-        <v xml:space="preserve">  • Markdown</v>
-      </c>
-      <c r="AE153" s="13" t="str">
-        <v xml:space="preserve">  • Analysis</v>
-      </c>
-      <c r="AF153" s="13" t="str">
-        <v xml:space="preserve">  • Requirements Development</v>
-      </c>
-      <c r="AG153" s="13" t="str">
-        <v xml:space="preserve">  • Quantification</v>
-      </c>
-    </row>
-    <row r="154" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD154" s="32" t="str">
-        <v xml:space="preserve">  • Drawio</v>
-      </c>
-      <c r="AE154" s="13" t="str">
-        <v xml:space="preserve">  • Communication</v>
-      </c>
-      <c r="AF154" s="13" t="str">
-        <v xml:space="preserve">  • Development Execution</v>
-      </c>
-      <c r="AG154" s="13" t="str">
-        <v xml:space="preserve">  • Frameworks</v>
-      </c>
-    </row>
-    <row r="155" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD155" s="32" t="str">
-        <v xml:space="preserve">  • VSCode</v>
-      </c>
-      <c r="AE155" s="13" t="str">
-        <v xml:space="preserve">  • Impact Assessment</v>
-      </c>
-      <c r="AF155" s="13" t="str">
-        <v xml:space="preserve">  • Core Team Support</v>
-      </c>
-      <c r="AG155" s="29" t="str">
-        <v xml:space="preserve">  • Structured Analysis</v>
-      </c>
-    </row>
-    <row r="156" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD156" s="32" t="str">
-        <v>Incidental</v>
-      </c>
-      <c r="AE156" s="14"/>
-      <c r="AF156" s="16"/>
-      <c r="AG156" s="13" t="str">
-        <v xml:space="preserve">  • Work Breakdown</v>
-      </c>
-    </row>
-    <row r="157" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD157" s="33" t="str">
-        <v xml:space="preserve">  • Confluence</v>
-      </c>
-      <c r="AE157" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF157" s="34"/>
-      <c r="AG157" s="13" t="str">
-        <v xml:space="preserve">  Priorities</v>
-      </c>
-    </row>
-    <row r="158" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD158" s="33" t="str">
-        <v xml:space="preserve">  • PowerPoint</v>
-      </c>
-      <c r="AE158" s="28" t="str" cm="1">
-        <f t="array" ref="AE158:AF163">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
-" • "&amp;_xlfn._xlws.FILTER(L4:L18,K4:K18=TRUE),
-" • "&amp;_xlfn._xlws.FILTER(L4:L18,(K4:K18=FALSE)*(L4:L18&lt;&gt;""))),"")),"")</f>
-        <v xml:space="preserve"> • Data Visualization</v>
-      </c>
-      <c r="AF158" s="28" t="str">
-        <v xml:space="preserve"> • API Defintiion</v>
-      </c>
-      <c r="AG158" s="13" t="str">
-        <v xml:space="preserve">  • Purpose</v>
-      </c>
-    </row>
-    <row r="159" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD159" s="33" t="str">
-        <v xml:space="preserve">  • Jira</v>
-      </c>
-      <c r="AE159" s="28" t="str">
-        <v xml:space="preserve"> • Data Modeling</v>
-      </c>
-      <c r="AF159" s="28" t="str">
-        <v xml:space="preserve"> • Market Analysis</v>
-      </c>
-      <c r="AG159" s="13" t="str">
-        <v xml:space="preserve">  • Efficiency</v>
-      </c>
-    </row>
-    <row r="160" spans="30:33" x14ac:dyDescent="0.45">
-      <c r="AD160" s="33" t="str">
-        <v xml:space="preserve">  • Jira Align</v>
-      </c>
-      <c r="AE160" s="28" t="str">
-        <v xml:space="preserve"> • Extract/Transform/Load (ETL)</v>
-      </c>
-      <c r="AF160" s="28" t="str">
-        <v xml:space="preserve"> • System Architecture</v>
-      </c>
-      <c r="AG160" s="13" t="str">
-        <v xml:space="preserve">  • Process</v>
-      </c>
-    </row>
-    <row r="161" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD161" s="33" t="str">
-        <v xml:space="preserve">  • Miro</v>
-      </c>
-      <c r="AE161" s="28" t="str">
-        <v xml:space="preserve"> • Agile Development</v>
-      </c>
-      <c r="AF161" s="28" t="str">
-        <v xml:space="preserve"> • Market Analysis</v>
-      </c>
-      <c r="AG161" s="13" t="str">
-        <v xml:space="preserve">  • Clarity</v>
-      </c>
-    </row>
-    <row r="162" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD162" s="33" t="str">
-        <v xml:space="preserve">  • CoPilot</v>
-      </c>
-      <c r="AE162" s="28" t="str">
-        <v xml:space="preserve"> • Value Pricing</v>
-      </c>
-      <c r="AF162" s="28" t="str">
-        <v xml:space="preserve"> • Hypothesis Testing</v>
-      </c>
-      <c r="AG162" s="13" t="str">
-        <v xml:space="preserve">  • Consistency</v>
-      </c>
-      <c r="AI162" s="17" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="163" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD163" s="33"/>
-      <c r="AE163" s="28" t="str">
-        <v xml:space="preserve"> • Project Management</v>
-      </c>
-      <c r="AF163" s="28" t="str">
-        <v/>
-      </c>
-      <c r="AG163" s="13" t="str">
-        <v xml:space="preserve">  • Community</v>
-      </c>
-      <c r="AI163" s="18" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="164" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD164" s="16"/>
-      <c r="AE164" s="28"/>
-      <c r="AF164" s="28"/>
-      <c r="AG164" s="13"/>
-      <c r="AI164" s="19" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="165" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AD165" s="35" t="s">
-        <v>62</v>
-      </c>
-      <c r="AE165" t="str" cm="1">
-        <f t="array" ref="AE165:AE168">_xlfn._xlws.FILTER(B21:B25,B21:B25&lt;&gt;"")</f>
-        <v xml:space="preserve">Standardized Dell ISG 2-year software lifecycle policy, replacing fragmented product cycles with predictable enterprise planning.  </v>
-      </c>
-    </row>
-    <row r="166" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE166" t="str">
-        <v>Created constent data model for representation of Dell and 3rd party infrastructure assets in Dell Automation Platform</v>
-      </c>
-    </row>
-    <row r="167" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE167" t="str">
-        <v>Streamlined UI/API definition handoff with UI Mockup-as-code initiative</v>
-      </c>
-    </row>
-    <row r="168" spans="30:35" x14ac:dyDescent="0.45">
-      <c r="AE168" t="str">
-        <v>Created consistent project management consumption method to naviagte the transitionbetween project management platforms and approaches</v>
-      </c>
-    </row>
+      <c r="A24" s="26"/>
+      <c r="B24" s="6"/>
+    </row>
+    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="AD148:AG148"/>
-  </mergeCells>
-  <conditionalFormatting sqref="A21:A1048576 A3:A18">
-    <cfRule type="expression" dxfId="12" priority="9">
-      <formula>A3=""</formula>
+  <conditionalFormatting sqref="A20:A1048576 A1:A9 F1:F9 A15:A17">
+    <cfRule type="expression" dxfId="20" priority="9">
+      <formula>A1=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A21:A25">
-    <cfRule type="expression" dxfId="11" priority="8">
-      <formula>B21=""</formula>
+  <conditionalFormatting sqref="A20:A23">
+    <cfRule type="expression" dxfId="19" priority="8">
+      <formula>B20=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:G26">
-    <cfRule type="expression" dxfId="10" priority="4">
-      <formula>LEN($B21)&gt;149</formula>
+  <conditionalFormatting sqref="B20:I23 B24">
+    <cfRule type="expression" dxfId="18" priority="4">
+      <formula>LEN($B20)&gt;149</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:D16">
-    <cfRule type="expression" dxfId="9" priority="18">
-      <formula>$E4=""</formula>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$G2=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD20 AD165:AD168">
-    <cfRule type="expression" dxfId="8" priority="2">
-      <formula>$AE20&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AD169:AD1048576 AD49:AD145 AD25">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>OR(AD25="Core",AD25="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD22:AD1048576 AG149">
-    <cfRule type="expression" dxfId="7" priority="17">
-      <formula>OR(AD22="Core",AD22="Incidental")</formula>
+  <conditionalFormatting sqref="AD25:AE25">
+    <cfRule type="expression" dxfId="15" priority="14">
+      <formula>OR(AD25="Core",AD25="Incidental",AD25="Key Accomplishments")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD22:AE47 AD149:AE164">
-    <cfRule type="expression" dxfId="6" priority="14">
-      <formula>OR(AD22="Core",AD22="Incidental",AD22="Key Accomplishments")</formula>
+  <conditionalFormatting sqref="AG169:AG1048576 AG49:AG145 AG25">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>OR(AG25="                                     Practices",AG25="                                     Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD20:AG20 AD165:AG167">
-    <cfRule type="expression" dxfId="5" priority="3">
-      <formula>AND($AE21="",$AE20&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="expression" dxfId="13" priority="22">
+      <formula>#REF!=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD168:AG168">
-    <cfRule type="expression" dxfId="4" priority="20">
-      <formula>AND($AE20="",$AE168&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG20 AG165:AG168">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$AE20&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG22:AG1048576">
-    <cfRule type="expression" dxfId="2" priority="15">
-      <formula>OR(AG22="  Practices",AG22="  Priorities")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI163:AI164">
-    <cfRule type="expression" dxfId="1" priority="11">
-      <formula>OR(AI163="Core",AI163="Incidental")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AI164">
-    <cfRule type="expression" dxfId="0" priority="10">
-      <formula>OR(AI164="Practices",AI164="Priorities")</formula>
+  <conditionalFormatting sqref="E24:I25">
+    <cfRule type="expression" dxfId="12" priority="24">
+      <formula>LEN(#REF!)&gt;149</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3059,13 +2603,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175234B1-B47F-451A-9952-E15FBC3697C2}">
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="9.796875" customWidth="1"/>
+    <col min="7" max="10" width="33.265625" customWidth="1"/>
+    <col min="11" max="11" width="1.265625" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -3075,12 +2622,21 @@
       <c r="C1" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="str">
-        <f ca="1">_xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[first])&amp;" " &amp; _xlfn.XLOOKUP(RANDBETWEEN(1,ROWS(names[])),names[index],names[last])</f>
-        <v>Finley Phillips</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G1" s="37" t="str">
+        <f>careerstop!B1&amp; " ("&amp;careerstop!B8&amp;")"</f>
+        <v>Avery Taylor (Retail/Hospitality)</v>
+      </c>
+      <c r="H1" s="38" t="str">
+        <f>careerstop!B7&amp;" with "&amp;careerstop!B3&amp;" ("&amp;careerstop!B4&amp;")"</f>
+        <v>Store Manager with Acme Retail (Anytown USA)</v>
+      </c>
+      <c r="I1" s="39"/>
+      <c r="J1" s="43" t="str">
+        <f>careerstop!B5&amp;" - "&amp;careerstop!B6</f>
+        <v>Oct 2019 - Oct 2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2">
         <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
@@ -3091,8 +2647,15 @@
       <c r="C2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G2" s="40" t="str">
+        <f>careerstop!B17</f>
+        <v>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</v>
+      </c>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="42"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -3103,8 +2666,26 @@
       <c r="C3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G3" s="11" t="str" cm="1">
+        <f t="array" ref="G3:G17">_xlfn.VSTACK(
+"Tools",
+"Core","  • "&amp;_xlfn._xlws.FILTER(careerstop!G1:'careerstop'!G17,careerstop!F1:'careerstop'!F17=TRUE),
+"Incidental","  • "&amp;_xlfn._xlws.FILTER(careerstop!G1:'careerstop'!G17,(careerstop!F1:'careerstop'!F17=FALSE)*(careerstop!G1:'careerstop'!G17&lt;&gt;"")))</f>
+        <v>Tools</v>
+      </c>
+      <c r="H3" s="10" t="str" cm="1">
+        <f t="array" ref="H3:H9">_xlfn.VSTACK("Profession",careerstop!B2,"  • "&amp;_xlfn._xlws.FILTER(careerstop!I2:'careerstop'!I7,careerstop!I2:'careerstop'!I7&lt;&gt;""))</f>
+        <v>Profession</v>
+      </c>
+      <c r="I3" s="9" t="str" cm="1">
+        <f t="array" ref="I3:I9">_xlfn.VSTACK("Job",careerstop!B7,careerstop!B8,"  • "&amp;_xlfn._xlws.FILTER(careerstop!D2:D6,careerstop!D2:D6&lt;&gt;""))</f>
+        <v>Job</v>
+      </c>
+      <c r="J3" s="36" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -3115,8 +2696,23 @@
       <c r="C4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G4" s="30" t="str">
+        <v>Core</v>
+      </c>
+      <c r="H4" s="12" t="str">
+        <v>Operations Specialist</v>
+      </c>
+      <c r="I4" s="12" t="str">
+        <v>Store Manager</v>
+      </c>
+      <c r="J4" s="31" t="str" cm="1">
+        <f t="array" ref="J4:J17">_xlfn.VSTACK(
+  "                                     Practices","  • "&amp;_xlfn._xlws.FILTER(careerstop!N2:'careerstop'!N17,careerstop!N2:'careerstop'!N17&lt;&gt;""),
+"                                     Priorities","  • "&amp;_xlfn._xlws.FILTER(careerstop!P2:'careerstop'!P17,careerstop!P2:'careerstop'!P17&lt;&gt;""))</f>
+        <v xml:space="preserve">                                     Practices</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -3127,8 +2723,20 @@
       <c r="C5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G5" s="32" t="str">
+        <v xml:space="preserve">  • Square POS</v>
+      </c>
+      <c r="H5" s="13" t="str">
+        <v xml:space="preserve">  • Process Optimization</v>
+      </c>
+      <c r="I5" s="15" t="str">
+        <v>Retail/Hospitality</v>
+      </c>
+      <c r="J5" s="13" t="str">
+        <v xml:space="preserve">  • Daily Standups</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -3139,8 +2747,20 @@
       <c r="C6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G6" s="32" t="str">
+        <v xml:space="preserve">  • Shopify</v>
+      </c>
+      <c r="H6" s="13" t="str">
+        <v xml:space="preserve">  • Performance Monitoring</v>
+      </c>
+      <c r="I6" s="13" t="str">
+        <v xml:space="preserve">  • Product Planning</v>
+      </c>
+      <c r="J6" s="13" t="str">
+        <v xml:space="preserve">  • Performance Dashboards</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -3151,8 +2771,20 @@
       <c r="C7" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G7" s="32" t="str">
+        <v xml:space="preserve">  • NetSuite</v>
+      </c>
+      <c r="H7" s="13" t="str">
+        <v xml:space="preserve">  • Resource Coordination</v>
+      </c>
+      <c r="I7" s="13" t="str">
+        <v xml:space="preserve">  • Requirements Development</v>
+      </c>
+      <c r="J7" s="13" t="str">
+        <v xml:space="preserve">  • Mystery Shopping</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -3163,8 +2795,20 @@
       <c r="C8" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G8" s="32" t="str">
+        <v xml:space="preserve">  • TradeGecko</v>
+      </c>
+      <c r="H8" s="13" t="str">
+        <v xml:space="preserve">  • Cross-Functional Coordination</v>
+      </c>
+      <c r="I8" s="13" t="str">
+        <v xml:space="preserve">  • Development Execution</v>
+      </c>
+      <c r="J8" s="13" t="str">
+        <v xml:space="preserve">  • Staff Cross-training</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -3175,8 +2819,20 @@
       <c r="C9" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G9" s="32" t="str">
+        <v xml:space="preserve">  • Deputy</v>
+      </c>
+      <c r="H9" s="13" t="str">
+        <v xml:space="preserve">  • Staff Development</v>
+      </c>
+      <c r="I9" s="13" t="str">
+        <v xml:space="preserve">  • Core Team Support</v>
+      </c>
+      <c r="J9" s="29" t="str">
+        <v xml:space="preserve">  • Standard Operating Procedures</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -3187,8 +2843,16 @@
       <c r="C10" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G10" s="32" t="str">
+        <v xml:space="preserve">  • Excel</v>
+      </c>
+      <c r="H10" s="14"/>
+      <c r="I10" s="16"/>
+      <c r="J10" s="13" t="str">
+        <v xml:space="preserve">                                     Priorities</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -3199,8 +2863,18 @@
       <c r="C11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G11" s="33" t="str">
+        <v xml:space="preserve">  • Slack</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="34"/>
+      <c r="J11" s="13" t="str">
+        <v xml:space="preserve">  • Customer Satisfaction</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -3211,8 +2885,23 @@
       <c r="C12" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G12" s="33" t="str">
+        <v>Incidental</v>
+      </c>
+      <c r="H12" s="28" t="str" cm="1">
+        <f t="array" ref="H12:I16">IFERROR(_xlfn.VSTACK(IFERROR(_xlfn.HSTACK(
+" • "&amp;_xlfn._xlws.FILTER(careerstop!L2:'careerstop'!L17,careerstop!K2:'careerstop'!K17=TRUE),
+" • "&amp;_xlfn._xlws.FILTER(careerstop!L2:'careerstop'!L17,(careerstop!K2:'careerstop'!K17=FALSE)*(careerstop!L2:'careerstop'!L17&lt;&gt;""))),"")),"")</f>
+        <v xml:space="preserve"> • P&amp;L Management</v>
+      </c>
+      <c r="I12" s="28" t="str">
+        <v xml:space="preserve"> • Staff Training &amp; Development</v>
+      </c>
+      <c r="J12" s="13" t="str">
+        <v xml:space="preserve">  • Operational Efficiency</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -3223,8 +2912,20 @@
       <c r="C13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G13" s="33" t="str">
+        <v xml:space="preserve">  • PowerBI</v>
+      </c>
+      <c r="H13" s="28" t="str">
+        <v xml:space="preserve"> • Merchandising Strategy</v>
+      </c>
+      <c r="I13" s="28" t="str">
+        <v xml:space="preserve"> • Supply Chain Coordination</v>
+      </c>
+      <c r="J13" s="13" t="str">
+        <v xml:space="preserve">  • Team Development</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -3235,8 +2936,20 @@
       <c r="C14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G14" s="33" t="str">
+        <v xml:space="preserve">  • Salesforce</v>
+      </c>
+      <c r="H14" s="28" t="str">
+        <v xml:space="preserve"> • Customer Service Management</v>
+      </c>
+      <c r="I14" s="28" t="str">
+        <v xml:space="preserve"> • Compliance Management</v>
+      </c>
+      <c r="J14" s="13" t="str">
+        <v xml:space="preserve">  • Brand Consistency</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -3247,8 +2960,20 @@
       <c r="C15" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="G15" s="33" t="str">
+        <v xml:space="preserve">  • Zendesk</v>
+      </c>
+      <c r="H15" s="28" t="str">
+        <v xml:space="preserve"> • Multi-location Oversight</v>
+      </c>
+      <c r="I15" s="28" t="str">
+        <v xml:space="preserve"> • Crisis Management</v>
+      </c>
+      <c r="J15" s="13" t="str">
+        <v xml:space="preserve">  • Safety &amp; Compliance</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3259,8 +2984,23 @@
       <c r="C16" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G16" s="33" t="str">
+        <v xml:space="preserve">  • Mailchimp</v>
+      </c>
+      <c r="H16" s="28" t="str">
+        <v xml:space="preserve"> • Seasonal Planning</v>
+      </c>
+      <c r="I16" s="28" t="str">
+        <v xml:space="preserve"> • Budget Forecasting</v>
+      </c>
+      <c r="J16" s="13" t="str">
+        <v xml:space="preserve">  • Community Engagement</v>
+      </c>
+      <c r="L16" s="17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3271,8 +3011,19 @@
       <c r="C17" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G17" s="33" t="str">
+        <v xml:space="preserve">  • QuickBooks</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="13" t="str">
+        <v xml:space="preserve">  • Profitability</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3283,8 +3034,15 @@
       <c r="C18" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G18" s="16"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="13"/>
+      <c r="L18" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3295,8 +3053,17 @@
       <c r="C19" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G19" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="28" t="str" cm="1">
+        <f t="array" ref="H19:H22">" • "&amp;_xlfn._xlws.FILTER(careerstop!B20:'careerstop'!B25,careerstop!B20:'careerstop'!B25&lt;&gt;"")</f>
+        <v xml:space="preserve"> • Increased store profitability by 23% through optimized inventory turnover and staff scheduling efficiency</v>
+      </c>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3307,8 +3074,14 @@
       <c r="C20" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G20" s="28"/>
+      <c r="H20" s="28" t="str">
+        <v xml:space="preserve"> • Reduced employee turnover from 45% to 18% via enhanced training programs and performance incentive structure</v>
+      </c>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3319,8 +3092,14 @@
       <c r="C21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G21" s="28"/>
+      <c r="H21" s="28" t="str">
+        <v xml:space="preserve"> • Implemented customer loyalty program driving 15% increase in repeat purchase rate and $180K additional revenue</v>
+      </c>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3331,8 +3110,14 @@
       <c r="C22" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28" t="str">
+        <v xml:space="preserve"> • Led district in customer satisfaction scores for 18 consecutive months with 4.8/5.0 average rating</v>
+      </c>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3344,7 +3129,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3356,7 +3141,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3368,7 +3153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3380,7 +3165,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3392,7 +3177,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3404,7 +3189,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3416,7 +3201,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3428,7 +3213,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3440,7 +3225,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -4689,7 +4474,65 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sheetProtection sheet="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="G2:J2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="J3 G1:G23">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>OR(G1="Core",G1="Incidental")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:H18">
+    <cfRule type="expression" dxfId="10" priority="6">
+      <formula>OR(G3="Core",G3="Incidental",G3="Key Accomplishments")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J23">
+    <cfRule type="expression" dxfId="9" priority="7">
+      <formula>OR(J1="                                     Practices",J1="                                     Priorities")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L17:L18">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>OR(L17="Core",L17="Incidental")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L18">
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>OR(L18="Practices",L18="Priorities")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:G22">
+    <cfRule type="expression" dxfId="6" priority="9">
+      <formula>$H19&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:J21">
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>AND($H20="",$H19&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J19:J22">
+    <cfRule type="expression" dxfId="4" priority="11">
+      <formula>$H19&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H22:I22">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G22">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J22">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/careerstop.xlsx
+++ b/careerstop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29107"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29115"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\galja\pgaljan.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038209E8-FA6F-4D1B-B4AF-68B42B5A45C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{509D58E1-5167-4F96-B1F8-040E62EA0187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-37" windowWidth="28996" windowHeight="15675" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D14A6CAB-8ABE-4996-ABD5-087D26C23723}"/>
   </bookViews>
   <sheets>
     <sheet name="careerstop" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1276,7 +1276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1375,6 +1375,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1384,85 +1391,11 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <b/>
@@ -1481,6 +1414,15 @@
       </font>
     </dxf>
     <dxf>
+      <border>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1492,10 +1434,13 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
+      <border>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -1504,21 +1449,19 @@
       </font>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
-        <color theme="0"/>
+        <b/>
+        <i val="0"/>
       </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1552,6 +1495,23 @@
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1628,7 +1588,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="output!$G$1:$L$22" spid="_x0000_s1104"/>
+                  <a14:cameraTool cellRange="output!$G$1:$L$22" spid="_x0000_s1107"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -1689,7 +1649,7 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}" name="names" displayName="names" ref="A1:C135" totalsRowShown="0">
   <autoFilter ref="A1:C135" xr:uid="{FEDACFEC-E357-4205-A303-E06B7819AD81}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{B68AA56A-4332-4D26-AA2C-F1A53AF8F246}" name="index" dataDxfId="17">
       <calculatedColumnFormula>ROW()-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" xr3:uid="{2FBF4AE8-10BE-49DC-A08D-B377AD3CB245}" name="first"/>
@@ -2017,33 +1977,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3348163-AFAC-4B5E-B6D7-A630EDC47AB4}">
   <dimension ref="A1:AB147"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.73046875" customWidth="1"/>
-    <col min="3" max="3" width="1.06640625" customWidth="1"/>
-    <col min="4" max="4" width="23.73046875" customWidth="1"/>
-    <col min="5" max="5" width="3.46484375" customWidth="1"/>
-    <col min="7" max="7" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="3.86328125" customWidth="1"/>
-    <col min="9" max="9" width="25.86328125" customWidth="1"/>
-    <col min="10" max="10" width="3.46484375" customWidth="1"/>
-    <col min="11" max="11" width="9.6640625" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="25.86328125" customWidth="1"/>
-    <col min="13" max="13" width="3.86328125" customWidth="1"/>
-    <col min="14" max="14" width="25.86328125" customWidth="1"/>
-    <col min="15" max="15" width="3.86328125" customWidth="1"/>
-    <col min="16" max="16" width="25.86328125" customWidth="1"/>
-    <col min="17" max="17" width="3.86328125" customWidth="1"/>
-    <col min="18" max="18" width="23.46484375" customWidth="1"/>
-    <col min="28" max="28" width="9.06640625" style="23"/>
-    <col min="30" max="33" width="37.9296875" customWidth="1"/>
-    <col min="34" max="34" width="1.86328125" customWidth="1"/>
-    <col min="35" max="35" width="13.3984375" customWidth="1"/>
-    <col min="36" max="36" width="24.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" customWidth="1"/>
+    <col min="5" max="5" width="3.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.85546875" customWidth="1"/>
+    <col min="9" max="9" width="25.85546875" customWidth="1"/>
+    <col min="10" max="10" width="3.42578125" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="25.85546875" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" customWidth="1"/>
+    <col min="14" max="14" width="25.85546875" customWidth="1"/>
+    <col min="15" max="15" width="3.85546875" customWidth="1"/>
+    <col min="16" max="16" width="25.85546875" customWidth="1"/>
+    <col min="17" max="17" width="3.85546875" customWidth="1"/>
+    <col min="18" max="18" width="23.42578125" customWidth="1"/>
+    <col min="28" max="28" width="9" style="23"/>
+    <col min="30" max="33" width="38" customWidth="1"/>
+    <col min="34" max="34" width="1.85546875" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" customWidth="1"/>
+    <col min="36" max="36" width="24.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>15</v>
       </c>
@@ -2073,7 +2033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2111,7 +2071,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
@@ -2149,7 +2109,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
@@ -2187,7 +2147,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>13</v>
       </c>
@@ -2225,7 +2185,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>14</v>
       </c>
@@ -2261,7 +2221,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>2</v>
       </c>
@@ -2293,7 +2253,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>3</v>
       </c>
@@ -2325,7 +2285,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B9" s="25"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
@@ -2350,7 +2310,7 @@
       <c r="O9" s="6"/>
       <c r="P9" s="20"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F10" s="22" t="b">
         <v>0</v>
       </c>
@@ -2372,7 +2332,7 @@
       <c r="O10" s="6"/>
       <c r="P10" s="7"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F11" s="22" t="b">
         <v>0</v>
       </c>
@@ -2394,7 +2354,7 @@
       <c r="O11" s="6"/>
       <c r="P11" s="6"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F12" s="22" t="b">
         <v>0</v>
       </c>
@@ -2414,7 +2374,7 @@
       <c r="O12" s="6"/>
       <c r="P12" s="6"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F13" s="22" t="b">
         <v>0</v>
       </c>
@@ -2434,7 +2394,7 @@
       <c r="O13" s="6"/>
       <c r="P13" s="6"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F14" s="22" t="b">
         <v>0</v>
       </c>
@@ -2451,9 +2411,9 @@
       <c r="O14" s="6"/>
       <c r="P14" s="6"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F15" s="27"/>
-      <c r="G15" s="44"/>
+      <c r="G15" s="41"/>
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
@@ -2461,23 +2421,23 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="L15" s="45"/>
+      <c r="L15" s="20"/>
       <c r="M15" s="6"/>
       <c r="O15" s="6"/>
       <c r="P15" s="6"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G16" s="20"/>
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
       <c r="J16" s="6"/>
       <c r="K16" s="6"/>
-      <c r="L16" s="44"/>
+      <c r="L16" s="41"/>
       <c r="M16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>251</v>
       </c>
@@ -2499,12 +2459,12 @@
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
         <v>58</v>
       </c>
@@ -2514,7 +2474,7 @@
       <c r="C20" s="6"/>
       <c r="D20" s="6"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>61</v>
       </c>
@@ -2524,7 +2484,7 @@
       <c r="C21" s="6"/>
       <c r="D21" s="6"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
         <v>60</v>
       </c>
@@ -2534,7 +2494,7 @@
       <c r="C22" s="6"/>
       <c r="D22" s="6"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
         <v>59</v>
       </c>
@@ -2544,55 +2504,55 @@
       <c r="C23" s="6"/>
       <c r="D23" s="6"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="26"/>
       <c r="B24" s="6"/>
     </row>
-    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="147" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A20:A1048576 A1:A9 F1:F9 A15:A17">
-    <cfRule type="expression" dxfId="20" priority="9">
+  <conditionalFormatting sqref="A1:A9 F1:F9 A15:A17 A20:A1048576">
+    <cfRule type="expression" dxfId="16" priority="9">
       <formula>A1=""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A20:A23">
-    <cfRule type="expression" dxfId="19" priority="8">
+    <cfRule type="expression" dxfId="15" priority="8">
       <formula>B20=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B20:I23 B24">
-    <cfRule type="expression" dxfId="18" priority="4">
-      <formula>LEN($B20)&gt;149</formula>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="expression" dxfId="14" priority="22">
+      <formula>#REF!=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F14">
-    <cfRule type="expression" dxfId="17" priority="18">
-      <formula>$G2=""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD169:AD1048576 AD49:AD145 AD25">
-    <cfRule type="expression" dxfId="16" priority="17">
-      <formula>OR(AD25="Core",AD25="Incidental")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD25:AE25">
-    <cfRule type="expression" dxfId="15" priority="14">
-      <formula>OR(AD25="Core",AD25="Incidental",AD25="Key Accomplishments")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AG169:AG1048576 AG49:AG145 AG25">
-    <cfRule type="expression" dxfId="14" priority="15">
-      <formula>OR(AG25="                                     Practices",AG25="                                     Priorities")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="expression" dxfId="13" priority="22">
-      <formula>#REF!=""</formula>
+  <conditionalFormatting sqref="B20:I23 B24">
+    <cfRule type="expression" dxfId="13" priority="4">
+      <formula>LEN($B20)&gt;149</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24:I25">
     <cfRule type="expression" dxfId="12" priority="24">
       <formula>LEN(#REF!)&gt;149</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F14">
+    <cfRule type="expression" dxfId="11" priority="18">
+      <formula>$G2=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD25 AD49:AD145 AD169:AD1048576">
+    <cfRule type="expression" dxfId="10" priority="17">
+      <formula>OR(AD25="Core",AD25="Incidental")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD25:AE25">
+    <cfRule type="expression" dxfId="9" priority="14">
+      <formula>OR(AD25="Core",AD25="Incidental",AD25="Key Accomplishments")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AG25 AG49:AG145 AG169:AG1048576">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>OR(AG25="                                     Practices",AG25="                                     Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2604,15 +2564,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{175234B1-B47F-451A-9952-E15FBC3697C2}">
   <dimension ref="A1:L135"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="9.796875" customWidth="1"/>
-    <col min="7" max="10" width="33.265625" customWidth="1"/>
-    <col min="11" max="11" width="1.265625" customWidth="1"/>
+    <col min="1" max="3" width="9.85546875" customWidth="1"/>
+    <col min="7" max="10" width="33.28515625" customWidth="1"/>
+    <col min="11" max="11" width="1.28515625" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2631,12 +2591,12 @@
         <v>Store Manager with Acme Retail (Anytown USA)</v>
       </c>
       <c r="I1" s="39"/>
-      <c r="J1" s="43" t="str">
+      <c r="J1" s="40" t="str">
         <f>careerstop!B5&amp;" - "&amp;careerstop!B6</f>
         <v>Oct 2019 - Oct 2023</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <f t="shared" ref="A2:A33" si="0">ROW()-1</f>
         <v>1</v>
@@ -2647,15 +2607,15 @@
       <c r="C2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="40" t="str">
+      <c r="G2" s="42" t="str">
         <f>careerstop!B17</f>
         <v>Regional specialty retail chain with 25 locations across the Northeast focused on outdoor recreation and sporting goods with annual revenues of $45M and emphasis on customer experience and community engagement.</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="42"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="44"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -2685,7 +2645,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2712,7 +2672,7 @@
         <v xml:space="preserve">                                     Practices</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2736,7 +2696,7 @@
         <v xml:space="preserve">  • Daily Standups</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2760,7 +2720,7 @@
         <v xml:space="preserve">  • Performance Dashboards</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2784,7 +2744,7 @@
         <v xml:space="preserve">  • Mystery Shopping</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2808,7 +2768,7 @@
         <v xml:space="preserve">  • Staff Cross-training</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2832,7 +2792,7 @@
         <v xml:space="preserve">  • Standard Operating Procedures</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2852,7 +2812,7 @@
         <v xml:space="preserve">                                     Priorities</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2874,7 +2834,7 @@
         <v xml:space="preserve">  • Customer Satisfaction</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2901,7 +2861,7 @@
         <v xml:space="preserve">  • Operational Efficiency</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2925,7 +2885,7 @@
         <v xml:space="preserve">  • Team Development</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2949,7 +2909,7 @@
         <v xml:space="preserve">  • Brand Consistency</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2973,7 +2933,7 @@
         <v xml:space="preserve">  • Safety &amp; Compliance</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -3000,7 +2960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -3023,7 +2983,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -3042,7 +3002,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -3063,7 +3023,7 @@
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -3081,7 +3041,7 @@
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -3099,7 +3059,7 @@
       <c r="I21" s="28"/>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -3117,7 +3077,7 @@
       <c r="I22" s="28"/>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -3129,7 +3089,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3141,7 +3101,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3153,7 +3113,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3165,7 +3125,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3177,7 +3137,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3189,7 +3149,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3201,7 +3161,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3213,7 +3173,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3225,7 +3185,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3237,7 +3197,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3249,7 +3209,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
         <f t="shared" ref="A34:A65" si="1">ROW()-1</f>
         <v>33</v>
@@ -3261,7 +3221,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <f t="shared" si="1"/>
         <v>34</v>
@@ -3273,7 +3233,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
         <f t="shared" si="1"/>
         <v>35</v>
@@ -3285,7 +3245,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
         <f t="shared" si="1"/>
         <v>36</v>
@@ -3297,7 +3257,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
         <f t="shared" si="1"/>
         <v>37</v>
@@ -3309,7 +3269,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <f t="shared" si="1"/>
         <v>38</v>
@@ -3321,7 +3281,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
         <f t="shared" si="1"/>
         <v>39</v>
@@ -3333,7 +3293,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <f t="shared" si="1"/>
         <v>40</v>
@@ -3345,7 +3305,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
         <f t="shared" si="1"/>
         <v>41</v>
@@ -3357,7 +3317,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
         <f t="shared" si="1"/>
         <v>42</v>
@@ -3369,7 +3329,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
         <f t="shared" si="1"/>
         <v>43</v>
@@ -3381,7 +3341,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <f t="shared" si="1"/>
         <v>44</v>
@@ -3393,7 +3353,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
         <f t="shared" si="1"/>
         <v>45</v>
@@ -3405,7 +3365,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
         <f t="shared" si="1"/>
         <v>46</v>
@@ -3417,7 +3377,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
         <f t="shared" si="1"/>
         <v>47</v>
@@ -3429,7 +3389,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <f t="shared" si="1"/>
         <v>48</v>
@@ -3441,7 +3401,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
         <f t="shared" si="1"/>
         <v>49</v>
@@ -3453,7 +3413,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
         <f t="shared" si="1"/>
         <v>50</v>
@@ -3465,7 +3425,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <f t="shared" si="1"/>
         <v>51</v>
@@ -3477,7 +3437,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
         <f t="shared" si="1"/>
         <v>52</v>
@@ -3489,7 +3449,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
         <f t="shared" si="1"/>
         <v>53</v>
@@ -3501,7 +3461,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
         <f t="shared" si="1"/>
         <v>54</v>
@@ -3513,7 +3473,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <f t="shared" si="1"/>
         <v>55</v>
@@ -3525,7 +3485,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
         <f t="shared" si="1"/>
         <v>56</v>
@@ -3537,7 +3497,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
         <f t="shared" si="1"/>
         <v>57</v>
@@ -3549,7 +3509,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
         <f t="shared" si="1"/>
         <v>58</v>
@@ -3561,7 +3521,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <f t="shared" si="1"/>
         <v>59</v>
@@ -3573,7 +3533,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
         <f t="shared" si="1"/>
         <v>60</v>
@@ -3585,7 +3545,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
         <f t="shared" si="1"/>
         <v>61</v>
@@ -3597,7 +3557,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
         <f t="shared" si="1"/>
         <v>62</v>
@@ -3609,7 +3569,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
         <f t="shared" si="1"/>
         <v>63</v>
@@ -3621,7 +3581,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <f t="shared" si="1"/>
         <v>64</v>
@@ -3633,7 +3593,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
         <f t="shared" ref="A66:A97" si="2">ROW()-1</f>
         <v>65</v>
@@ -3645,7 +3605,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3657,7 +3617,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3669,7 +3629,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3681,7 +3641,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3693,7 +3653,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3705,7 +3665,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3717,7 +3677,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3729,7 +3689,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3741,7 +3701,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3753,7 +3713,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3765,7 +3725,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3777,7 +3737,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3789,7 +3749,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -3801,7 +3761,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
         <f t="shared" si="2"/>
         <v>79</v>
@@ -3813,7 +3773,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -3825,7 +3785,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -3837,7 +3797,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -3849,7 +3809,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -3861,7 +3821,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -3873,7 +3833,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -3885,7 +3845,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -3897,7 +3857,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -3909,7 +3869,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -3921,7 +3881,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90">
         <f t="shared" si="2"/>
         <v>89</v>
@@ -3933,7 +3893,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91">
         <f t="shared" si="2"/>
         <v>90</v>
@@ -3945,7 +3905,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92">
         <f t="shared" si="2"/>
         <v>91</v>
@@ -3957,7 +3917,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93">
         <f t="shared" si="2"/>
         <v>92</v>
@@ -3969,7 +3929,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <f t="shared" si="2"/>
         <v>93</v>
@@ -3981,7 +3941,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95">
         <f t="shared" si="2"/>
         <v>94</v>
@@ -3993,7 +3953,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96">
         <f t="shared" si="2"/>
         <v>95</v>
@@ -4005,7 +3965,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97">
         <f t="shared" si="2"/>
         <v>96</v>
@@ -4017,7 +3977,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98">
         <f t="shared" ref="A98:A129" si="3">ROW()-1</f>
         <v>97</v>
@@ -4029,7 +3989,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <f t="shared" si="3"/>
         <v>98</v>
@@ -4041,7 +4001,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100">
         <f t="shared" si="3"/>
         <v>99</v>
@@ -4053,7 +4013,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101">
         <f t="shared" si="3"/>
         <v>100</v>
@@ -4065,7 +4025,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102">
         <f t="shared" si="3"/>
         <v>101</v>
@@ -4077,7 +4037,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103">
         <f t="shared" si="3"/>
         <v>102</v>
@@ -4089,7 +4049,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <f t="shared" si="3"/>
         <v>103</v>
@@ -4101,7 +4061,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105">
         <f t="shared" si="3"/>
         <v>104</v>
@@ -4113,7 +4073,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106">
         <f t="shared" si="3"/>
         <v>105</v>
@@ -4125,7 +4085,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107">
         <f t="shared" si="3"/>
         <v>106</v>
@@ -4137,7 +4097,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108">
         <f t="shared" si="3"/>
         <v>107</v>
@@ -4149,7 +4109,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <f t="shared" si="3"/>
         <v>108</v>
@@ -4161,7 +4121,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110">
         <f t="shared" si="3"/>
         <v>109</v>
@@ -4173,7 +4133,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111">
         <f t="shared" si="3"/>
         <v>110</v>
@@ -4185,7 +4145,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112">
         <f t="shared" si="3"/>
         <v>111</v>
@@ -4197,7 +4157,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113">
         <f t="shared" si="3"/>
         <v>112</v>
@@ -4209,7 +4169,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <f t="shared" si="3"/>
         <v>113</v>
@@ -4221,7 +4181,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115">
         <f t="shared" si="3"/>
         <v>114</v>
@@ -4233,7 +4193,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116">
         <f t="shared" si="3"/>
         <v>115</v>
@@ -4245,7 +4205,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117">
         <f t="shared" si="3"/>
         <v>116</v>
@@ -4257,7 +4217,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <f t="shared" si="3"/>
         <v>117</v>
@@ -4269,7 +4229,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119">
         <f t="shared" si="3"/>
         <v>118</v>
@@ -4281,7 +4241,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <f t="shared" si="3"/>
         <v>119</v>
@@ -4293,7 +4253,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121">
         <f t="shared" si="3"/>
         <v>120</v>
@@ -4305,7 +4265,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122">
         <f t="shared" si="3"/>
         <v>121</v>
@@ -4317,7 +4277,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123">
         <f t="shared" si="3"/>
         <v>122</v>
@@ -4329,7 +4289,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124">
         <f t="shared" si="3"/>
         <v>123</v>
@@ -4341,7 +4301,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <f t="shared" si="3"/>
         <v>124</v>
@@ -4353,7 +4313,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126">
         <f t="shared" si="3"/>
         <v>125</v>
@@ -4365,7 +4325,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127">
         <f t="shared" si="3"/>
         <v>126</v>
@@ -4377,7 +4337,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128">
         <f t="shared" si="3"/>
         <v>127</v>
@@ -4389,7 +4349,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129">
         <f t="shared" si="3"/>
         <v>128</v>
@@ -4401,7 +4361,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <f t="shared" ref="A130:A135" si="4">ROW()-1</f>
         <v>129</v>
@@ -4413,7 +4373,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131">
         <f t="shared" si="4"/>
         <v>130</v>
@@ -4425,7 +4385,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132">
         <f t="shared" si="4"/>
         <v>131</v>
@@ -4437,7 +4397,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133">
         <f t="shared" si="4"/>
         <v>132</v>
@@ -4449,7 +4409,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134">
         <f t="shared" si="4"/>
         <v>133</v>
@@ -4461,7 +4421,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <f t="shared" si="4"/>
         <v>134</v>
@@ -4478,29 +4438,9 @@
   <mergeCells count="1">
     <mergeCell ref="G2:J2"/>
   </mergeCells>
-  <conditionalFormatting sqref="J3 G1:G23">
-    <cfRule type="expression" dxfId="11" priority="8">
+  <conditionalFormatting sqref="G1:G23 J3">
+    <cfRule type="expression" dxfId="7" priority="8">
       <formula>OR(G1="Core",G1="Incidental")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3:H18">
-    <cfRule type="expression" dxfId="10" priority="6">
-      <formula>OR(G3="Core",G3="Incidental",G3="Key Accomplishments")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:J23">
-    <cfRule type="expression" dxfId="9" priority="7">
-      <formula>OR(J1="                                     Practices",J1="                                     Priorities")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L17:L18">
-    <cfRule type="expression" dxfId="8" priority="5">
-      <formula>OR(L17="Core",L17="Incidental")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L18">
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>OR(L18="Practices",L18="Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G19:G22">
@@ -4508,29 +4448,34 @@
       <formula>$H19&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19:J21">
-    <cfRule type="expression" dxfId="5" priority="10">
+  <conditionalFormatting sqref="G3:H18">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>OR(G3="Core",G3="Incidental",G3="Key Accomplishments")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19:J22">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>AND($H20="",$H19&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J1:J23">
+    <cfRule type="expression" dxfId="3" priority="7">
+      <formula>OR(J1="                                     Practices",J1="                                     Priorities")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="J19:J22">
-    <cfRule type="expression" dxfId="4" priority="11">
+    <cfRule type="expression" dxfId="2" priority="11">
       <formula>$H19&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H22:I22">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="L17:L18">
+    <cfRule type="expression" dxfId="1" priority="5">
+      <formula>OR(L17="Core",L17="Incidental")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G22">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J22">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND($H23="",$H22&lt;&gt;"")</formula>
+  <conditionalFormatting sqref="L18">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>OR(L18="Practices",L18="Priorities")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
